--- a/backend/assets/templates/sip-v1.xlsx
+++ b/backend/assets/templates/sip-v1.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIP检验记录" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="气泡图" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SIP检验记录" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="气泡图" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SIP检验记录'!$A$5:$H$69</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'SIP检验记录'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'SIP检验记录'!$A$1:$H$74</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'SIP检验记录'!$A$1:$H$522</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'气泡图'!$A$1:$R$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -141,7 +141,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -387,11 +387,44 @@
         <color rgb="00FFFFFF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -554,6 +587,7 @@
     <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -631,7 +665,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -646,13 +680,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -950,7 +987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1016,7 +1053,7 @@
           <t>产品报检</t>
         </is>
       </c>
-      <c r="B4" s="31" t="n"/>
+      <c r="B4" s="55" t="n"/>
       <c r="C4" s="32" t="inlineStr">
         <is>
           <t>外观检验</t>
@@ -1027,7 +1064,7 @@
           <t>尺寸检验</t>
         </is>
       </c>
-      <c r="E4" s="33" t="n"/>
+      <c r="E4" s="55" t="n"/>
       <c r="F4" s="34" t="inlineStr">
         <is>
           <t>螺纹检验</t>
@@ -1038,7 +1075,7 @@
           <t>流入下道工序</t>
         </is>
       </c>
-      <c r="H4" s="35" t="n"/>
+      <c r="H4" s="55" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="36" t="inlineStr">
@@ -1076,7 +1113,7 @@
           <t>来源页码</t>
         </is>
       </c>
-      <c r="H5" s="37" t="n"/>
+      <c r="H5" s="16" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="38" t="n"/>
@@ -1086,7 +1123,7 @@
       <c r="E6" s="38" t="n"/>
       <c r="F6" s="38" t="n"/>
       <c r="G6" s="38" t="n"/>
-      <c r="H6" s="39" t="n"/>
+      <c r="H6" s="15" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="38" t="n"/>
@@ -1096,7 +1133,7 @@
       <c r="E7" s="38" t="n"/>
       <c r="F7" s="38" t="n"/>
       <c r="G7" s="38" t="n"/>
-      <c r="H7" s="39" t="n"/>
+      <c r="H7" s="15" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="38" t="n"/>
@@ -1106,7 +1143,7 @@
       <c r="E8" s="38" t="n"/>
       <c r="F8" s="38" t="n"/>
       <c r="G8" s="38" t="n"/>
-      <c r="H8" s="39" t="n"/>
+      <c r="H8" s="15" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="38" t="n"/>
@@ -1116,7 +1153,7 @@
       <c r="E9" s="38" t="n"/>
       <c r="F9" s="38" t="n"/>
       <c r="G9" s="38" t="n"/>
-      <c r="H9" s="39" t="n"/>
+      <c r="H9" s="15" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="38" t="n"/>
@@ -1126,7 +1163,7 @@
       <c r="E10" s="38" t="n"/>
       <c r="F10" s="38" t="n"/>
       <c r="G10" s="38" t="n"/>
-      <c r="H10" s="39" t="n"/>
+      <c r="H10" s="15" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="38" t="n"/>
@@ -1136,7 +1173,7 @@
       <c r="E11" s="38" t="n"/>
       <c r="F11" s="38" t="n"/>
       <c r="G11" s="38" t="n"/>
-      <c r="H11" s="39" t="n"/>
+      <c r="H11" s="15" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="38" t="n"/>
@@ -1146,7 +1183,7 @@
       <c r="E12" s="38" t="n"/>
       <c r="F12" s="38" t="n"/>
       <c r="G12" s="38" t="n"/>
-      <c r="H12" s="39" t="n"/>
+      <c r="H12" s="15" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="38" t="n"/>
@@ -1156,7 +1193,7 @@
       <c r="E13" s="38" t="n"/>
       <c r="F13" s="38" t="n"/>
       <c r="G13" s="38" t="n"/>
-      <c r="H13" s="39" t="n"/>
+      <c r="H13" s="15" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="38" t="n"/>
@@ -1166,7 +1203,7 @@
       <c r="E14" s="38" t="n"/>
       <c r="F14" s="38" t="n"/>
       <c r="G14" s="38" t="n"/>
-      <c r="H14" s="39" t="n"/>
+      <c r="H14" s="15" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="38" t="n"/>
@@ -1176,7 +1213,7 @@
       <c r="E15" s="38" t="n"/>
       <c r="F15" s="38" t="n"/>
       <c r="G15" s="38" t="n"/>
-      <c r="H15" s="39" t="n"/>
+      <c r="H15" s="15" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="38" t="n"/>
@@ -1186,7 +1223,7 @@
       <c r="E16" s="38" t="n"/>
       <c r="F16" s="38" t="n"/>
       <c r="G16" s="38" t="n"/>
-      <c r="H16" s="39" t="n"/>
+      <c r="H16" s="15" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="38" t="n"/>
@@ -1196,7 +1233,7 @@
       <c r="E17" s="38" t="n"/>
       <c r="F17" s="38" t="n"/>
       <c r="G17" s="38" t="n"/>
-      <c r="H17" s="39" t="n"/>
+      <c r="H17" s="15" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="38" t="n"/>
@@ -1206,7 +1243,7 @@
       <c r="E18" s="38" t="n"/>
       <c r="F18" s="38" t="n"/>
       <c r="G18" s="38" t="n"/>
-      <c r="H18" s="39" t="n"/>
+      <c r="H18" s="15" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="38" t="n"/>
@@ -1216,7 +1253,7 @@
       <c r="E19" s="38" t="n"/>
       <c r="F19" s="38" t="n"/>
       <c r="G19" s="38" t="n"/>
-      <c r="H19" s="39" t="n"/>
+      <c r="H19" s="15" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="38" t="n"/>
@@ -1226,7 +1263,7 @@
       <c r="E20" s="38" t="n"/>
       <c r="F20" s="38" t="n"/>
       <c r="G20" s="38" t="n"/>
-      <c r="H20" s="39" t="n"/>
+      <c r="H20" s="15" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="38" t="n"/>
@@ -1236,7 +1273,7 @@
       <c r="E21" s="38" t="n"/>
       <c r="F21" s="38" t="n"/>
       <c r="G21" s="38" t="n"/>
-      <c r="H21" s="39" t="n"/>
+      <c r="H21" s="15" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="38" t="n"/>
@@ -1246,7 +1283,7 @@
       <c r="E22" s="38" t="n"/>
       <c r="F22" s="38" t="n"/>
       <c r="G22" s="38" t="n"/>
-      <c r="H22" s="39" t="n"/>
+      <c r="H22" s="15" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="38" t="n"/>
@@ -1256,7 +1293,7 @@
       <c r="E23" s="38" t="n"/>
       <c r="F23" s="38" t="n"/>
       <c r="G23" s="38" t="n"/>
-      <c r="H23" s="39" t="n"/>
+      <c r="H23" s="15" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="38" t="n"/>
@@ -1266,7 +1303,7 @@
       <c r="E24" s="38" t="n"/>
       <c r="F24" s="38" t="n"/>
       <c r="G24" s="38" t="n"/>
-      <c r="H24" s="39" t="n"/>
+      <c r="H24" s="15" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="38" t="n"/>
@@ -1276,7 +1313,7 @@
       <c r="E25" s="38" t="n"/>
       <c r="F25" s="38" t="n"/>
       <c r="G25" s="38" t="n"/>
-      <c r="H25" s="39" t="n"/>
+      <c r="H25" s="15" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="38" t="n"/>
@@ -1286,7 +1323,7 @@
       <c r="E26" s="38" t="n"/>
       <c r="F26" s="38" t="n"/>
       <c r="G26" s="38" t="n"/>
-      <c r="H26" s="39" t="n"/>
+      <c r="H26" s="15" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="38" t="n"/>
@@ -1296,7 +1333,7 @@
       <c r="E27" s="38" t="n"/>
       <c r="F27" s="38" t="n"/>
       <c r="G27" s="38" t="n"/>
-      <c r="H27" s="39" t="n"/>
+      <c r="H27" s="15" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="38" t="n"/>
@@ -1306,7 +1343,7 @@
       <c r="E28" s="38" t="n"/>
       <c r="F28" s="38" t="n"/>
       <c r="G28" s="38" t="n"/>
-      <c r="H28" s="39" t="n"/>
+      <c r="H28" s="15" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="38" t="n"/>
@@ -1316,7 +1353,7 @@
       <c r="E29" s="38" t="n"/>
       <c r="F29" s="38" t="n"/>
       <c r="G29" s="38" t="n"/>
-      <c r="H29" s="39" t="n"/>
+      <c r="H29" s="15" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="38" t="n"/>
@@ -1326,7 +1363,7 @@
       <c r="E30" s="38" t="n"/>
       <c r="F30" s="38" t="n"/>
       <c r="G30" s="38" t="n"/>
-      <c r="H30" s="39" t="n"/>
+      <c r="H30" s="15" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="38" t="n"/>
@@ -1336,7 +1373,7 @@
       <c r="E31" s="38" t="n"/>
       <c r="F31" s="38" t="n"/>
       <c r="G31" s="38" t="n"/>
-      <c r="H31" s="39" t="n"/>
+      <c r="H31" s="15" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="38" t="n"/>
@@ -1346,7 +1383,7 @@
       <c r="E32" s="38" t="n"/>
       <c r="F32" s="38" t="n"/>
       <c r="G32" s="38" t="n"/>
-      <c r="H32" s="39" t="n"/>
+      <c r="H32" s="15" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="38" t="n"/>
@@ -1356,7 +1393,7 @@
       <c r="E33" s="38" t="n"/>
       <c r="F33" s="38" t="n"/>
       <c r="G33" s="38" t="n"/>
-      <c r="H33" s="39" t="n"/>
+      <c r="H33" s="15" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="38" t="n"/>
@@ -1366,7 +1403,7 @@
       <c r="E34" s="38" t="n"/>
       <c r="F34" s="38" t="n"/>
       <c r="G34" s="38" t="n"/>
-      <c r="H34" s="39" t="n"/>
+      <c r="H34" s="15" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="38" t="n"/>
@@ -1376,7 +1413,7 @@
       <c r="E35" s="38" t="n"/>
       <c r="F35" s="38" t="n"/>
       <c r="G35" s="38" t="n"/>
-      <c r="H35" s="39" t="n"/>
+      <c r="H35" s="15" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="38" t="n"/>
@@ -1386,7 +1423,7 @@
       <c r="E36" s="38" t="n"/>
       <c r="F36" s="38" t="n"/>
       <c r="G36" s="38" t="n"/>
-      <c r="H36" s="39" t="n"/>
+      <c r="H36" s="15" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="38" t="n"/>
@@ -1396,7 +1433,7 @@
       <c r="E37" s="38" t="n"/>
       <c r="F37" s="38" t="n"/>
       <c r="G37" s="38" t="n"/>
-      <c r="H37" s="39" t="n"/>
+      <c r="H37" s="15" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="38" t="n"/>
@@ -1406,7 +1443,7 @@
       <c r="E38" s="38" t="n"/>
       <c r="F38" s="38" t="n"/>
       <c r="G38" s="38" t="n"/>
-      <c r="H38" s="39" t="n"/>
+      <c r="H38" s="15" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="38" t="n"/>
@@ -1416,7 +1453,7 @@
       <c r="E39" s="38" t="n"/>
       <c r="F39" s="38" t="n"/>
       <c r="G39" s="38" t="n"/>
-      <c r="H39" s="39" t="n"/>
+      <c r="H39" s="15" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="38" t="n"/>
@@ -1426,7 +1463,7 @@
       <c r="E40" s="38" t="n"/>
       <c r="F40" s="38" t="n"/>
       <c r="G40" s="38" t="n"/>
-      <c r="H40" s="39" t="n"/>
+      <c r="H40" s="15" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="38" t="n"/>
@@ -1436,7 +1473,7 @@
       <c r="E41" s="38" t="n"/>
       <c r="F41" s="38" t="n"/>
       <c r="G41" s="38" t="n"/>
-      <c r="H41" s="39" t="n"/>
+      <c r="H41" s="15" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="38" t="n"/>
@@ -1446,7 +1483,7 @@
       <c r="E42" s="38" t="n"/>
       <c r="F42" s="38" t="n"/>
       <c r="G42" s="38" t="n"/>
-      <c r="H42" s="39" t="n"/>
+      <c r="H42" s="15" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="38" t="n"/>
@@ -1456,7 +1493,7 @@
       <c r="E43" s="38" t="n"/>
       <c r="F43" s="38" t="n"/>
       <c r="G43" s="38" t="n"/>
-      <c r="H43" s="39" t="n"/>
+      <c r="H43" s="15" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="38" t="n"/>
@@ -1466,7 +1503,7 @@
       <c r="E44" s="38" t="n"/>
       <c r="F44" s="38" t="n"/>
       <c r="G44" s="38" t="n"/>
-      <c r="H44" s="39" t="n"/>
+      <c r="H44" s="15" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="38" t="n"/>
@@ -1476,7 +1513,7 @@
       <c r="E45" s="38" t="n"/>
       <c r="F45" s="38" t="n"/>
       <c r="G45" s="38" t="n"/>
-      <c r="H45" s="39" t="n"/>
+      <c r="H45" s="15" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="38" t="n"/>
@@ -1486,7 +1523,7 @@
       <c r="E46" s="38" t="n"/>
       <c r="F46" s="38" t="n"/>
       <c r="G46" s="38" t="n"/>
-      <c r="H46" s="39" t="n"/>
+      <c r="H46" s="15" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="38" t="n"/>
@@ -1496,7 +1533,7 @@
       <c r="E47" s="38" t="n"/>
       <c r="F47" s="38" t="n"/>
       <c r="G47" s="38" t="n"/>
-      <c r="H47" s="39" t="n"/>
+      <c r="H47" s="15" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="38" t="n"/>
@@ -1506,7 +1543,7 @@
       <c r="E48" s="38" t="n"/>
       <c r="F48" s="38" t="n"/>
       <c r="G48" s="38" t="n"/>
-      <c r="H48" s="39" t="n"/>
+      <c r="H48" s="15" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="38" t="n"/>
@@ -1516,7 +1553,7 @@
       <c r="E49" s="38" t="n"/>
       <c r="F49" s="38" t="n"/>
       <c r="G49" s="38" t="n"/>
-      <c r="H49" s="39" t="n"/>
+      <c r="H49" s="15" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="38" t="n"/>
@@ -1526,7 +1563,7 @@
       <c r="E50" s="38" t="n"/>
       <c r="F50" s="38" t="n"/>
       <c r="G50" s="38" t="n"/>
-      <c r="H50" s="39" t="n"/>
+      <c r="H50" s="15" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="38" t="n"/>
@@ -1536,7 +1573,7 @@
       <c r="E51" s="38" t="n"/>
       <c r="F51" s="38" t="n"/>
       <c r="G51" s="38" t="n"/>
-      <c r="H51" s="39" t="n"/>
+      <c r="H51" s="15" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="38" t="n"/>
@@ -1546,7 +1583,7 @@
       <c r="E52" s="38" t="n"/>
       <c r="F52" s="38" t="n"/>
       <c r="G52" s="38" t="n"/>
-      <c r="H52" s="39" t="n"/>
+      <c r="H52" s="15" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="38" t="n"/>
@@ -1556,7 +1593,7 @@
       <c r="E53" s="38" t="n"/>
       <c r="F53" s="38" t="n"/>
       <c r="G53" s="38" t="n"/>
-      <c r="H53" s="39" t="n"/>
+      <c r="H53" s="15" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="38" t="n"/>
@@ -1566,7 +1603,7 @@
       <c r="E54" s="38" t="n"/>
       <c r="F54" s="38" t="n"/>
       <c r="G54" s="38" t="n"/>
-      <c r="H54" s="39" t="n"/>
+      <c r="H54" s="15" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="38" t="n"/>
@@ -1576,7 +1613,7 @@
       <c r="E55" s="38" t="n"/>
       <c r="F55" s="38" t="n"/>
       <c r="G55" s="38" t="n"/>
-      <c r="H55" s="39" t="n"/>
+      <c r="H55" s="15" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="38" t="n"/>
@@ -1586,7 +1623,7 @@
       <c r="E56" s="38" t="n"/>
       <c r="F56" s="38" t="n"/>
       <c r="G56" s="38" t="n"/>
-      <c r="H56" s="39" t="n"/>
+      <c r="H56" s="15" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="38" t="n"/>
@@ -1596,7 +1633,7 @@
       <c r="E57" s="38" t="n"/>
       <c r="F57" s="38" t="n"/>
       <c r="G57" s="38" t="n"/>
-      <c r="H57" s="39" t="n"/>
+      <c r="H57" s="15" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="38" t="n"/>
@@ -1606,7 +1643,7 @@
       <c r="E58" s="38" t="n"/>
       <c r="F58" s="38" t="n"/>
       <c r="G58" s="38" t="n"/>
-      <c r="H58" s="39" t="n"/>
+      <c r="H58" s="15" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="38" t="n"/>
@@ -1616,7 +1653,7 @@
       <c r="E59" s="38" t="n"/>
       <c r="F59" s="38" t="n"/>
       <c r="G59" s="38" t="n"/>
-      <c r="H59" s="39" t="n"/>
+      <c r="H59" s="15" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="38" t="n"/>
@@ -1626,7 +1663,7 @@
       <c r="E60" s="38" t="n"/>
       <c r="F60" s="38" t="n"/>
       <c r="G60" s="38" t="n"/>
-      <c r="H60" s="39" t="n"/>
+      <c r="H60" s="15" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="38" t="n"/>
@@ -1636,7 +1673,7 @@
       <c r="E61" s="38" t="n"/>
       <c r="F61" s="38" t="n"/>
       <c r="G61" s="38" t="n"/>
-      <c r="H61" s="39" t="n"/>
+      <c r="H61" s="15" t="n"/>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="38" t="n"/>
@@ -1646,7 +1683,7 @@
       <c r="E62" s="38" t="n"/>
       <c r="F62" s="38" t="n"/>
       <c r="G62" s="38" t="n"/>
-      <c r="H62" s="39" t="n"/>
+      <c r="H62" s="15" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="38" t="n"/>
@@ -1656,7 +1693,7 @@
       <c r="E63" s="38" t="n"/>
       <c r="F63" s="38" t="n"/>
       <c r="G63" s="38" t="n"/>
-      <c r="H63" s="39" t="n"/>
+      <c r="H63" s="15" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="38" t="n"/>
@@ -1666,7 +1703,7 @@
       <c r="E64" s="38" t="n"/>
       <c r="F64" s="38" t="n"/>
       <c r="G64" s="38" t="n"/>
-      <c r="H64" s="39" t="n"/>
+      <c r="H64" s="15" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="38" t="n"/>
@@ -1676,7 +1713,7 @@
       <c r="E65" s="38" t="n"/>
       <c r="F65" s="38" t="n"/>
       <c r="G65" s="38" t="n"/>
-      <c r="H65" s="39" t="n"/>
+      <c r="H65" s="15" t="n"/>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="38" t="n"/>
@@ -1686,7 +1723,7 @@
       <c r="E66" s="38" t="n"/>
       <c r="F66" s="38" t="n"/>
       <c r="G66" s="38" t="n"/>
-      <c r="H66" s="39" t="n"/>
+      <c r="H66" s="15" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="38" t="n"/>
@@ -1696,7 +1733,7 @@
       <c r="E67" s="38" t="n"/>
       <c r="F67" s="38" t="n"/>
       <c r="G67" s="38" t="n"/>
-      <c r="H67" s="39" t="n"/>
+      <c r="H67" s="15" t="n"/>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="38" t="n"/>
@@ -1706,7 +1743,7 @@
       <c r="E68" s="38" t="n"/>
       <c r="F68" s="38" t="n"/>
       <c r="G68" s="38" t="n"/>
-      <c r="H68" s="39" t="n"/>
+      <c r="H68" s="15" t="n"/>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="40" t="n"/>
@@ -1716,196 +1753,5124 @@
       <c r="E69" s="40" t="n"/>
       <c r="F69" s="40" t="n"/>
       <c r="G69" s="40" t="n"/>
-      <c r="H69" s="41" t="n"/>
+      <c r="H69" s="17" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="42" t="inlineStr">
+      <c r="A70" s="40" t="n"/>
+      <c r="B70" s="40" t="n"/>
+      <c r="C70" s="40" t="n"/>
+      <c r="D70" s="40" t="n"/>
+      <c r="E70" s="40" t="n"/>
+      <c r="F70" s="40" t="n"/>
+      <c r="G70" s="40" t="n"/>
+      <c r="H70" s="17" t="n"/>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="40" t="n"/>
+      <c r="B71" s="40" t="n"/>
+      <c r="C71" s="40" t="n"/>
+      <c r="D71" s="40" t="n"/>
+      <c r="E71" s="40" t="n"/>
+      <c r="F71" s="40" t="n"/>
+      <c r="G71" s="40" t="n"/>
+      <c r="H71" s="17" t="n"/>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="40" t="n"/>
+      <c r="B72" s="40" t="n"/>
+      <c r="C72" s="40" t="n"/>
+      <c r="D72" s="40" t="n"/>
+      <c r="E72" s="40" t="n"/>
+      <c r="F72" s="40" t="n"/>
+      <c r="G72" s="40" t="n"/>
+      <c r="H72" s="17" t="n"/>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="40" t="n"/>
+      <c r="B73" s="40" t="n"/>
+      <c r="C73" s="40" t="n"/>
+      <c r="D73" s="40" t="n"/>
+      <c r="E73" s="40" t="n"/>
+      <c r="F73" s="40" t="n"/>
+      <c r="G73" s="40" t="n"/>
+      <c r="H73" s="17" t="n"/>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="40" t="n"/>
+      <c r="B74" s="40" t="n"/>
+      <c r="C74" s="40" t="n"/>
+      <c r="D74" s="40" t="n"/>
+      <c r="E74" s="40" t="n"/>
+      <c r="F74" s="40" t="n"/>
+      <c r="G74" s="40" t="n"/>
+      <c r="H74" s="17" t="n"/>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="40" t="n"/>
+      <c r="B75" s="40" t="n"/>
+      <c r="C75" s="40" t="n"/>
+      <c r="D75" s="40" t="n"/>
+      <c r="E75" s="40" t="n"/>
+      <c r="F75" s="40" t="n"/>
+      <c r="G75" s="40" t="n"/>
+      <c r="H75" s="17" t="n"/>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="40" t="n"/>
+      <c r="B76" s="40" t="n"/>
+      <c r="C76" s="40" t="n"/>
+      <c r="D76" s="40" t="n"/>
+      <c r="E76" s="40" t="n"/>
+      <c r="F76" s="40" t="n"/>
+      <c r="G76" s="40" t="n"/>
+      <c r="H76" s="17" t="n"/>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="40" t="n"/>
+      <c r="B77" s="40" t="n"/>
+      <c r="C77" s="40" t="n"/>
+      <c r="D77" s="40" t="n"/>
+      <c r="E77" s="40" t="n"/>
+      <c r="F77" s="40" t="n"/>
+      <c r="G77" s="40" t="n"/>
+      <c r="H77" s="17" t="n"/>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="40" t="n"/>
+      <c r="B78" s="40" t="n"/>
+      <c r="C78" s="40" t="n"/>
+      <c r="D78" s="40" t="n"/>
+      <c r="E78" s="40" t="n"/>
+      <c r="F78" s="40" t="n"/>
+      <c r="G78" s="40" t="n"/>
+      <c r="H78" s="17" t="n"/>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="40" t="n"/>
+      <c r="B79" s="40" t="n"/>
+      <c r="C79" s="40" t="n"/>
+      <c r="D79" s="40" t="n"/>
+      <c r="E79" s="40" t="n"/>
+      <c r="F79" s="40" t="n"/>
+      <c r="G79" s="40" t="n"/>
+      <c r="H79" s="17" t="n"/>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="40" t="n"/>
+      <c r="B80" s="40" t="n"/>
+      <c r="C80" s="40" t="n"/>
+      <c r="D80" s="40" t="n"/>
+      <c r="E80" s="40" t="n"/>
+      <c r="F80" s="40" t="n"/>
+      <c r="G80" s="40" t="n"/>
+      <c r="H80" s="17" t="n"/>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="40" t="n"/>
+      <c r="B81" s="40" t="n"/>
+      <c r="C81" s="40" t="n"/>
+      <c r="D81" s="40" t="n"/>
+      <c r="E81" s="40" t="n"/>
+      <c r="F81" s="40" t="n"/>
+      <c r="G81" s="40" t="n"/>
+      <c r="H81" s="17" t="n"/>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="40" t="n"/>
+      <c r="B82" s="40" t="n"/>
+      <c r="C82" s="40" t="n"/>
+      <c r="D82" s="40" t="n"/>
+      <c r="E82" s="40" t="n"/>
+      <c r="F82" s="40" t="n"/>
+      <c r="G82" s="40" t="n"/>
+      <c r="H82" s="17" t="n"/>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="40" t="n"/>
+      <c r="B83" s="40" t="n"/>
+      <c r="C83" s="40" t="n"/>
+      <c r="D83" s="40" t="n"/>
+      <c r="E83" s="40" t="n"/>
+      <c r="F83" s="40" t="n"/>
+      <c r="G83" s="40" t="n"/>
+      <c r="H83" s="17" t="n"/>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="40" t="n"/>
+      <c r="B84" s="40" t="n"/>
+      <c r="C84" s="40" t="n"/>
+      <c r="D84" s="40" t="n"/>
+      <c r="E84" s="40" t="n"/>
+      <c r="F84" s="40" t="n"/>
+      <c r="G84" s="40" t="n"/>
+      <c r="H84" s="17" t="n"/>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="40" t="n"/>
+      <c r="B85" s="40" t="n"/>
+      <c r="C85" s="40" t="n"/>
+      <c r="D85" s="40" t="n"/>
+      <c r="E85" s="40" t="n"/>
+      <c r="F85" s="40" t="n"/>
+      <c r="G85" s="40" t="n"/>
+      <c r="H85" s="17" t="n"/>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="40" t="n"/>
+      <c r="B86" s="40" t="n"/>
+      <c r="C86" s="40" t="n"/>
+      <c r="D86" s="40" t="n"/>
+      <c r="E86" s="40" t="n"/>
+      <c r="F86" s="40" t="n"/>
+      <c r="G86" s="40" t="n"/>
+      <c r="H86" s="17" t="n"/>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="40" t="n"/>
+      <c r="B87" s="40" t="n"/>
+      <c r="C87" s="40" t="n"/>
+      <c r="D87" s="40" t="n"/>
+      <c r="E87" s="40" t="n"/>
+      <c r="F87" s="40" t="n"/>
+      <c r="G87" s="40" t="n"/>
+      <c r="H87" s="17" t="n"/>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="40" t="n"/>
+      <c r="B88" s="40" t="n"/>
+      <c r="C88" s="40" t="n"/>
+      <c r="D88" s="40" t="n"/>
+      <c r="E88" s="40" t="n"/>
+      <c r="F88" s="40" t="n"/>
+      <c r="G88" s="40" t="n"/>
+      <c r="H88" s="17" t="n"/>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="40" t="n"/>
+      <c r="B89" s="40" t="n"/>
+      <c r="C89" s="40" t="n"/>
+      <c r="D89" s="40" t="n"/>
+      <c r="E89" s="40" t="n"/>
+      <c r="F89" s="40" t="n"/>
+      <c r="G89" s="40" t="n"/>
+      <c r="H89" s="17" t="n"/>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="40" t="n"/>
+      <c r="B90" s="40" t="n"/>
+      <c r="C90" s="40" t="n"/>
+      <c r="D90" s="40" t="n"/>
+      <c r="E90" s="40" t="n"/>
+      <c r="F90" s="40" t="n"/>
+      <c r="G90" s="40" t="n"/>
+      <c r="H90" s="17" t="n"/>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="40" t="n"/>
+      <c r="B91" s="40" t="n"/>
+      <c r="C91" s="40" t="n"/>
+      <c r="D91" s="40" t="n"/>
+      <c r="E91" s="40" t="n"/>
+      <c r="F91" s="40" t="n"/>
+      <c r="G91" s="40" t="n"/>
+      <c r="H91" s="17" t="n"/>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="40" t="n"/>
+      <c r="B92" s="40" t="n"/>
+      <c r="C92" s="40" t="n"/>
+      <c r="D92" s="40" t="n"/>
+      <c r="E92" s="40" t="n"/>
+      <c r="F92" s="40" t="n"/>
+      <c r="G92" s="40" t="n"/>
+      <c r="H92" s="17" t="n"/>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="40" t="n"/>
+      <c r="B93" s="40" t="n"/>
+      <c r="C93" s="40" t="n"/>
+      <c r="D93" s="40" t="n"/>
+      <c r="E93" s="40" t="n"/>
+      <c r="F93" s="40" t="n"/>
+      <c r="G93" s="40" t="n"/>
+      <c r="H93" s="17" t="n"/>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="40" t="n"/>
+      <c r="B94" s="40" t="n"/>
+      <c r="C94" s="40" t="n"/>
+      <c r="D94" s="40" t="n"/>
+      <c r="E94" s="40" t="n"/>
+      <c r="F94" s="40" t="n"/>
+      <c r="G94" s="40" t="n"/>
+      <c r="H94" s="17" t="n"/>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="40" t="n"/>
+      <c r="B95" s="40" t="n"/>
+      <c r="C95" s="40" t="n"/>
+      <c r="D95" s="40" t="n"/>
+      <c r="E95" s="40" t="n"/>
+      <c r="F95" s="40" t="n"/>
+      <c r="G95" s="40" t="n"/>
+      <c r="H95" s="17" t="n"/>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="40" t="n"/>
+      <c r="B96" s="40" t="n"/>
+      <c r="C96" s="40" t="n"/>
+      <c r="D96" s="40" t="n"/>
+      <c r="E96" s="40" t="n"/>
+      <c r="F96" s="40" t="n"/>
+      <c r="G96" s="40" t="n"/>
+      <c r="H96" s="17" t="n"/>
+    </row>
+    <row r="97" ht="22" customHeight="1">
+      <c r="A97" s="40" t="n"/>
+      <c r="B97" s="40" t="n"/>
+      <c r="C97" s="40" t="n"/>
+      <c r="D97" s="40" t="n"/>
+      <c r="E97" s="40" t="n"/>
+      <c r="F97" s="40" t="n"/>
+      <c r="G97" s="40" t="n"/>
+      <c r="H97" s="17" t="n"/>
+    </row>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="40" t="n"/>
+      <c r="B98" s="40" t="n"/>
+      <c r="C98" s="40" t="n"/>
+      <c r="D98" s="40" t="n"/>
+      <c r="E98" s="40" t="n"/>
+      <c r="F98" s="40" t="n"/>
+      <c r="G98" s="40" t="n"/>
+      <c r="H98" s="17" t="n"/>
+    </row>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="40" t="n"/>
+      <c r="B99" s="40" t="n"/>
+      <c r="C99" s="40" t="n"/>
+      <c r="D99" s="40" t="n"/>
+      <c r="E99" s="40" t="n"/>
+      <c r="F99" s="40" t="n"/>
+      <c r="G99" s="40" t="n"/>
+      <c r="H99" s="17" t="n"/>
+    </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="40" t="n"/>
+      <c r="B100" s="40" t="n"/>
+      <c r="C100" s="40" t="n"/>
+      <c r="D100" s="40" t="n"/>
+      <c r="E100" s="40" t="n"/>
+      <c r="F100" s="40" t="n"/>
+      <c r="G100" s="40" t="n"/>
+      <c r="H100" s="17" t="n"/>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="40" t="n"/>
+      <c r="B101" s="40" t="n"/>
+      <c r="C101" s="40" t="n"/>
+      <c r="D101" s="40" t="n"/>
+      <c r="E101" s="40" t="n"/>
+      <c r="F101" s="40" t="n"/>
+      <c r="G101" s="40" t="n"/>
+      <c r="H101" s="17" t="n"/>
+    </row>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="40" t="n"/>
+      <c r="B102" s="40" t="n"/>
+      <c r="C102" s="40" t="n"/>
+      <c r="D102" s="40" t="n"/>
+      <c r="E102" s="40" t="n"/>
+      <c r="F102" s="40" t="n"/>
+      <c r="G102" s="40" t="n"/>
+      <c r="H102" s="17" t="n"/>
+    </row>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="40" t="n"/>
+      <c r="B103" s="40" t="n"/>
+      <c r="C103" s="40" t="n"/>
+      <c r="D103" s="40" t="n"/>
+      <c r="E103" s="40" t="n"/>
+      <c r="F103" s="40" t="n"/>
+      <c r="G103" s="40" t="n"/>
+      <c r="H103" s="17" t="n"/>
+    </row>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="40" t="n"/>
+      <c r="B104" s="40" t="n"/>
+      <c r="C104" s="40" t="n"/>
+      <c r="D104" s="40" t="n"/>
+      <c r="E104" s="40" t="n"/>
+      <c r="F104" s="40" t="n"/>
+      <c r="G104" s="40" t="n"/>
+      <c r="H104" s="17" t="n"/>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="A105" s="40" t="n"/>
+      <c r="B105" s="40" t="n"/>
+      <c r="C105" s="40" t="n"/>
+      <c r="D105" s="40" t="n"/>
+      <c r="E105" s="40" t="n"/>
+      <c r="F105" s="40" t="n"/>
+      <c r="G105" s="40" t="n"/>
+      <c r="H105" s="17" t="n"/>
+    </row>
+    <row r="106" ht="22" customHeight="1">
+      <c r="A106" s="40" t="n"/>
+      <c r="B106" s="40" t="n"/>
+      <c r="C106" s="40" t="n"/>
+      <c r="D106" s="40" t="n"/>
+      <c r="E106" s="40" t="n"/>
+      <c r="F106" s="40" t="n"/>
+      <c r="G106" s="40" t="n"/>
+      <c r="H106" s="17" t="n"/>
+    </row>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="40" t="n"/>
+      <c r="B107" s="40" t="n"/>
+      <c r="C107" s="40" t="n"/>
+      <c r="D107" s="40" t="n"/>
+      <c r="E107" s="40" t="n"/>
+      <c r="F107" s="40" t="n"/>
+      <c r="G107" s="40" t="n"/>
+      <c r="H107" s="17" t="n"/>
+    </row>
+    <row r="108" ht="22" customHeight="1">
+      <c r="A108" s="40" t="n"/>
+      <c r="B108" s="40" t="n"/>
+      <c r="C108" s="40" t="n"/>
+      <c r="D108" s="40" t="n"/>
+      <c r="E108" s="40" t="n"/>
+      <c r="F108" s="40" t="n"/>
+      <c r="G108" s="40" t="n"/>
+      <c r="H108" s="17" t="n"/>
+    </row>
+    <row r="109" ht="22" customHeight="1">
+      <c r="A109" s="40" t="n"/>
+      <c r="B109" s="40" t="n"/>
+      <c r="C109" s="40" t="n"/>
+      <c r="D109" s="40" t="n"/>
+      <c r="E109" s="40" t="n"/>
+      <c r="F109" s="40" t="n"/>
+      <c r="G109" s="40" t="n"/>
+      <c r="H109" s="17" t="n"/>
+    </row>
+    <row r="110" ht="22" customHeight="1">
+      <c r="A110" s="40" t="n"/>
+      <c r="B110" s="40" t="n"/>
+      <c r="C110" s="40" t="n"/>
+      <c r="D110" s="40" t="n"/>
+      <c r="E110" s="40" t="n"/>
+      <c r="F110" s="40" t="n"/>
+      <c r="G110" s="40" t="n"/>
+      <c r="H110" s="17" t="n"/>
+    </row>
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="40" t="n"/>
+      <c r="B111" s="40" t="n"/>
+      <c r="C111" s="40" t="n"/>
+      <c r="D111" s="40" t="n"/>
+      <c r="E111" s="40" t="n"/>
+      <c r="F111" s="40" t="n"/>
+      <c r="G111" s="40" t="n"/>
+      <c r="H111" s="17" t="n"/>
+    </row>
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="40" t="n"/>
+      <c r="B112" s="40" t="n"/>
+      <c r="C112" s="40" t="n"/>
+      <c r="D112" s="40" t="n"/>
+      <c r="E112" s="40" t="n"/>
+      <c r="F112" s="40" t="n"/>
+      <c r="G112" s="40" t="n"/>
+      <c r="H112" s="17" t="n"/>
+    </row>
+    <row r="113" ht="22" customHeight="1">
+      <c r="A113" s="40" t="n"/>
+      <c r="B113" s="40" t="n"/>
+      <c r="C113" s="40" t="n"/>
+      <c r="D113" s="40" t="n"/>
+      <c r="E113" s="40" t="n"/>
+      <c r="F113" s="40" t="n"/>
+      <c r="G113" s="40" t="n"/>
+      <c r="H113" s="17" t="n"/>
+    </row>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="40" t="n"/>
+      <c r="B114" s="40" t="n"/>
+      <c r="C114" s="40" t="n"/>
+      <c r="D114" s="40" t="n"/>
+      <c r="E114" s="40" t="n"/>
+      <c r="F114" s="40" t="n"/>
+      <c r="G114" s="40" t="n"/>
+      <c r="H114" s="17" t="n"/>
+    </row>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="40" t="n"/>
+      <c r="B115" s="40" t="n"/>
+      <c r="C115" s="40" t="n"/>
+      <c r="D115" s="40" t="n"/>
+      <c r="E115" s="40" t="n"/>
+      <c r="F115" s="40" t="n"/>
+      <c r="G115" s="40" t="n"/>
+      <c r="H115" s="17" t="n"/>
+    </row>
+    <row r="116" ht="22" customHeight="1">
+      <c r="A116" s="40" t="n"/>
+      <c r="B116" s="40" t="n"/>
+      <c r="C116" s="40" t="n"/>
+      <c r="D116" s="40" t="n"/>
+      <c r="E116" s="40" t="n"/>
+      <c r="F116" s="40" t="n"/>
+      <c r="G116" s="40" t="n"/>
+      <c r="H116" s="17" t="n"/>
+    </row>
+    <row r="117" ht="22" customHeight="1">
+      <c r="A117" s="40" t="n"/>
+      <c r="B117" s="40" t="n"/>
+      <c r="C117" s="40" t="n"/>
+      <c r="D117" s="40" t="n"/>
+      <c r="E117" s="40" t="n"/>
+      <c r="F117" s="40" t="n"/>
+      <c r="G117" s="40" t="n"/>
+      <c r="H117" s="17" t="n"/>
+    </row>
+    <row r="118" ht="22" customHeight="1">
+      <c r="A118" s="40" t="n"/>
+      <c r="B118" s="40" t="n"/>
+      <c r="C118" s="40" t="n"/>
+      <c r="D118" s="40" t="n"/>
+      <c r="E118" s="40" t="n"/>
+      <c r="F118" s="40" t="n"/>
+      <c r="G118" s="40" t="n"/>
+      <c r="H118" s="17" t="n"/>
+    </row>
+    <row r="119" ht="22" customHeight="1">
+      <c r="A119" s="40" t="n"/>
+      <c r="B119" s="40" t="n"/>
+      <c r="C119" s="40" t="n"/>
+      <c r="D119" s="40" t="n"/>
+      <c r="E119" s="40" t="n"/>
+      <c r="F119" s="40" t="n"/>
+      <c r="G119" s="40" t="n"/>
+      <c r="H119" s="17" t="n"/>
+    </row>
+    <row r="120" ht="22" customHeight="1">
+      <c r="A120" s="40" t="n"/>
+      <c r="B120" s="40" t="n"/>
+      <c r="C120" s="40" t="n"/>
+      <c r="D120" s="40" t="n"/>
+      <c r="E120" s="40" t="n"/>
+      <c r="F120" s="40" t="n"/>
+      <c r="G120" s="40" t="n"/>
+      <c r="H120" s="17" t="n"/>
+    </row>
+    <row r="121" ht="22" customHeight="1">
+      <c r="A121" s="40" t="n"/>
+      <c r="B121" s="40" t="n"/>
+      <c r="C121" s="40" t="n"/>
+      <c r="D121" s="40" t="n"/>
+      <c r="E121" s="40" t="n"/>
+      <c r="F121" s="40" t="n"/>
+      <c r="G121" s="40" t="n"/>
+      <c r="H121" s="17" t="n"/>
+    </row>
+    <row r="122" ht="22" customHeight="1">
+      <c r="A122" s="40" t="n"/>
+      <c r="B122" s="40" t="n"/>
+      <c r="C122" s="40" t="n"/>
+      <c r="D122" s="40" t="n"/>
+      <c r="E122" s="40" t="n"/>
+      <c r="F122" s="40" t="n"/>
+      <c r="G122" s="40" t="n"/>
+      <c r="H122" s="17" t="n"/>
+    </row>
+    <row r="123" ht="22" customHeight="1">
+      <c r="A123" s="40" t="n"/>
+      <c r="B123" s="40" t="n"/>
+      <c r="C123" s="40" t="n"/>
+      <c r="D123" s="40" t="n"/>
+      <c r="E123" s="40" t="n"/>
+      <c r="F123" s="40" t="n"/>
+      <c r="G123" s="40" t="n"/>
+      <c r="H123" s="17" t="n"/>
+    </row>
+    <row r="124" ht="22" customHeight="1">
+      <c r="A124" s="40" t="n"/>
+      <c r="B124" s="40" t="n"/>
+      <c r="C124" s="40" t="n"/>
+      <c r="D124" s="40" t="n"/>
+      <c r="E124" s="40" t="n"/>
+      <c r="F124" s="40" t="n"/>
+      <c r="G124" s="40" t="n"/>
+      <c r="H124" s="17" t="n"/>
+    </row>
+    <row r="125" ht="22" customHeight="1">
+      <c r="A125" s="40" t="n"/>
+      <c r="B125" s="40" t="n"/>
+      <c r="C125" s="40" t="n"/>
+      <c r="D125" s="40" t="n"/>
+      <c r="E125" s="40" t="n"/>
+      <c r="F125" s="40" t="n"/>
+      <c r="G125" s="40" t="n"/>
+      <c r="H125" s="17" t="n"/>
+    </row>
+    <row r="126" ht="22" customHeight="1">
+      <c r="A126" s="40" t="n"/>
+      <c r="B126" s="40" t="n"/>
+      <c r="C126" s="40" t="n"/>
+      <c r="D126" s="40" t="n"/>
+      <c r="E126" s="40" t="n"/>
+      <c r="F126" s="40" t="n"/>
+      <c r="G126" s="40" t="n"/>
+      <c r="H126" s="17" t="n"/>
+    </row>
+    <row r="127" ht="22" customHeight="1">
+      <c r="A127" s="40" t="n"/>
+      <c r="B127" s="40" t="n"/>
+      <c r="C127" s="40" t="n"/>
+      <c r="D127" s="40" t="n"/>
+      <c r="E127" s="40" t="n"/>
+      <c r="F127" s="40" t="n"/>
+      <c r="G127" s="40" t="n"/>
+      <c r="H127" s="17" t="n"/>
+    </row>
+    <row r="128" ht="22" customHeight="1">
+      <c r="A128" s="40" t="n"/>
+      <c r="B128" s="40" t="n"/>
+      <c r="C128" s="40" t="n"/>
+      <c r="D128" s="40" t="n"/>
+      <c r="E128" s="40" t="n"/>
+      <c r="F128" s="40" t="n"/>
+      <c r="G128" s="40" t="n"/>
+      <c r="H128" s="17" t="n"/>
+    </row>
+    <row r="129" ht="22" customHeight="1">
+      <c r="A129" s="40" t="n"/>
+      <c r="B129" s="40" t="n"/>
+      <c r="C129" s="40" t="n"/>
+      <c r="D129" s="40" t="n"/>
+      <c r="E129" s="40" t="n"/>
+      <c r="F129" s="40" t="n"/>
+      <c r="G129" s="40" t="n"/>
+      <c r="H129" s="17" t="n"/>
+    </row>
+    <row r="130" ht="22" customHeight="1">
+      <c r="A130" s="40" t="n"/>
+      <c r="B130" s="40" t="n"/>
+      <c r="C130" s="40" t="n"/>
+      <c r="D130" s="40" t="n"/>
+      <c r="E130" s="40" t="n"/>
+      <c r="F130" s="40" t="n"/>
+      <c r="G130" s="40" t="n"/>
+      <c r="H130" s="17" t="n"/>
+    </row>
+    <row r="131" ht="22" customHeight="1">
+      <c r="A131" s="40" t="n"/>
+      <c r="B131" s="40" t="n"/>
+      <c r="C131" s="40" t="n"/>
+      <c r="D131" s="40" t="n"/>
+      <c r="E131" s="40" t="n"/>
+      <c r="F131" s="40" t="n"/>
+      <c r="G131" s="40" t="n"/>
+      <c r="H131" s="17" t="n"/>
+    </row>
+    <row r="132" ht="22" customHeight="1">
+      <c r="A132" s="40" t="n"/>
+      <c r="B132" s="40" t="n"/>
+      <c r="C132" s="40" t="n"/>
+      <c r="D132" s="40" t="n"/>
+      <c r="E132" s="40" t="n"/>
+      <c r="F132" s="40" t="n"/>
+      <c r="G132" s="40" t="n"/>
+      <c r="H132" s="17" t="n"/>
+    </row>
+    <row r="133" ht="22" customHeight="1">
+      <c r="A133" s="40" t="n"/>
+      <c r="B133" s="40" t="n"/>
+      <c r="C133" s="40" t="n"/>
+      <c r="D133" s="40" t="n"/>
+      <c r="E133" s="40" t="n"/>
+      <c r="F133" s="40" t="n"/>
+      <c r="G133" s="40" t="n"/>
+      <c r="H133" s="17" t="n"/>
+    </row>
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="40" t="n"/>
+      <c r="B134" s="40" t="n"/>
+      <c r="C134" s="40" t="n"/>
+      <c r="D134" s="40" t="n"/>
+      <c r="E134" s="40" t="n"/>
+      <c r="F134" s="40" t="n"/>
+      <c r="G134" s="40" t="n"/>
+      <c r="H134" s="17" t="n"/>
+    </row>
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="40" t="n"/>
+      <c r="B135" s="40" t="n"/>
+      <c r="C135" s="40" t="n"/>
+      <c r="D135" s="40" t="n"/>
+      <c r="E135" s="40" t="n"/>
+      <c r="F135" s="40" t="n"/>
+      <c r="G135" s="40" t="n"/>
+      <c r="H135" s="17" t="n"/>
+    </row>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="40" t="n"/>
+      <c r="B136" s="40" t="n"/>
+      <c r="C136" s="40" t="n"/>
+      <c r="D136" s="40" t="n"/>
+      <c r="E136" s="40" t="n"/>
+      <c r="F136" s="40" t="n"/>
+      <c r="G136" s="40" t="n"/>
+      <c r="H136" s="17" t="n"/>
+    </row>
+    <row r="137" ht="22" customHeight="1">
+      <c r="A137" s="40" t="n"/>
+      <c r="B137" s="40" t="n"/>
+      <c r="C137" s="40" t="n"/>
+      <c r="D137" s="40" t="n"/>
+      <c r="E137" s="40" t="n"/>
+      <c r="F137" s="40" t="n"/>
+      <c r="G137" s="40" t="n"/>
+      <c r="H137" s="17" t="n"/>
+    </row>
+    <row r="138" ht="22" customHeight="1">
+      <c r="A138" s="40" t="n"/>
+      <c r="B138" s="40" t="n"/>
+      <c r="C138" s="40" t="n"/>
+      <c r="D138" s="40" t="n"/>
+      <c r="E138" s="40" t="n"/>
+      <c r="F138" s="40" t="n"/>
+      <c r="G138" s="40" t="n"/>
+      <c r="H138" s="17" t="n"/>
+    </row>
+    <row r="139" ht="22" customHeight="1">
+      <c r="A139" s="40" t="n"/>
+      <c r="B139" s="40" t="n"/>
+      <c r="C139" s="40" t="n"/>
+      <c r="D139" s="40" t="n"/>
+      <c r="E139" s="40" t="n"/>
+      <c r="F139" s="40" t="n"/>
+      <c r="G139" s="40" t="n"/>
+      <c r="H139" s="17" t="n"/>
+    </row>
+    <row r="140" ht="22" customHeight="1">
+      <c r="A140" s="40" t="n"/>
+      <c r="B140" s="40" t="n"/>
+      <c r="C140" s="40" t="n"/>
+      <c r="D140" s="40" t="n"/>
+      <c r="E140" s="40" t="n"/>
+      <c r="F140" s="40" t="n"/>
+      <c r="G140" s="40" t="n"/>
+      <c r="H140" s="17" t="n"/>
+    </row>
+    <row r="141" ht="22" customHeight="1">
+      <c r="A141" s="40" t="n"/>
+      <c r="B141" s="40" t="n"/>
+      <c r="C141" s="40" t="n"/>
+      <c r="D141" s="40" t="n"/>
+      <c r="E141" s="40" t="n"/>
+      <c r="F141" s="40" t="n"/>
+      <c r="G141" s="40" t="n"/>
+      <c r="H141" s="17" t="n"/>
+    </row>
+    <row r="142" ht="22" customHeight="1">
+      <c r="A142" s="40" t="n"/>
+      <c r="B142" s="40" t="n"/>
+      <c r="C142" s="40" t="n"/>
+      <c r="D142" s="40" t="n"/>
+      <c r="E142" s="40" t="n"/>
+      <c r="F142" s="40" t="n"/>
+      <c r="G142" s="40" t="n"/>
+      <c r="H142" s="17" t="n"/>
+    </row>
+    <row r="143" ht="22" customHeight="1">
+      <c r="A143" s="40" t="n"/>
+      <c r="B143" s="40" t="n"/>
+      <c r="C143" s="40" t="n"/>
+      <c r="D143" s="40" t="n"/>
+      <c r="E143" s="40" t="n"/>
+      <c r="F143" s="40" t="n"/>
+      <c r="G143" s="40" t="n"/>
+      <c r="H143" s="17" t="n"/>
+    </row>
+    <row r="144" ht="22" customHeight="1">
+      <c r="A144" s="40" t="n"/>
+      <c r="B144" s="40" t="n"/>
+      <c r="C144" s="40" t="n"/>
+      <c r="D144" s="40" t="n"/>
+      <c r="E144" s="40" t="n"/>
+      <c r="F144" s="40" t="n"/>
+      <c r="G144" s="40" t="n"/>
+      <c r="H144" s="17" t="n"/>
+    </row>
+    <row r="145" ht="22" customHeight="1">
+      <c r="A145" s="40" t="n"/>
+      <c r="B145" s="40" t="n"/>
+      <c r="C145" s="40" t="n"/>
+      <c r="D145" s="40" t="n"/>
+      <c r="E145" s="40" t="n"/>
+      <c r="F145" s="40" t="n"/>
+      <c r="G145" s="40" t="n"/>
+      <c r="H145" s="17" t="n"/>
+    </row>
+    <row r="146" ht="22" customHeight="1">
+      <c r="A146" s="40" t="n"/>
+      <c r="B146" s="40" t="n"/>
+      <c r="C146" s="40" t="n"/>
+      <c r="D146" s="40" t="n"/>
+      <c r="E146" s="40" t="n"/>
+      <c r="F146" s="40" t="n"/>
+      <c r="G146" s="40" t="n"/>
+      <c r="H146" s="17" t="n"/>
+    </row>
+    <row r="147" ht="22" customHeight="1">
+      <c r="A147" s="40" t="n"/>
+      <c r="B147" s="40" t="n"/>
+      <c r="C147" s="40" t="n"/>
+      <c r="D147" s="40" t="n"/>
+      <c r="E147" s="40" t="n"/>
+      <c r="F147" s="40" t="n"/>
+      <c r="G147" s="40" t="n"/>
+      <c r="H147" s="17" t="n"/>
+    </row>
+    <row r="148" ht="22" customHeight="1">
+      <c r="A148" s="40" t="n"/>
+      <c r="B148" s="40" t="n"/>
+      <c r="C148" s="40" t="n"/>
+      <c r="D148" s="40" t="n"/>
+      <c r="E148" s="40" t="n"/>
+      <c r="F148" s="40" t="n"/>
+      <c r="G148" s="40" t="n"/>
+      <c r="H148" s="17" t="n"/>
+    </row>
+    <row r="149" ht="22" customHeight="1">
+      <c r="A149" s="40" t="n"/>
+      <c r="B149" s="40" t="n"/>
+      <c r="C149" s="40" t="n"/>
+      <c r="D149" s="40" t="n"/>
+      <c r="E149" s="40" t="n"/>
+      <c r="F149" s="40" t="n"/>
+      <c r="G149" s="40" t="n"/>
+      <c r="H149" s="17" t="n"/>
+    </row>
+    <row r="150" ht="22" customHeight="1">
+      <c r="A150" s="40" t="n"/>
+      <c r="B150" s="40" t="n"/>
+      <c r="C150" s="40" t="n"/>
+      <c r="D150" s="40" t="n"/>
+      <c r="E150" s="40" t="n"/>
+      <c r="F150" s="40" t="n"/>
+      <c r="G150" s="40" t="n"/>
+      <c r="H150" s="17" t="n"/>
+    </row>
+    <row r="151" ht="22" customHeight="1">
+      <c r="A151" s="40" t="n"/>
+      <c r="B151" s="40" t="n"/>
+      <c r="C151" s="40" t="n"/>
+      <c r="D151" s="40" t="n"/>
+      <c r="E151" s="40" t="n"/>
+      <c r="F151" s="40" t="n"/>
+      <c r="G151" s="40" t="n"/>
+      <c r="H151" s="17" t="n"/>
+    </row>
+    <row r="152" ht="22" customHeight="1">
+      <c r="A152" s="40" t="n"/>
+      <c r="B152" s="40" t="n"/>
+      <c r="C152" s="40" t="n"/>
+      <c r="D152" s="40" t="n"/>
+      <c r="E152" s="40" t="n"/>
+      <c r="F152" s="40" t="n"/>
+      <c r="G152" s="40" t="n"/>
+      <c r="H152" s="17" t="n"/>
+    </row>
+    <row r="153" ht="22" customHeight="1">
+      <c r="A153" s="40" t="n"/>
+      <c r="B153" s="40" t="n"/>
+      <c r="C153" s="40" t="n"/>
+      <c r="D153" s="40" t="n"/>
+      <c r="E153" s="40" t="n"/>
+      <c r="F153" s="40" t="n"/>
+      <c r="G153" s="40" t="n"/>
+      <c r="H153" s="17" t="n"/>
+    </row>
+    <row r="154" ht="22" customHeight="1">
+      <c r="A154" s="40" t="n"/>
+      <c r="B154" s="40" t="n"/>
+      <c r="C154" s="40" t="n"/>
+      <c r="D154" s="40" t="n"/>
+      <c r="E154" s="40" t="n"/>
+      <c r="F154" s="40" t="n"/>
+      <c r="G154" s="40" t="n"/>
+      <c r="H154" s="17" t="n"/>
+    </row>
+    <row r="155" ht="22" customHeight="1">
+      <c r="A155" s="40" t="n"/>
+      <c r="B155" s="40" t="n"/>
+      <c r="C155" s="40" t="n"/>
+      <c r="D155" s="40" t="n"/>
+      <c r="E155" s="40" t="n"/>
+      <c r="F155" s="40" t="n"/>
+      <c r="G155" s="40" t="n"/>
+      <c r="H155" s="17" t="n"/>
+    </row>
+    <row r="156" ht="22" customHeight="1">
+      <c r="A156" s="40" t="n"/>
+      <c r="B156" s="40" t="n"/>
+      <c r="C156" s="40" t="n"/>
+      <c r="D156" s="40" t="n"/>
+      <c r="E156" s="40" t="n"/>
+      <c r="F156" s="40" t="n"/>
+      <c r="G156" s="40" t="n"/>
+      <c r="H156" s="17" t="n"/>
+    </row>
+    <row r="157" ht="22" customHeight="1">
+      <c r="A157" s="40" t="n"/>
+      <c r="B157" s="40" t="n"/>
+      <c r="C157" s="40" t="n"/>
+      <c r="D157" s="40" t="n"/>
+      <c r="E157" s="40" t="n"/>
+      <c r="F157" s="40" t="n"/>
+      <c r="G157" s="40" t="n"/>
+      <c r="H157" s="17" t="n"/>
+    </row>
+    <row r="158" ht="22" customHeight="1">
+      <c r="A158" s="40" t="n"/>
+      <c r="B158" s="40" t="n"/>
+      <c r="C158" s="40" t="n"/>
+      <c r="D158" s="40" t="n"/>
+      <c r="E158" s="40" t="n"/>
+      <c r="F158" s="40" t="n"/>
+      <c r="G158" s="40" t="n"/>
+      <c r="H158" s="17" t="n"/>
+    </row>
+    <row r="159" ht="22" customHeight="1">
+      <c r="A159" s="40" t="n"/>
+      <c r="B159" s="40" t="n"/>
+      <c r="C159" s="40" t="n"/>
+      <c r="D159" s="40" t="n"/>
+      <c r="E159" s="40" t="n"/>
+      <c r="F159" s="40" t="n"/>
+      <c r="G159" s="40" t="n"/>
+      <c r="H159" s="17" t="n"/>
+    </row>
+    <row r="160" ht="22" customHeight="1">
+      <c r="A160" s="40" t="n"/>
+      <c r="B160" s="40" t="n"/>
+      <c r="C160" s="40" t="n"/>
+      <c r="D160" s="40" t="n"/>
+      <c r="E160" s="40" t="n"/>
+      <c r="F160" s="40" t="n"/>
+      <c r="G160" s="40" t="n"/>
+      <c r="H160" s="17" t="n"/>
+    </row>
+    <row r="161" ht="22" customHeight="1">
+      <c r="A161" s="40" t="n"/>
+      <c r="B161" s="40" t="n"/>
+      <c r="C161" s="40" t="n"/>
+      <c r="D161" s="40" t="n"/>
+      <c r="E161" s="40" t="n"/>
+      <c r="F161" s="40" t="n"/>
+      <c r="G161" s="40" t="n"/>
+      <c r="H161" s="17" t="n"/>
+    </row>
+    <row r="162" ht="22" customHeight="1">
+      <c r="A162" s="40" t="n"/>
+      <c r="B162" s="40" t="n"/>
+      <c r="C162" s="40" t="n"/>
+      <c r="D162" s="40" t="n"/>
+      <c r="E162" s="40" t="n"/>
+      <c r="F162" s="40" t="n"/>
+      <c r="G162" s="40" t="n"/>
+      <c r="H162" s="17" t="n"/>
+    </row>
+    <row r="163" ht="22" customHeight="1">
+      <c r="A163" s="40" t="n"/>
+      <c r="B163" s="40" t="n"/>
+      <c r="C163" s="40" t="n"/>
+      <c r="D163" s="40" t="n"/>
+      <c r="E163" s="40" t="n"/>
+      <c r="F163" s="40" t="n"/>
+      <c r="G163" s="40" t="n"/>
+      <c r="H163" s="17" t="n"/>
+    </row>
+    <row r="164" ht="22" customHeight="1">
+      <c r="A164" s="40" t="n"/>
+      <c r="B164" s="40" t="n"/>
+      <c r="C164" s="40" t="n"/>
+      <c r="D164" s="40" t="n"/>
+      <c r="E164" s="40" t="n"/>
+      <c r="F164" s="40" t="n"/>
+      <c r="G164" s="40" t="n"/>
+      <c r="H164" s="17" t="n"/>
+    </row>
+    <row r="165" ht="22" customHeight="1">
+      <c r="A165" s="40" t="n"/>
+      <c r="B165" s="40" t="n"/>
+      <c r="C165" s="40" t="n"/>
+      <c r="D165" s="40" t="n"/>
+      <c r="E165" s="40" t="n"/>
+      <c r="F165" s="40" t="n"/>
+      <c r="G165" s="40" t="n"/>
+      <c r="H165" s="17" t="n"/>
+    </row>
+    <row r="166" ht="22" customHeight="1">
+      <c r="A166" s="40" t="n"/>
+      <c r="B166" s="40" t="n"/>
+      <c r="C166" s="40" t="n"/>
+      <c r="D166" s="40" t="n"/>
+      <c r="E166" s="40" t="n"/>
+      <c r="F166" s="40" t="n"/>
+      <c r="G166" s="40" t="n"/>
+      <c r="H166" s="17" t="n"/>
+    </row>
+    <row r="167" ht="22" customHeight="1">
+      <c r="A167" s="40" t="n"/>
+      <c r="B167" s="40" t="n"/>
+      <c r="C167" s="40" t="n"/>
+      <c r="D167" s="40" t="n"/>
+      <c r="E167" s="40" t="n"/>
+      <c r="F167" s="40" t="n"/>
+      <c r="G167" s="40" t="n"/>
+      <c r="H167" s="17" t="n"/>
+    </row>
+    <row r="168" ht="22" customHeight="1">
+      <c r="A168" s="40" t="n"/>
+      <c r="B168" s="40" t="n"/>
+      <c r="C168" s="40" t="n"/>
+      <c r="D168" s="40" t="n"/>
+      <c r="E168" s="40" t="n"/>
+      <c r="F168" s="40" t="n"/>
+      <c r="G168" s="40" t="n"/>
+      <c r="H168" s="17" t="n"/>
+    </row>
+    <row r="169" ht="22" customHeight="1">
+      <c r="A169" s="40" t="n"/>
+      <c r="B169" s="40" t="n"/>
+      <c r="C169" s="40" t="n"/>
+      <c r="D169" s="40" t="n"/>
+      <c r="E169" s="40" t="n"/>
+      <c r="F169" s="40" t="n"/>
+      <c r="G169" s="40" t="n"/>
+      <c r="H169" s="17" t="n"/>
+    </row>
+    <row r="170" ht="22" customHeight="1">
+      <c r="A170" s="40" t="n"/>
+      <c r="B170" s="40" t="n"/>
+      <c r="C170" s="40" t="n"/>
+      <c r="D170" s="40" t="n"/>
+      <c r="E170" s="40" t="n"/>
+      <c r="F170" s="40" t="n"/>
+      <c r="G170" s="40" t="n"/>
+      <c r="H170" s="17" t="n"/>
+    </row>
+    <row r="171" ht="22" customHeight="1">
+      <c r="A171" s="40" t="n"/>
+      <c r="B171" s="40" t="n"/>
+      <c r="C171" s="40" t="n"/>
+      <c r="D171" s="40" t="n"/>
+      <c r="E171" s="40" t="n"/>
+      <c r="F171" s="40" t="n"/>
+      <c r="G171" s="40" t="n"/>
+      <c r="H171" s="17" t="n"/>
+    </row>
+    <row r="172" ht="22" customHeight="1">
+      <c r="A172" s="40" t="n"/>
+      <c r="B172" s="40" t="n"/>
+      <c r="C172" s="40" t="n"/>
+      <c r="D172" s="40" t="n"/>
+      <c r="E172" s="40" t="n"/>
+      <c r="F172" s="40" t="n"/>
+      <c r="G172" s="40" t="n"/>
+      <c r="H172" s="17" t="n"/>
+    </row>
+    <row r="173" ht="22" customHeight="1">
+      <c r="A173" s="40" t="n"/>
+      <c r="B173" s="40" t="n"/>
+      <c r="C173" s="40" t="n"/>
+      <c r="D173" s="40" t="n"/>
+      <c r="E173" s="40" t="n"/>
+      <c r="F173" s="40" t="n"/>
+      <c r="G173" s="40" t="n"/>
+      <c r="H173" s="17" t="n"/>
+    </row>
+    <row r="174" ht="22" customHeight="1">
+      <c r="A174" s="40" t="n"/>
+      <c r="B174" s="40" t="n"/>
+      <c r="C174" s="40" t="n"/>
+      <c r="D174" s="40" t="n"/>
+      <c r="E174" s="40" t="n"/>
+      <c r="F174" s="40" t="n"/>
+      <c r="G174" s="40" t="n"/>
+      <c r="H174" s="17" t="n"/>
+    </row>
+    <row r="175" ht="22" customHeight="1">
+      <c r="A175" s="40" t="n"/>
+      <c r="B175" s="40" t="n"/>
+      <c r="C175" s="40" t="n"/>
+      <c r="D175" s="40" t="n"/>
+      <c r="E175" s="40" t="n"/>
+      <c r="F175" s="40" t="n"/>
+      <c r="G175" s="40" t="n"/>
+      <c r="H175" s="17" t="n"/>
+    </row>
+    <row r="176" ht="22" customHeight="1">
+      <c r="A176" s="40" t="n"/>
+      <c r="B176" s="40" t="n"/>
+      <c r="C176" s="40" t="n"/>
+      <c r="D176" s="40" t="n"/>
+      <c r="E176" s="40" t="n"/>
+      <c r="F176" s="40" t="n"/>
+      <c r="G176" s="40" t="n"/>
+      <c r="H176" s="17" t="n"/>
+    </row>
+    <row r="177" ht="22" customHeight="1">
+      <c r="A177" s="40" t="n"/>
+      <c r="B177" s="40" t="n"/>
+      <c r="C177" s="40" t="n"/>
+      <c r="D177" s="40" t="n"/>
+      <c r="E177" s="40" t="n"/>
+      <c r="F177" s="40" t="n"/>
+      <c r="G177" s="40" t="n"/>
+      <c r="H177" s="17" t="n"/>
+    </row>
+    <row r="178" ht="22" customHeight="1">
+      <c r="A178" s="40" t="n"/>
+      <c r="B178" s="40" t="n"/>
+      <c r="C178" s="40" t="n"/>
+      <c r="D178" s="40" t="n"/>
+      <c r="E178" s="40" t="n"/>
+      <c r="F178" s="40" t="n"/>
+      <c r="G178" s="40" t="n"/>
+      <c r="H178" s="17" t="n"/>
+    </row>
+    <row r="179" ht="22" customHeight="1">
+      <c r="A179" s="40" t="n"/>
+      <c r="B179" s="40" t="n"/>
+      <c r="C179" s="40" t="n"/>
+      <c r="D179" s="40" t="n"/>
+      <c r="E179" s="40" t="n"/>
+      <c r="F179" s="40" t="n"/>
+      <c r="G179" s="40" t="n"/>
+      <c r="H179" s="17" t="n"/>
+    </row>
+    <row r="180" ht="22" customHeight="1">
+      <c r="A180" s="40" t="n"/>
+      <c r="B180" s="40" t="n"/>
+      <c r="C180" s="40" t="n"/>
+      <c r="D180" s="40" t="n"/>
+      <c r="E180" s="40" t="n"/>
+      <c r="F180" s="40" t="n"/>
+      <c r="G180" s="40" t="n"/>
+      <c r="H180" s="17" t="n"/>
+    </row>
+    <row r="181" ht="22" customHeight="1">
+      <c r="A181" s="40" t="n"/>
+      <c r="B181" s="40" t="n"/>
+      <c r="C181" s="40" t="n"/>
+      <c r="D181" s="40" t="n"/>
+      <c r="E181" s="40" t="n"/>
+      <c r="F181" s="40" t="n"/>
+      <c r="G181" s="40" t="n"/>
+      <c r="H181" s="17" t="n"/>
+    </row>
+    <row r="182" ht="22" customHeight="1">
+      <c r="A182" s="40" t="n"/>
+      <c r="B182" s="40" t="n"/>
+      <c r="C182" s="40" t="n"/>
+      <c r="D182" s="40" t="n"/>
+      <c r="E182" s="40" t="n"/>
+      <c r="F182" s="40" t="n"/>
+      <c r="G182" s="40" t="n"/>
+      <c r="H182" s="17" t="n"/>
+    </row>
+    <row r="183" ht="22" customHeight="1">
+      <c r="A183" s="40" t="n"/>
+      <c r="B183" s="40" t="n"/>
+      <c r="C183" s="40" t="n"/>
+      <c r="D183" s="40" t="n"/>
+      <c r="E183" s="40" t="n"/>
+      <c r="F183" s="40" t="n"/>
+      <c r="G183" s="40" t="n"/>
+      <c r="H183" s="17" t="n"/>
+    </row>
+    <row r="184" ht="22" customHeight="1">
+      <c r="A184" s="40" t="n"/>
+      <c r="B184" s="40" t="n"/>
+      <c r="C184" s="40" t="n"/>
+      <c r="D184" s="40" t="n"/>
+      <c r="E184" s="40" t="n"/>
+      <c r="F184" s="40" t="n"/>
+      <c r="G184" s="40" t="n"/>
+      <c r="H184" s="17" t="n"/>
+    </row>
+    <row r="185" ht="22" customHeight="1">
+      <c r="A185" s="40" t="n"/>
+      <c r="B185" s="40" t="n"/>
+      <c r="C185" s="40" t="n"/>
+      <c r="D185" s="40" t="n"/>
+      <c r="E185" s="40" t="n"/>
+      <c r="F185" s="40" t="n"/>
+      <c r="G185" s="40" t="n"/>
+      <c r="H185" s="17" t="n"/>
+    </row>
+    <row r="186" ht="22" customHeight="1">
+      <c r="A186" s="40" t="n"/>
+      <c r="B186" s="40" t="n"/>
+      <c r="C186" s="40" t="n"/>
+      <c r="D186" s="40" t="n"/>
+      <c r="E186" s="40" t="n"/>
+      <c r="F186" s="40" t="n"/>
+      <c r="G186" s="40" t="n"/>
+      <c r="H186" s="17" t="n"/>
+    </row>
+    <row r="187" ht="22" customHeight="1">
+      <c r="A187" s="40" t="n"/>
+      <c r="B187" s="40" t="n"/>
+      <c r="C187" s="40" t="n"/>
+      <c r="D187" s="40" t="n"/>
+      <c r="E187" s="40" t="n"/>
+      <c r="F187" s="40" t="n"/>
+      <c r="G187" s="40" t="n"/>
+      <c r="H187" s="17" t="n"/>
+    </row>
+    <row r="188" ht="22" customHeight="1">
+      <c r="A188" s="40" t="n"/>
+      <c r="B188" s="40" t="n"/>
+      <c r="C188" s="40" t="n"/>
+      <c r="D188" s="40" t="n"/>
+      <c r="E188" s="40" t="n"/>
+      <c r="F188" s="40" t="n"/>
+      <c r="G188" s="40" t="n"/>
+      <c r="H188" s="17" t="n"/>
+    </row>
+    <row r="189" ht="22" customHeight="1">
+      <c r="A189" s="40" t="n"/>
+      <c r="B189" s="40" t="n"/>
+      <c r="C189" s="40" t="n"/>
+      <c r="D189" s="40" t="n"/>
+      <c r="E189" s="40" t="n"/>
+      <c r="F189" s="40" t="n"/>
+      <c r="G189" s="40" t="n"/>
+      <c r="H189" s="17" t="n"/>
+    </row>
+    <row r="190" ht="22" customHeight="1">
+      <c r="A190" s="40" t="n"/>
+      <c r="B190" s="40" t="n"/>
+      <c r="C190" s="40" t="n"/>
+      <c r="D190" s="40" t="n"/>
+      <c r="E190" s="40" t="n"/>
+      <c r="F190" s="40" t="n"/>
+      <c r="G190" s="40" t="n"/>
+      <c r="H190" s="17" t="n"/>
+    </row>
+    <row r="191" ht="22" customHeight="1">
+      <c r="A191" s="40" t="n"/>
+      <c r="B191" s="40" t="n"/>
+      <c r="C191" s="40" t="n"/>
+      <c r="D191" s="40" t="n"/>
+      <c r="E191" s="40" t="n"/>
+      <c r="F191" s="40" t="n"/>
+      <c r="G191" s="40" t="n"/>
+      <c r="H191" s="17" t="n"/>
+    </row>
+    <row r="192" ht="22" customHeight="1">
+      <c r="A192" s="40" t="n"/>
+      <c r="B192" s="40" t="n"/>
+      <c r="C192" s="40" t="n"/>
+      <c r="D192" s="40" t="n"/>
+      <c r="E192" s="40" t="n"/>
+      <c r="F192" s="40" t="n"/>
+      <c r="G192" s="40" t="n"/>
+      <c r="H192" s="17" t="n"/>
+    </row>
+    <row r="193" ht="22" customHeight="1">
+      <c r="A193" s="40" t="n"/>
+      <c r="B193" s="40" t="n"/>
+      <c r="C193" s="40" t="n"/>
+      <c r="D193" s="40" t="n"/>
+      <c r="E193" s="40" t="n"/>
+      <c r="F193" s="40" t="n"/>
+      <c r="G193" s="40" t="n"/>
+      <c r="H193" s="17" t="n"/>
+    </row>
+    <row r="194" ht="22" customHeight="1">
+      <c r="A194" s="40" t="n"/>
+      <c r="B194" s="40" t="n"/>
+      <c r="C194" s="40" t="n"/>
+      <c r="D194" s="40" t="n"/>
+      <c r="E194" s="40" t="n"/>
+      <c r="F194" s="40" t="n"/>
+      <c r="G194" s="40" t="n"/>
+      <c r="H194" s="17" t="n"/>
+    </row>
+    <row r="195" ht="22" customHeight="1">
+      <c r="A195" s="40" t="n"/>
+      <c r="B195" s="40" t="n"/>
+      <c r="C195" s="40" t="n"/>
+      <c r="D195" s="40" t="n"/>
+      <c r="E195" s="40" t="n"/>
+      <c r="F195" s="40" t="n"/>
+      <c r="G195" s="40" t="n"/>
+      <c r="H195" s="17" t="n"/>
+    </row>
+    <row r="196" ht="22" customHeight="1">
+      <c r="A196" s="40" t="n"/>
+      <c r="B196" s="40" t="n"/>
+      <c r="C196" s="40" t="n"/>
+      <c r="D196" s="40" t="n"/>
+      <c r="E196" s="40" t="n"/>
+      <c r="F196" s="40" t="n"/>
+      <c r="G196" s="40" t="n"/>
+      <c r="H196" s="17" t="n"/>
+    </row>
+    <row r="197" ht="22" customHeight="1">
+      <c r="A197" s="40" t="n"/>
+      <c r="B197" s="40" t="n"/>
+      <c r="C197" s="40" t="n"/>
+      <c r="D197" s="40" t="n"/>
+      <c r="E197" s="40" t="n"/>
+      <c r="F197" s="40" t="n"/>
+      <c r="G197" s="40" t="n"/>
+      <c r="H197" s="17" t="n"/>
+    </row>
+    <row r="198" ht="22" customHeight="1">
+      <c r="A198" s="40" t="n"/>
+      <c r="B198" s="40" t="n"/>
+      <c r="C198" s="40" t="n"/>
+      <c r="D198" s="40" t="n"/>
+      <c r="E198" s="40" t="n"/>
+      <c r="F198" s="40" t="n"/>
+      <c r="G198" s="40" t="n"/>
+      <c r="H198" s="17" t="n"/>
+    </row>
+    <row r="199" ht="22" customHeight="1">
+      <c r="A199" s="40" t="n"/>
+      <c r="B199" s="40" t="n"/>
+      <c r="C199" s="40" t="n"/>
+      <c r="D199" s="40" t="n"/>
+      <c r="E199" s="40" t="n"/>
+      <c r="F199" s="40" t="n"/>
+      <c r="G199" s="40" t="n"/>
+      <c r="H199" s="17" t="n"/>
+    </row>
+    <row r="200" ht="22" customHeight="1">
+      <c r="A200" s="40" t="n"/>
+      <c r="B200" s="40" t="n"/>
+      <c r="C200" s="40" t="n"/>
+      <c r="D200" s="40" t="n"/>
+      <c r="E200" s="40" t="n"/>
+      <c r="F200" s="40" t="n"/>
+      <c r="G200" s="40" t="n"/>
+      <c r="H200" s="17" t="n"/>
+    </row>
+    <row r="201" ht="22" customHeight="1">
+      <c r="A201" s="40" t="n"/>
+      <c r="B201" s="40" t="n"/>
+      <c r="C201" s="40" t="n"/>
+      <c r="D201" s="40" t="n"/>
+      <c r="E201" s="40" t="n"/>
+      <c r="F201" s="40" t="n"/>
+      <c r="G201" s="40" t="n"/>
+      <c r="H201" s="17" t="n"/>
+    </row>
+    <row r="202" ht="22" customHeight="1">
+      <c r="A202" s="40" t="n"/>
+      <c r="B202" s="40" t="n"/>
+      <c r="C202" s="40" t="n"/>
+      <c r="D202" s="40" t="n"/>
+      <c r="E202" s="40" t="n"/>
+      <c r="F202" s="40" t="n"/>
+      <c r="G202" s="40" t="n"/>
+      <c r="H202" s="17" t="n"/>
+    </row>
+    <row r="203" ht="22" customHeight="1">
+      <c r="A203" s="40" t="n"/>
+      <c r="B203" s="40" t="n"/>
+      <c r="C203" s="40" t="n"/>
+      <c r="D203" s="40" t="n"/>
+      <c r="E203" s="40" t="n"/>
+      <c r="F203" s="40" t="n"/>
+      <c r="G203" s="40" t="n"/>
+      <c r="H203" s="17" t="n"/>
+    </row>
+    <row r="204" ht="22" customHeight="1">
+      <c r="A204" s="40" t="n"/>
+      <c r="B204" s="40" t="n"/>
+      <c r="C204" s="40" t="n"/>
+      <c r="D204" s="40" t="n"/>
+      <c r="E204" s="40" t="n"/>
+      <c r="F204" s="40" t="n"/>
+      <c r="G204" s="40" t="n"/>
+      <c r="H204" s="17" t="n"/>
+    </row>
+    <row r="205" ht="22" customHeight="1">
+      <c r="A205" s="40" t="n"/>
+      <c r="B205" s="40" t="n"/>
+      <c r="C205" s="40" t="n"/>
+      <c r="D205" s="40" t="n"/>
+      <c r="E205" s="40" t="n"/>
+      <c r="F205" s="40" t="n"/>
+      <c r="G205" s="40" t="n"/>
+      <c r="H205" s="17" t="n"/>
+    </row>
+    <row r="206" ht="22" customHeight="1">
+      <c r="A206" s="40" t="n"/>
+      <c r="B206" s="40" t="n"/>
+      <c r="C206" s="40" t="n"/>
+      <c r="D206" s="40" t="n"/>
+      <c r="E206" s="40" t="n"/>
+      <c r="F206" s="40" t="n"/>
+      <c r="G206" s="40" t="n"/>
+      <c r="H206" s="17" t="n"/>
+    </row>
+    <row r="207" ht="22" customHeight="1">
+      <c r="A207" s="40" t="n"/>
+      <c r="B207" s="40" t="n"/>
+      <c r="C207" s="40" t="n"/>
+      <c r="D207" s="40" t="n"/>
+      <c r="E207" s="40" t="n"/>
+      <c r="F207" s="40" t="n"/>
+      <c r="G207" s="40" t="n"/>
+      <c r="H207" s="17" t="n"/>
+    </row>
+    <row r="208" ht="22" customHeight="1">
+      <c r="A208" s="40" t="n"/>
+      <c r="B208" s="40" t="n"/>
+      <c r="C208" s="40" t="n"/>
+      <c r="D208" s="40" t="n"/>
+      <c r="E208" s="40" t="n"/>
+      <c r="F208" s="40" t="n"/>
+      <c r="G208" s="40" t="n"/>
+      <c r="H208" s="17" t="n"/>
+    </row>
+    <row r="209" ht="22" customHeight="1">
+      <c r="A209" s="40" t="n"/>
+      <c r="B209" s="40" t="n"/>
+      <c r="C209" s="40" t="n"/>
+      <c r="D209" s="40" t="n"/>
+      <c r="E209" s="40" t="n"/>
+      <c r="F209" s="40" t="n"/>
+      <c r="G209" s="40" t="n"/>
+      <c r="H209" s="17" t="n"/>
+    </row>
+    <row r="210" ht="22" customHeight="1">
+      <c r="A210" s="40" t="n"/>
+      <c r="B210" s="40" t="n"/>
+      <c r="C210" s="40" t="n"/>
+      <c r="D210" s="40" t="n"/>
+      <c r="E210" s="40" t="n"/>
+      <c r="F210" s="40" t="n"/>
+      <c r="G210" s="40" t="n"/>
+      <c r="H210" s="17" t="n"/>
+    </row>
+    <row r="211" ht="22" customHeight="1">
+      <c r="A211" s="40" t="n"/>
+      <c r="B211" s="40" t="n"/>
+      <c r="C211" s="40" t="n"/>
+      <c r="D211" s="40" t="n"/>
+      <c r="E211" s="40" t="n"/>
+      <c r="F211" s="40" t="n"/>
+      <c r="G211" s="40" t="n"/>
+      <c r="H211" s="17" t="n"/>
+    </row>
+    <row r="212" ht="22" customHeight="1">
+      <c r="A212" s="40" t="n"/>
+      <c r="B212" s="40" t="n"/>
+      <c r="C212" s="40" t="n"/>
+      <c r="D212" s="40" t="n"/>
+      <c r="E212" s="40" t="n"/>
+      <c r="F212" s="40" t="n"/>
+      <c r="G212" s="40" t="n"/>
+      <c r="H212" s="17" t="n"/>
+    </row>
+    <row r="213" ht="22" customHeight="1">
+      <c r="A213" s="40" t="n"/>
+      <c r="B213" s="40" t="n"/>
+      <c r="C213" s="40" t="n"/>
+      <c r="D213" s="40" t="n"/>
+      <c r="E213" s="40" t="n"/>
+      <c r="F213" s="40" t="n"/>
+      <c r="G213" s="40" t="n"/>
+      <c r="H213" s="17" t="n"/>
+    </row>
+    <row r="214" ht="22" customHeight="1">
+      <c r="A214" s="40" t="n"/>
+      <c r="B214" s="40" t="n"/>
+      <c r="C214" s="40" t="n"/>
+      <c r="D214" s="40" t="n"/>
+      <c r="E214" s="40" t="n"/>
+      <c r="F214" s="40" t="n"/>
+      <c r="G214" s="40" t="n"/>
+      <c r="H214" s="17" t="n"/>
+    </row>
+    <row r="215" ht="22" customHeight="1">
+      <c r="A215" s="40" t="n"/>
+      <c r="B215" s="40" t="n"/>
+      <c r="C215" s="40" t="n"/>
+      <c r="D215" s="40" t="n"/>
+      <c r="E215" s="40" t="n"/>
+      <c r="F215" s="40" t="n"/>
+      <c r="G215" s="40" t="n"/>
+      <c r="H215" s="17" t="n"/>
+    </row>
+    <row r="216" ht="22" customHeight="1">
+      <c r="A216" s="40" t="n"/>
+      <c r="B216" s="40" t="n"/>
+      <c r="C216" s="40" t="n"/>
+      <c r="D216" s="40" t="n"/>
+      <c r="E216" s="40" t="n"/>
+      <c r="F216" s="40" t="n"/>
+      <c r="G216" s="40" t="n"/>
+      <c r="H216" s="17" t="n"/>
+    </row>
+    <row r="217" ht="22" customHeight="1">
+      <c r="A217" s="40" t="n"/>
+      <c r="B217" s="40" t="n"/>
+      <c r="C217" s="40" t="n"/>
+      <c r="D217" s="40" t="n"/>
+      <c r="E217" s="40" t="n"/>
+      <c r="F217" s="40" t="n"/>
+      <c r="G217" s="40" t="n"/>
+      <c r="H217" s="17" t="n"/>
+    </row>
+    <row r="218" ht="22" customHeight="1">
+      <c r="A218" s="40" t="n"/>
+      <c r="B218" s="40" t="n"/>
+      <c r="C218" s="40" t="n"/>
+      <c r="D218" s="40" t="n"/>
+      <c r="E218" s="40" t="n"/>
+      <c r="F218" s="40" t="n"/>
+      <c r="G218" s="40" t="n"/>
+      <c r="H218" s="17" t="n"/>
+    </row>
+    <row r="219" ht="22" customHeight="1">
+      <c r="A219" s="40" t="n"/>
+      <c r="B219" s="40" t="n"/>
+      <c r="C219" s="40" t="n"/>
+      <c r="D219" s="40" t="n"/>
+      <c r="E219" s="40" t="n"/>
+      <c r="F219" s="40" t="n"/>
+      <c r="G219" s="40" t="n"/>
+      <c r="H219" s="17" t="n"/>
+    </row>
+    <row r="220" ht="22" customHeight="1">
+      <c r="A220" s="40" t="n"/>
+      <c r="B220" s="40" t="n"/>
+      <c r="C220" s="40" t="n"/>
+      <c r="D220" s="40" t="n"/>
+      <c r="E220" s="40" t="n"/>
+      <c r="F220" s="40" t="n"/>
+      <c r="G220" s="40" t="n"/>
+      <c r="H220" s="17" t="n"/>
+    </row>
+    <row r="221" ht="22" customHeight="1">
+      <c r="A221" s="40" t="n"/>
+      <c r="B221" s="40" t="n"/>
+      <c r="C221" s="40" t="n"/>
+      <c r="D221" s="40" t="n"/>
+      <c r="E221" s="40" t="n"/>
+      <c r="F221" s="40" t="n"/>
+      <c r="G221" s="40" t="n"/>
+      <c r="H221" s="17" t="n"/>
+    </row>
+    <row r="222" ht="22" customHeight="1">
+      <c r="A222" s="40" t="n"/>
+      <c r="B222" s="40" t="n"/>
+      <c r="C222" s="40" t="n"/>
+      <c r="D222" s="40" t="n"/>
+      <c r="E222" s="40" t="n"/>
+      <c r="F222" s="40" t="n"/>
+      <c r="G222" s="40" t="n"/>
+      <c r="H222" s="17" t="n"/>
+    </row>
+    <row r="223" ht="22" customHeight="1">
+      <c r="A223" s="40" t="n"/>
+      <c r="B223" s="40" t="n"/>
+      <c r="C223" s="40" t="n"/>
+      <c r="D223" s="40" t="n"/>
+      <c r="E223" s="40" t="n"/>
+      <c r="F223" s="40" t="n"/>
+      <c r="G223" s="40" t="n"/>
+      <c r="H223" s="17" t="n"/>
+    </row>
+    <row r="224" ht="22" customHeight="1">
+      <c r="A224" s="40" t="n"/>
+      <c r="B224" s="40" t="n"/>
+      <c r="C224" s="40" t="n"/>
+      <c r="D224" s="40" t="n"/>
+      <c r="E224" s="40" t="n"/>
+      <c r="F224" s="40" t="n"/>
+      <c r="G224" s="40" t="n"/>
+      <c r="H224" s="17" t="n"/>
+    </row>
+    <row r="225" ht="22" customHeight="1">
+      <c r="A225" s="40" t="n"/>
+      <c r="B225" s="40" t="n"/>
+      <c r="C225" s="40" t="n"/>
+      <c r="D225" s="40" t="n"/>
+      <c r="E225" s="40" t="n"/>
+      <c r="F225" s="40" t="n"/>
+      <c r="G225" s="40" t="n"/>
+      <c r="H225" s="17" t="n"/>
+    </row>
+    <row r="226" ht="22" customHeight="1">
+      <c r="A226" s="40" t="n"/>
+      <c r="B226" s="40" t="n"/>
+      <c r="C226" s="40" t="n"/>
+      <c r="D226" s="40" t="n"/>
+      <c r="E226" s="40" t="n"/>
+      <c r="F226" s="40" t="n"/>
+      <c r="G226" s="40" t="n"/>
+      <c r="H226" s="17" t="n"/>
+    </row>
+    <row r="227" ht="22" customHeight="1">
+      <c r="A227" s="40" t="n"/>
+      <c r="B227" s="40" t="n"/>
+      <c r="C227" s="40" t="n"/>
+      <c r="D227" s="40" t="n"/>
+      <c r="E227" s="40" t="n"/>
+      <c r="F227" s="40" t="n"/>
+      <c r="G227" s="40" t="n"/>
+      <c r="H227" s="17" t="n"/>
+    </row>
+    <row r="228" ht="22" customHeight="1">
+      <c r="A228" s="40" t="n"/>
+      <c r="B228" s="40" t="n"/>
+      <c r="C228" s="40" t="n"/>
+      <c r="D228" s="40" t="n"/>
+      <c r="E228" s="40" t="n"/>
+      <c r="F228" s="40" t="n"/>
+      <c r="G228" s="40" t="n"/>
+      <c r="H228" s="17" t="n"/>
+    </row>
+    <row r="229" ht="22" customHeight="1">
+      <c r="A229" s="40" t="n"/>
+      <c r="B229" s="40" t="n"/>
+      <c r="C229" s="40" t="n"/>
+      <c r="D229" s="40" t="n"/>
+      <c r="E229" s="40" t="n"/>
+      <c r="F229" s="40" t="n"/>
+      <c r="G229" s="40" t="n"/>
+      <c r="H229" s="17" t="n"/>
+    </row>
+    <row r="230" ht="22" customHeight="1">
+      <c r="A230" s="40" t="n"/>
+      <c r="B230" s="40" t="n"/>
+      <c r="C230" s="40" t="n"/>
+      <c r="D230" s="40" t="n"/>
+      <c r="E230" s="40" t="n"/>
+      <c r="F230" s="40" t="n"/>
+      <c r="G230" s="40" t="n"/>
+      <c r="H230" s="17" t="n"/>
+    </row>
+    <row r="231" ht="22" customHeight="1">
+      <c r="A231" s="40" t="n"/>
+      <c r="B231" s="40" t="n"/>
+      <c r="C231" s="40" t="n"/>
+      <c r="D231" s="40" t="n"/>
+      <c r="E231" s="40" t="n"/>
+      <c r="F231" s="40" t="n"/>
+      <c r="G231" s="40" t="n"/>
+      <c r="H231" s="17" t="n"/>
+    </row>
+    <row r="232" ht="22" customHeight="1">
+      <c r="A232" s="40" t="n"/>
+      <c r="B232" s="40" t="n"/>
+      <c r="C232" s="40" t="n"/>
+      <c r="D232" s="40" t="n"/>
+      <c r="E232" s="40" t="n"/>
+      <c r="F232" s="40" t="n"/>
+      <c r="G232" s="40" t="n"/>
+      <c r="H232" s="17" t="n"/>
+    </row>
+    <row r="233" ht="22" customHeight="1">
+      <c r="A233" s="40" t="n"/>
+      <c r="B233" s="40" t="n"/>
+      <c r="C233" s="40" t="n"/>
+      <c r="D233" s="40" t="n"/>
+      <c r="E233" s="40" t="n"/>
+      <c r="F233" s="40" t="n"/>
+      <c r="G233" s="40" t="n"/>
+      <c r="H233" s="17" t="n"/>
+    </row>
+    <row r="234" ht="22" customHeight="1">
+      <c r="A234" s="40" t="n"/>
+      <c r="B234" s="40" t="n"/>
+      <c r="C234" s="40" t="n"/>
+      <c r="D234" s="40" t="n"/>
+      <c r="E234" s="40" t="n"/>
+      <c r="F234" s="40" t="n"/>
+      <c r="G234" s="40" t="n"/>
+      <c r="H234" s="17" t="n"/>
+    </row>
+    <row r="235" ht="22" customHeight="1">
+      <c r="A235" s="40" t="n"/>
+      <c r="B235" s="40" t="n"/>
+      <c r="C235" s="40" t="n"/>
+      <c r="D235" s="40" t="n"/>
+      <c r="E235" s="40" t="n"/>
+      <c r="F235" s="40" t="n"/>
+      <c r="G235" s="40" t="n"/>
+      <c r="H235" s="17" t="n"/>
+    </row>
+    <row r="236" ht="22" customHeight="1">
+      <c r="A236" s="40" t="n"/>
+      <c r="B236" s="40" t="n"/>
+      <c r="C236" s="40" t="n"/>
+      <c r="D236" s="40" t="n"/>
+      <c r="E236" s="40" t="n"/>
+      <c r="F236" s="40" t="n"/>
+      <c r="G236" s="40" t="n"/>
+      <c r="H236" s="17" t="n"/>
+    </row>
+    <row r="237" ht="22" customHeight="1">
+      <c r="A237" s="40" t="n"/>
+      <c r="B237" s="40" t="n"/>
+      <c r="C237" s="40" t="n"/>
+      <c r="D237" s="40" t="n"/>
+      <c r="E237" s="40" t="n"/>
+      <c r="F237" s="40" t="n"/>
+      <c r="G237" s="40" t="n"/>
+      <c r="H237" s="17" t="n"/>
+    </row>
+    <row r="238" ht="22" customHeight="1">
+      <c r="A238" s="40" t="n"/>
+      <c r="B238" s="40" t="n"/>
+      <c r="C238" s="40" t="n"/>
+      <c r="D238" s="40" t="n"/>
+      <c r="E238" s="40" t="n"/>
+      <c r="F238" s="40" t="n"/>
+      <c r="G238" s="40" t="n"/>
+      <c r="H238" s="17" t="n"/>
+    </row>
+    <row r="239" ht="22" customHeight="1">
+      <c r="A239" s="40" t="n"/>
+      <c r="B239" s="40" t="n"/>
+      <c r="C239" s="40" t="n"/>
+      <c r="D239" s="40" t="n"/>
+      <c r="E239" s="40" t="n"/>
+      <c r="F239" s="40" t="n"/>
+      <c r="G239" s="40" t="n"/>
+      <c r="H239" s="17" t="n"/>
+    </row>
+    <row r="240" ht="22" customHeight="1">
+      <c r="A240" s="40" t="n"/>
+      <c r="B240" s="40" t="n"/>
+      <c r="C240" s="40" t="n"/>
+      <c r="D240" s="40" t="n"/>
+      <c r="E240" s="40" t="n"/>
+      <c r="F240" s="40" t="n"/>
+      <c r="G240" s="40" t="n"/>
+      <c r="H240" s="17" t="n"/>
+    </row>
+    <row r="241" ht="22" customHeight="1">
+      <c r="A241" s="40" t="n"/>
+      <c r="B241" s="40" t="n"/>
+      <c r="C241" s="40" t="n"/>
+      <c r="D241" s="40" t="n"/>
+      <c r="E241" s="40" t="n"/>
+      <c r="F241" s="40" t="n"/>
+      <c r="G241" s="40" t="n"/>
+      <c r="H241" s="17" t="n"/>
+    </row>
+    <row r="242" ht="22" customHeight="1">
+      <c r="A242" s="40" t="n"/>
+      <c r="B242" s="40" t="n"/>
+      <c r="C242" s="40" t="n"/>
+      <c r="D242" s="40" t="n"/>
+      <c r="E242" s="40" t="n"/>
+      <c r="F242" s="40" t="n"/>
+      <c r="G242" s="40" t="n"/>
+      <c r="H242" s="17" t="n"/>
+    </row>
+    <row r="243" ht="22" customHeight="1">
+      <c r="A243" s="40" t="n"/>
+      <c r="B243" s="40" t="n"/>
+      <c r="C243" s="40" t="n"/>
+      <c r="D243" s="40" t="n"/>
+      <c r="E243" s="40" t="n"/>
+      <c r="F243" s="40" t="n"/>
+      <c r="G243" s="40" t="n"/>
+      <c r="H243" s="17" t="n"/>
+    </row>
+    <row r="244" ht="22" customHeight="1">
+      <c r="A244" s="40" t="n"/>
+      <c r="B244" s="40" t="n"/>
+      <c r="C244" s="40" t="n"/>
+      <c r="D244" s="40" t="n"/>
+      <c r="E244" s="40" t="n"/>
+      <c r="F244" s="40" t="n"/>
+      <c r="G244" s="40" t="n"/>
+      <c r="H244" s="17" t="n"/>
+    </row>
+    <row r="245" ht="22" customHeight="1">
+      <c r="A245" s="40" t="n"/>
+      <c r="B245" s="40" t="n"/>
+      <c r="C245" s="40" t="n"/>
+      <c r="D245" s="40" t="n"/>
+      <c r="E245" s="40" t="n"/>
+      <c r="F245" s="40" t="n"/>
+      <c r="G245" s="40" t="n"/>
+      <c r="H245" s="17" t="n"/>
+    </row>
+    <row r="246" ht="22" customHeight="1">
+      <c r="A246" s="40" t="n"/>
+      <c r="B246" s="40" t="n"/>
+      <c r="C246" s="40" t="n"/>
+      <c r="D246" s="40" t="n"/>
+      <c r="E246" s="40" t="n"/>
+      <c r="F246" s="40" t="n"/>
+      <c r="G246" s="40" t="n"/>
+      <c r="H246" s="17" t="n"/>
+    </row>
+    <row r="247" ht="22" customHeight="1">
+      <c r="A247" s="40" t="n"/>
+      <c r="B247" s="40" t="n"/>
+      <c r="C247" s="40" t="n"/>
+      <c r="D247" s="40" t="n"/>
+      <c r="E247" s="40" t="n"/>
+      <c r="F247" s="40" t="n"/>
+      <c r="G247" s="40" t="n"/>
+      <c r="H247" s="17" t="n"/>
+    </row>
+    <row r="248" ht="22" customHeight="1">
+      <c r="A248" s="40" t="n"/>
+      <c r="B248" s="40" t="n"/>
+      <c r="C248" s="40" t="n"/>
+      <c r="D248" s="40" t="n"/>
+      <c r="E248" s="40" t="n"/>
+      <c r="F248" s="40" t="n"/>
+      <c r="G248" s="40" t="n"/>
+      <c r="H248" s="17" t="n"/>
+    </row>
+    <row r="249" ht="22" customHeight="1">
+      <c r="A249" s="40" t="n"/>
+      <c r="B249" s="40" t="n"/>
+      <c r="C249" s="40" t="n"/>
+      <c r="D249" s="40" t="n"/>
+      <c r="E249" s="40" t="n"/>
+      <c r="F249" s="40" t="n"/>
+      <c r="G249" s="40" t="n"/>
+      <c r="H249" s="17" t="n"/>
+    </row>
+    <row r="250" ht="22" customHeight="1">
+      <c r="A250" s="40" t="n"/>
+      <c r="B250" s="40" t="n"/>
+      <c r="C250" s="40" t="n"/>
+      <c r="D250" s="40" t="n"/>
+      <c r="E250" s="40" t="n"/>
+      <c r="F250" s="40" t="n"/>
+      <c r="G250" s="40" t="n"/>
+      <c r="H250" s="17" t="n"/>
+    </row>
+    <row r="251" ht="22" customHeight="1">
+      <c r="A251" s="40" t="n"/>
+      <c r="B251" s="40" t="n"/>
+      <c r="C251" s="40" t="n"/>
+      <c r="D251" s="40" t="n"/>
+      <c r="E251" s="40" t="n"/>
+      <c r="F251" s="40" t="n"/>
+      <c r="G251" s="40" t="n"/>
+      <c r="H251" s="17" t="n"/>
+    </row>
+    <row r="252" ht="22" customHeight="1">
+      <c r="A252" s="40" t="n"/>
+      <c r="B252" s="40" t="n"/>
+      <c r="C252" s="40" t="n"/>
+      <c r="D252" s="40" t="n"/>
+      <c r="E252" s="40" t="n"/>
+      <c r="F252" s="40" t="n"/>
+      <c r="G252" s="40" t="n"/>
+      <c r="H252" s="17" t="n"/>
+    </row>
+    <row r="253" ht="22" customHeight="1">
+      <c r="A253" s="40" t="n"/>
+      <c r="B253" s="40" t="n"/>
+      <c r="C253" s="40" t="n"/>
+      <c r="D253" s="40" t="n"/>
+      <c r="E253" s="40" t="n"/>
+      <c r="F253" s="40" t="n"/>
+      <c r="G253" s="40" t="n"/>
+      <c r="H253" s="17" t="n"/>
+    </row>
+    <row r="254" ht="22" customHeight="1">
+      <c r="A254" s="40" t="n"/>
+      <c r="B254" s="40" t="n"/>
+      <c r="C254" s="40" t="n"/>
+      <c r="D254" s="40" t="n"/>
+      <c r="E254" s="40" t="n"/>
+      <c r="F254" s="40" t="n"/>
+      <c r="G254" s="40" t="n"/>
+      <c r="H254" s="17" t="n"/>
+    </row>
+    <row r="255" ht="22" customHeight="1">
+      <c r="A255" s="40" t="n"/>
+      <c r="B255" s="40" t="n"/>
+      <c r="C255" s="40" t="n"/>
+      <c r="D255" s="40" t="n"/>
+      <c r="E255" s="40" t="n"/>
+      <c r="F255" s="40" t="n"/>
+      <c r="G255" s="40" t="n"/>
+      <c r="H255" s="17" t="n"/>
+    </row>
+    <row r="256" ht="22" customHeight="1">
+      <c r="A256" s="40" t="n"/>
+      <c r="B256" s="40" t="n"/>
+      <c r="C256" s="40" t="n"/>
+      <c r="D256" s="40" t="n"/>
+      <c r="E256" s="40" t="n"/>
+      <c r="F256" s="40" t="n"/>
+      <c r="G256" s="40" t="n"/>
+      <c r="H256" s="17" t="n"/>
+    </row>
+    <row r="257" ht="22" customHeight="1">
+      <c r="A257" s="40" t="n"/>
+      <c r="B257" s="40" t="n"/>
+      <c r="C257" s="40" t="n"/>
+      <c r="D257" s="40" t="n"/>
+      <c r="E257" s="40" t="n"/>
+      <c r="F257" s="40" t="n"/>
+      <c r="G257" s="40" t="n"/>
+      <c r="H257" s="17" t="n"/>
+    </row>
+    <row r="258" ht="22" customHeight="1">
+      <c r="A258" s="40" t="n"/>
+      <c r="B258" s="40" t="n"/>
+      <c r="C258" s="40" t="n"/>
+      <c r="D258" s="40" t="n"/>
+      <c r="E258" s="40" t="n"/>
+      <c r="F258" s="40" t="n"/>
+      <c r="G258" s="40" t="n"/>
+      <c r="H258" s="17" t="n"/>
+    </row>
+    <row r="259" ht="22" customHeight="1">
+      <c r="A259" s="40" t="n"/>
+      <c r="B259" s="40" t="n"/>
+      <c r="C259" s="40" t="n"/>
+      <c r="D259" s="40" t="n"/>
+      <c r="E259" s="40" t="n"/>
+      <c r="F259" s="40" t="n"/>
+      <c r="G259" s="40" t="n"/>
+      <c r="H259" s="17" t="n"/>
+    </row>
+    <row r="260" ht="22" customHeight="1">
+      <c r="A260" s="40" t="n"/>
+      <c r="B260" s="40" t="n"/>
+      <c r="C260" s="40" t="n"/>
+      <c r="D260" s="40" t="n"/>
+      <c r="E260" s="40" t="n"/>
+      <c r="F260" s="40" t="n"/>
+      <c r="G260" s="40" t="n"/>
+      <c r="H260" s="17" t="n"/>
+    </row>
+    <row r="261" ht="22" customHeight="1">
+      <c r="A261" s="40" t="n"/>
+      <c r="B261" s="40" t="n"/>
+      <c r="C261" s="40" t="n"/>
+      <c r="D261" s="40" t="n"/>
+      <c r="E261" s="40" t="n"/>
+      <c r="F261" s="40" t="n"/>
+      <c r="G261" s="40" t="n"/>
+      <c r="H261" s="17" t="n"/>
+    </row>
+    <row r="262" ht="22" customHeight="1">
+      <c r="A262" s="40" t="n"/>
+      <c r="B262" s="40" t="n"/>
+      <c r="C262" s="40" t="n"/>
+      <c r="D262" s="40" t="n"/>
+      <c r="E262" s="40" t="n"/>
+      <c r="F262" s="40" t="n"/>
+      <c r="G262" s="40" t="n"/>
+      <c r="H262" s="17" t="n"/>
+    </row>
+    <row r="263" ht="22" customHeight="1">
+      <c r="A263" s="40" t="n"/>
+      <c r="B263" s="40" t="n"/>
+      <c r="C263" s="40" t="n"/>
+      <c r="D263" s="40" t="n"/>
+      <c r="E263" s="40" t="n"/>
+      <c r="F263" s="40" t="n"/>
+      <c r="G263" s="40" t="n"/>
+      <c r="H263" s="17" t="n"/>
+    </row>
+    <row r="264" ht="22" customHeight="1">
+      <c r="A264" s="40" t="n"/>
+      <c r="B264" s="40" t="n"/>
+      <c r="C264" s="40" t="n"/>
+      <c r="D264" s="40" t="n"/>
+      <c r="E264" s="40" t="n"/>
+      <c r="F264" s="40" t="n"/>
+      <c r="G264" s="40" t="n"/>
+      <c r="H264" s="17" t="n"/>
+    </row>
+    <row r="265" ht="22" customHeight="1">
+      <c r="A265" s="40" t="n"/>
+      <c r="B265" s="40" t="n"/>
+      <c r="C265" s="40" t="n"/>
+      <c r="D265" s="40" t="n"/>
+      <c r="E265" s="40" t="n"/>
+      <c r="F265" s="40" t="n"/>
+      <c r="G265" s="40" t="n"/>
+      <c r="H265" s="17" t="n"/>
+    </row>
+    <row r="266" ht="22" customHeight="1">
+      <c r="A266" s="40" t="n"/>
+      <c r="B266" s="40" t="n"/>
+      <c r="C266" s="40" t="n"/>
+      <c r="D266" s="40" t="n"/>
+      <c r="E266" s="40" t="n"/>
+      <c r="F266" s="40" t="n"/>
+      <c r="G266" s="40" t="n"/>
+      <c r="H266" s="17" t="n"/>
+    </row>
+    <row r="267" ht="22" customHeight="1">
+      <c r="A267" s="40" t="n"/>
+      <c r="B267" s="40" t="n"/>
+      <c r="C267" s="40" t="n"/>
+      <c r="D267" s="40" t="n"/>
+      <c r="E267" s="40" t="n"/>
+      <c r="F267" s="40" t="n"/>
+      <c r="G267" s="40" t="n"/>
+      <c r="H267" s="17" t="n"/>
+    </row>
+    <row r="268" ht="22" customHeight="1">
+      <c r="A268" s="40" t="n"/>
+      <c r="B268" s="40" t="n"/>
+      <c r="C268" s="40" t="n"/>
+      <c r="D268" s="40" t="n"/>
+      <c r="E268" s="40" t="n"/>
+      <c r="F268" s="40" t="n"/>
+      <c r="G268" s="40" t="n"/>
+      <c r="H268" s="17" t="n"/>
+    </row>
+    <row r="269" ht="22" customHeight="1">
+      <c r="A269" s="40" t="n"/>
+      <c r="B269" s="40" t="n"/>
+      <c r="C269" s="40" t="n"/>
+      <c r="D269" s="40" t="n"/>
+      <c r="E269" s="40" t="n"/>
+      <c r="F269" s="40" t="n"/>
+      <c r="G269" s="40" t="n"/>
+      <c r="H269" s="17" t="n"/>
+    </row>
+    <row r="270" ht="22" customHeight="1">
+      <c r="A270" s="40" t="n"/>
+      <c r="B270" s="40" t="n"/>
+      <c r="C270" s="40" t="n"/>
+      <c r="D270" s="40" t="n"/>
+      <c r="E270" s="40" t="n"/>
+      <c r="F270" s="40" t="n"/>
+      <c r="G270" s="40" t="n"/>
+      <c r="H270" s="17" t="n"/>
+    </row>
+    <row r="271" ht="22" customHeight="1">
+      <c r="A271" s="40" t="n"/>
+      <c r="B271" s="40" t="n"/>
+      <c r="C271" s="40" t="n"/>
+      <c r="D271" s="40" t="n"/>
+      <c r="E271" s="40" t="n"/>
+      <c r="F271" s="40" t="n"/>
+      <c r="G271" s="40" t="n"/>
+      <c r="H271" s="17" t="n"/>
+    </row>
+    <row r="272" ht="22" customHeight="1">
+      <c r="A272" s="40" t="n"/>
+      <c r="B272" s="40" t="n"/>
+      <c r="C272" s="40" t="n"/>
+      <c r="D272" s="40" t="n"/>
+      <c r="E272" s="40" t="n"/>
+      <c r="F272" s="40" t="n"/>
+      <c r="G272" s="40" t="n"/>
+      <c r="H272" s="17" t="n"/>
+    </row>
+    <row r="273" ht="22" customHeight="1">
+      <c r="A273" s="40" t="n"/>
+      <c r="B273" s="40" t="n"/>
+      <c r="C273" s="40" t="n"/>
+      <c r="D273" s="40" t="n"/>
+      <c r="E273" s="40" t="n"/>
+      <c r="F273" s="40" t="n"/>
+      <c r="G273" s="40" t="n"/>
+      <c r="H273" s="17" t="n"/>
+    </row>
+    <row r="274" ht="22" customHeight="1">
+      <c r="A274" s="40" t="n"/>
+      <c r="B274" s="40" t="n"/>
+      <c r="C274" s="40" t="n"/>
+      <c r="D274" s="40" t="n"/>
+      <c r="E274" s="40" t="n"/>
+      <c r="F274" s="40" t="n"/>
+      <c r="G274" s="40" t="n"/>
+      <c r="H274" s="17" t="n"/>
+    </row>
+    <row r="275" ht="22" customHeight="1">
+      <c r="A275" s="40" t="n"/>
+      <c r="B275" s="40" t="n"/>
+      <c r="C275" s="40" t="n"/>
+      <c r="D275" s="40" t="n"/>
+      <c r="E275" s="40" t="n"/>
+      <c r="F275" s="40" t="n"/>
+      <c r="G275" s="40" t="n"/>
+      <c r="H275" s="17" t="n"/>
+    </row>
+    <row r="276" ht="22" customHeight="1">
+      <c r="A276" s="40" t="n"/>
+      <c r="B276" s="40" t="n"/>
+      <c r="C276" s="40" t="n"/>
+      <c r="D276" s="40" t="n"/>
+      <c r="E276" s="40" t="n"/>
+      <c r="F276" s="40" t="n"/>
+      <c r="G276" s="40" t="n"/>
+      <c r="H276" s="17" t="n"/>
+    </row>
+    <row r="277" ht="22" customHeight="1">
+      <c r="A277" s="40" t="n"/>
+      <c r="B277" s="40" t="n"/>
+      <c r="C277" s="40" t="n"/>
+      <c r="D277" s="40" t="n"/>
+      <c r="E277" s="40" t="n"/>
+      <c r="F277" s="40" t="n"/>
+      <c r="G277" s="40" t="n"/>
+      <c r="H277" s="17" t="n"/>
+    </row>
+    <row r="278" ht="22" customHeight="1">
+      <c r="A278" s="40" t="n"/>
+      <c r="B278" s="40" t="n"/>
+      <c r="C278" s="40" t="n"/>
+      <c r="D278" s="40" t="n"/>
+      <c r="E278" s="40" t="n"/>
+      <c r="F278" s="40" t="n"/>
+      <c r="G278" s="40" t="n"/>
+      <c r="H278" s="17" t="n"/>
+    </row>
+    <row r="279" ht="22" customHeight="1">
+      <c r="A279" s="40" t="n"/>
+      <c r="B279" s="40" t="n"/>
+      <c r="C279" s="40" t="n"/>
+      <c r="D279" s="40" t="n"/>
+      <c r="E279" s="40" t="n"/>
+      <c r="F279" s="40" t="n"/>
+      <c r="G279" s="40" t="n"/>
+      <c r="H279" s="17" t="n"/>
+    </row>
+    <row r="280" ht="22" customHeight="1">
+      <c r="A280" s="40" t="n"/>
+      <c r="B280" s="40" t="n"/>
+      <c r="C280" s="40" t="n"/>
+      <c r="D280" s="40" t="n"/>
+      <c r="E280" s="40" t="n"/>
+      <c r="F280" s="40" t="n"/>
+      <c r="G280" s="40" t="n"/>
+      <c r="H280" s="17" t="n"/>
+    </row>
+    <row r="281" ht="22" customHeight="1">
+      <c r="A281" s="40" t="n"/>
+      <c r="B281" s="40" t="n"/>
+      <c r="C281" s="40" t="n"/>
+      <c r="D281" s="40" t="n"/>
+      <c r="E281" s="40" t="n"/>
+      <c r="F281" s="40" t="n"/>
+      <c r="G281" s="40" t="n"/>
+      <c r="H281" s="17" t="n"/>
+    </row>
+    <row r="282" ht="22" customHeight="1">
+      <c r="A282" s="40" t="n"/>
+      <c r="B282" s="40" t="n"/>
+      <c r="C282" s="40" t="n"/>
+      <c r="D282" s="40" t="n"/>
+      <c r="E282" s="40" t="n"/>
+      <c r="F282" s="40" t="n"/>
+      <c r="G282" s="40" t="n"/>
+      <c r="H282" s="17" t="n"/>
+    </row>
+    <row r="283" ht="22" customHeight="1">
+      <c r="A283" s="40" t="n"/>
+      <c r="B283" s="40" t="n"/>
+      <c r="C283" s="40" t="n"/>
+      <c r="D283" s="40" t="n"/>
+      <c r="E283" s="40" t="n"/>
+      <c r="F283" s="40" t="n"/>
+      <c r="G283" s="40" t="n"/>
+      <c r="H283" s="17" t="n"/>
+    </row>
+    <row r="284" ht="22" customHeight="1">
+      <c r="A284" s="40" t="n"/>
+      <c r="B284" s="40" t="n"/>
+      <c r="C284" s="40" t="n"/>
+      <c r="D284" s="40" t="n"/>
+      <c r="E284" s="40" t="n"/>
+      <c r="F284" s="40" t="n"/>
+      <c r="G284" s="40" t="n"/>
+      <c r="H284" s="17" t="n"/>
+    </row>
+    <row r="285" ht="22" customHeight="1">
+      <c r="A285" s="40" t="n"/>
+      <c r="B285" s="40" t="n"/>
+      <c r="C285" s="40" t="n"/>
+      <c r="D285" s="40" t="n"/>
+      <c r="E285" s="40" t="n"/>
+      <c r="F285" s="40" t="n"/>
+      <c r="G285" s="40" t="n"/>
+      <c r="H285" s="17" t="n"/>
+    </row>
+    <row r="286" ht="22" customHeight="1">
+      <c r="A286" s="40" t="n"/>
+      <c r="B286" s="40" t="n"/>
+      <c r="C286" s="40" t="n"/>
+      <c r="D286" s="40" t="n"/>
+      <c r="E286" s="40" t="n"/>
+      <c r="F286" s="40" t="n"/>
+      <c r="G286" s="40" t="n"/>
+      <c r="H286" s="17" t="n"/>
+    </row>
+    <row r="287" ht="22" customHeight="1">
+      <c r="A287" s="40" t="n"/>
+      <c r="B287" s="40" t="n"/>
+      <c r="C287" s="40" t="n"/>
+      <c r="D287" s="40" t="n"/>
+      <c r="E287" s="40" t="n"/>
+      <c r="F287" s="40" t="n"/>
+      <c r="G287" s="40" t="n"/>
+      <c r="H287" s="17" t="n"/>
+    </row>
+    <row r="288" ht="22" customHeight="1">
+      <c r="A288" s="40" t="n"/>
+      <c r="B288" s="40" t="n"/>
+      <c r="C288" s="40" t="n"/>
+      <c r="D288" s="40" t="n"/>
+      <c r="E288" s="40" t="n"/>
+      <c r="F288" s="40" t="n"/>
+      <c r="G288" s="40" t="n"/>
+      <c r="H288" s="17" t="n"/>
+    </row>
+    <row r="289" ht="22" customHeight="1">
+      <c r="A289" s="40" t="n"/>
+      <c r="B289" s="40" t="n"/>
+      <c r="C289" s="40" t="n"/>
+      <c r="D289" s="40" t="n"/>
+      <c r="E289" s="40" t="n"/>
+      <c r="F289" s="40" t="n"/>
+      <c r="G289" s="40" t="n"/>
+      <c r="H289" s="17" t="n"/>
+    </row>
+    <row r="290" ht="22" customHeight="1">
+      <c r="A290" s="40" t="n"/>
+      <c r="B290" s="40" t="n"/>
+      <c r="C290" s="40" t="n"/>
+      <c r="D290" s="40" t="n"/>
+      <c r="E290" s="40" t="n"/>
+      <c r="F290" s="40" t="n"/>
+      <c r="G290" s="40" t="n"/>
+      <c r="H290" s="17" t="n"/>
+    </row>
+    <row r="291" ht="22" customHeight="1">
+      <c r="A291" s="40" t="n"/>
+      <c r="B291" s="40" t="n"/>
+      <c r="C291" s="40" t="n"/>
+      <c r="D291" s="40" t="n"/>
+      <c r="E291" s="40" t="n"/>
+      <c r="F291" s="40" t="n"/>
+      <c r="G291" s="40" t="n"/>
+      <c r="H291" s="17" t="n"/>
+    </row>
+    <row r="292" ht="22" customHeight="1">
+      <c r="A292" s="40" t="n"/>
+      <c r="B292" s="40" t="n"/>
+      <c r="C292" s="40" t="n"/>
+      <c r="D292" s="40" t="n"/>
+      <c r="E292" s="40" t="n"/>
+      <c r="F292" s="40" t="n"/>
+      <c r="G292" s="40" t="n"/>
+      <c r="H292" s="17" t="n"/>
+    </row>
+    <row r="293" ht="22" customHeight="1">
+      <c r="A293" s="40" t="n"/>
+      <c r="B293" s="40" t="n"/>
+      <c r="C293" s="40" t="n"/>
+      <c r="D293" s="40" t="n"/>
+      <c r="E293" s="40" t="n"/>
+      <c r="F293" s="40" t="n"/>
+      <c r="G293" s="40" t="n"/>
+      <c r="H293" s="17" t="n"/>
+    </row>
+    <row r="294" ht="22" customHeight="1">
+      <c r="A294" s="40" t="n"/>
+      <c r="B294" s="40" t="n"/>
+      <c r="C294" s="40" t="n"/>
+      <c r="D294" s="40" t="n"/>
+      <c r="E294" s="40" t="n"/>
+      <c r="F294" s="40" t="n"/>
+      <c r="G294" s="40" t="n"/>
+      <c r="H294" s="17" t="n"/>
+    </row>
+    <row r="295" ht="22" customHeight="1">
+      <c r="A295" s="40" t="n"/>
+      <c r="B295" s="40" t="n"/>
+      <c r="C295" s="40" t="n"/>
+      <c r="D295" s="40" t="n"/>
+      <c r="E295" s="40" t="n"/>
+      <c r="F295" s="40" t="n"/>
+      <c r="G295" s="40" t="n"/>
+      <c r="H295" s="17" t="n"/>
+    </row>
+    <row r="296" ht="22" customHeight="1">
+      <c r="A296" s="40" t="n"/>
+      <c r="B296" s="40" t="n"/>
+      <c r="C296" s="40" t="n"/>
+      <c r="D296" s="40" t="n"/>
+      <c r="E296" s="40" t="n"/>
+      <c r="F296" s="40" t="n"/>
+      <c r="G296" s="40" t="n"/>
+      <c r="H296" s="17" t="n"/>
+    </row>
+    <row r="297" ht="22" customHeight="1">
+      <c r="A297" s="40" t="n"/>
+      <c r="B297" s="40" t="n"/>
+      <c r="C297" s="40" t="n"/>
+      <c r="D297" s="40" t="n"/>
+      <c r="E297" s="40" t="n"/>
+      <c r="F297" s="40" t="n"/>
+      <c r="G297" s="40" t="n"/>
+      <c r="H297" s="17" t="n"/>
+    </row>
+    <row r="298" ht="22" customHeight="1">
+      <c r="A298" s="40" t="n"/>
+      <c r="B298" s="40" t="n"/>
+      <c r="C298" s="40" t="n"/>
+      <c r="D298" s="40" t="n"/>
+      <c r="E298" s="40" t="n"/>
+      <c r="F298" s="40" t="n"/>
+      <c r="G298" s="40" t="n"/>
+      <c r="H298" s="17" t="n"/>
+    </row>
+    <row r="299" ht="22" customHeight="1">
+      <c r="A299" s="40" t="n"/>
+      <c r="B299" s="40" t="n"/>
+      <c r="C299" s="40" t="n"/>
+      <c r="D299" s="40" t="n"/>
+      <c r="E299" s="40" t="n"/>
+      <c r="F299" s="40" t="n"/>
+      <c r="G299" s="40" t="n"/>
+      <c r="H299" s="17" t="n"/>
+    </row>
+    <row r="300" ht="22" customHeight="1">
+      <c r="A300" s="40" t="n"/>
+      <c r="B300" s="40" t="n"/>
+      <c r="C300" s="40" t="n"/>
+      <c r="D300" s="40" t="n"/>
+      <c r="E300" s="40" t="n"/>
+      <c r="F300" s="40" t="n"/>
+      <c r="G300" s="40" t="n"/>
+      <c r="H300" s="17" t="n"/>
+    </row>
+    <row r="301" ht="22" customHeight="1">
+      <c r="A301" s="40" t="n"/>
+      <c r="B301" s="40" t="n"/>
+      <c r="C301" s="40" t="n"/>
+      <c r="D301" s="40" t="n"/>
+      <c r="E301" s="40" t="n"/>
+      <c r="F301" s="40" t="n"/>
+      <c r="G301" s="40" t="n"/>
+      <c r="H301" s="17" t="n"/>
+    </row>
+    <row r="302" ht="22" customHeight="1">
+      <c r="A302" s="40" t="n"/>
+      <c r="B302" s="40" t="n"/>
+      <c r="C302" s="40" t="n"/>
+      <c r="D302" s="40" t="n"/>
+      <c r="E302" s="40" t="n"/>
+      <c r="F302" s="40" t="n"/>
+      <c r="G302" s="40" t="n"/>
+      <c r="H302" s="17" t="n"/>
+    </row>
+    <row r="303" ht="22" customHeight="1">
+      <c r="A303" s="40" t="n"/>
+      <c r="B303" s="40" t="n"/>
+      <c r="C303" s="40" t="n"/>
+      <c r="D303" s="40" t="n"/>
+      <c r="E303" s="40" t="n"/>
+      <c r="F303" s="40" t="n"/>
+      <c r="G303" s="40" t="n"/>
+      <c r="H303" s="17" t="n"/>
+    </row>
+    <row r="304" ht="22" customHeight="1">
+      <c r="A304" s="40" t="n"/>
+      <c r="B304" s="40" t="n"/>
+      <c r="C304" s="40" t="n"/>
+      <c r="D304" s="40" t="n"/>
+      <c r="E304" s="40" t="n"/>
+      <c r="F304" s="40" t="n"/>
+      <c r="G304" s="40" t="n"/>
+      <c r="H304" s="17" t="n"/>
+    </row>
+    <row r="305" ht="22" customHeight="1">
+      <c r="A305" s="40" t="n"/>
+      <c r="B305" s="40" t="n"/>
+      <c r="C305" s="40" t="n"/>
+      <c r="D305" s="40" t="n"/>
+      <c r="E305" s="40" t="n"/>
+      <c r="F305" s="40" t="n"/>
+      <c r="G305" s="40" t="n"/>
+      <c r="H305" s="17" t="n"/>
+    </row>
+    <row r="306" ht="22" customHeight="1">
+      <c r="A306" s="40" t="n"/>
+      <c r="B306" s="40" t="n"/>
+      <c r="C306" s="40" t="n"/>
+      <c r="D306" s="40" t="n"/>
+      <c r="E306" s="40" t="n"/>
+      <c r="F306" s="40" t="n"/>
+      <c r="G306" s="40" t="n"/>
+      <c r="H306" s="17" t="n"/>
+    </row>
+    <row r="307" ht="22" customHeight="1">
+      <c r="A307" s="40" t="n"/>
+      <c r="B307" s="40" t="n"/>
+      <c r="C307" s="40" t="n"/>
+      <c r="D307" s="40" t="n"/>
+      <c r="E307" s="40" t="n"/>
+      <c r="F307" s="40" t="n"/>
+      <c r="G307" s="40" t="n"/>
+      <c r="H307" s="17" t="n"/>
+    </row>
+    <row r="308" ht="22" customHeight="1">
+      <c r="A308" s="40" t="n"/>
+      <c r="B308" s="40" t="n"/>
+      <c r="C308" s="40" t="n"/>
+      <c r="D308" s="40" t="n"/>
+      <c r="E308" s="40" t="n"/>
+      <c r="F308" s="40" t="n"/>
+      <c r="G308" s="40" t="n"/>
+      <c r="H308" s="17" t="n"/>
+    </row>
+    <row r="309" ht="22" customHeight="1">
+      <c r="A309" s="40" t="n"/>
+      <c r="B309" s="40" t="n"/>
+      <c r="C309" s="40" t="n"/>
+      <c r="D309" s="40" t="n"/>
+      <c r="E309" s="40" t="n"/>
+      <c r="F309" s="40" t="n"/>
+      <c r="G309" s="40" t="n"/>
+      <c r="H309" s="17" t="n"/>
+    </row>
+    <row r="310" ht="22" customHeight="1">
+      <c r="A310" s="40" t="n"/>
+      <c r="B310" s="40" t="n"/>
+      <c r="C310" s="40" t="n"/>
+      <c r="D310" s="40" t="n"/>
+      <c r="E310" s="40" t="n"/>
+      <c r="F310" s="40" t="n"/>
+      <c r="G310" s="40" t="n"/>
+      <c r="H310" s="17" t="n"/>
+    </row>
+    <row r="311" ht="22" customHeight="1">
+      <c r="A311" s="40" t="n"/>
+      <c r="B311" s="40" t="n"/>
+      <c r="C311" s="40" t="n"/>
+      <c r="D311" s="40" t="n"/>
+      <c r="E311" s="40" t="n"/>
+      <c r="F311" s="40" t="n"/>
+      <c r="G311" s="40" t="n"/>
+      <c r="H311" s="17" t="n"/>
+    </row>
+    <row r="312" ht="22" customHeight="1">
+      <c r="A312" s="40" t="n"/>
+      <c r="B312" s="40" t="n"/>
+      <c r="C312" s="40" t="n"/>
+      <c r="D312" s="40" t="n"/>
+      <c r="E312" s="40" t="n"/>
+      <c r="F312" s="40" t="n"/>
+      <c r="G312" s="40" t="n"/>
+      <c r="H312" s="17" t="n"/>
+    </row>
+    <row r="313" ht="22" customHeight="1">
+      <c r="A313" s="40" t="n"/>
+      <c r="B313" s="40" t="n"/>
+      <c r="C313" s="40" t="n"/>
+      <c r="D313" s="40" t="n"/>
+      <c r="E313" s="40" t="n"/>
+      <c r="F313" s="40" t="n"/>
+      <c r="G313" s="40" t="n"/>
+      <c r="H313" s="17" t="n"/>
+    </row>
+    <row r="314" ht="22" customHeight="1">
+      <c r="A314" s="40" t="n"/>
+      <c r="B314" s="40" t="n"/>
+      <c r="C314" s="40" t="n"/>
+      <c r="D314" s="40" t="n"/>
+      <c r="E314" s="40" t="n"/>
+      <c r="F314" s="40" t="n"/>
+      <c r="G314" s="40" t="n"/>
+      <c r="H314" s="17" t="n"/>
+    </row>
+    <row r="315" ht="22" customHeight="1">
+      <c r="A315" s="40" t="n"/>
+      <c r="B315" s="40" t="n"/>
+      <c r="C315" s="40" t="n"/>
+      <c r="D315" s="40" t="n"/>
+      <c r="E315" s="40" t="n"/>
+      <c r="F315" s="40" t="n"/>
+      <c r="G315" s="40" t="n"/>
+      <c r="H315" s="17" t="n"/>
+    </row>
+    <row r="316" ht="22" customHeight="1">
+      <c r="A316" s="40" t="n"/>
+      <c r="B316" s="40" t="n"/>
+      <c r="C316" s="40" t="n"/>
+      <c r="D316" s="40" t="n"/>
+      <c r="E316" s="40" t="n"/>
+      <c r="F316" s="40" t="n"/>
+      <c r="G316" s="40" t="n"/>
+      <c r="H316" s="17" t="n"/>
+    </row>
+    <row r="317" ht="22" customHeight="1">
+      <c r="A317" s="40" t="n"/>
+      <c r="B317" s="40" t="n"/>
+      <c r="C317" s="40" t="n"/>
+      <c r="D317" s="40" t="n"/>
+      <c r="E317" s="40" t="n"/>
+      <c r="F317" s="40" t="n"/>
+      <c r="G317" s="40" t="n"/>
+      <c r="H317" s="17" t="n"/>
+    </row>
+    <row r="318" ht="22" customHeight="1">
+      <c r="A318" s="40" t="n"/>
+      <c r="B318" s="40" t="n"/>
+      <c r="C318" s="40" t="n"/>
+      <c r="D318" s="40" t="n"/>
+      <c r="E318" s="40" t="n"/>
+      <c r="F318" s="40" t="n"/>
+      <c r="G318" s="40" t="n"/>
+      <c r="H318" s="17" t="n"/>
+    </row>
+    <row r="319" ht="22" customHeight="1">
+      <c r="A319" s="40" t="n"/>
+      <c r="B319" s="40" t="n"/>
+      <c r="C319" s="40" t="n"/>
+      <c r="D319" s="40" t="n"/>
+      <c r="E319" s="40" t="n"/>
+      <c r="F319" s="40" t="n"/>
+      <c r="G319" s="40" t="n"/>
+      <c r="H319" s="17" t="n"/>
+    </row>
+    <row r="320" ht="22" customHeight="1">
+      <c r="A320" s="40" t="n"/>
+      <c r="B320" s="40" t="n"/>
+      <c r="C320" s="40" t="n"/>
+      <c r="D320" s="40" t="n"/>
+      <c r="E320" s="40" t="n"/>
+      <c r="F320" s="40" t="n"/>
+      <c r="G320" s="40" t="n"/>
+      <c r="H320" s="17" t="n"/>
+    </row>
+    <row r="321" ht="22" customHeight="1">
+      <c r="A321" s="40" t="n"/>
+      <c r="B321" s="40" t="n"/>
+      <c r="C321" s="40" t="n"/>
+      <c r="D321" s="40" t="n"/>
+      <c r="E321" s="40" t="n"/>
+      <c r="F321" s="40" t="n"/>
+      <c r="G321" s="40" t="n"/>
+      <c r="H321" s="17" t="n"/>
+    </row>
+    <row r="322" ht="22" customHeight="1">
+      <c r="A322" s="40" t="n"/>
+      <c r="B322" s="40" t="n"/>
+      <c r="C322" s="40" t="n"/>
+      <c r="D322" s="40" t="n"/>
+      <c r="E322" s="40" t="n"/>
+      <c r="F322" s="40" t="n"/>
+      <c r="G322" s="40" t="n"/>
+      <c r="H322" s="17" t="n"/>
+    </row>
+    <row r="323" ht="22" customHeight="1">
+      <c r="A323" s="40" t="n"/>
+      <c r="B323" s="40" t="n"/>
+      <c r="C323" s="40" t="n"/>
+      <c r="D323" s="40" t="n"/>
+      <c r="E323" s="40" t="n"/>
+      <c r="F323" s="40" t="n"/>
+      <c r="G323" s="40" t="n"/>
+      <c r="H323" s="17" t="n"/>
+    </row>
+    <row r="324" ht="22" customHeight="1">
+      <c r="A324" s="40" t="n"/>
+      <c r="B324" s="40" t="n"/>
+      <c r="C324" s="40" t="n"/>
+      <c r="D324" s="40" t="n"/>
+      <c r="E324" s="40" t="n"/>
+      <c r="F324" s="40" t="n"/>
+      <c r="G324" s="40" t="n"/>
+      <c r="H324" s="17" t="n"/>
+    </row>
+    <row r="325" ht="22" customHeight="1">
+      <c r="A325" s="40" t="n"/>
+      <c r="B325" s="40" t="n"/>
+      <c r="C325" s="40" t="n"/>
+      <c r="D325" s="40" t="n"/>
+      <c r="E325" s="40" t="n"/>
+      <c r="F325" s="40" t="n"/>
+      <c r="G325" s="40" t="n"/>
+      <c r="H325" s="17" t="n"/>
+    </row>
+    <row r="326" ht="22" customHeight="1">
+      <c r="A326" s="40" t="n"/>
+      <c r="B326" s="40" t="n"/>
+      <c r="C326" s="40" t="n"/>
+      <c r="D326" s="40" t="n"/>
+      <c r="E326" s="40" t="n"/>
+      <c r="F326" s="40" t="n"/>
+      <c r="G326" s="40" t="n"/>
+      <c r="H326" s="17" t="n"/>
+    </row>
+    <row r="327" ht="22" customHeight="1">
+      <c r="A327" s="40" t="n"/>
+      <c r="B327" s="40" t="n"/>
+      <c r="C327" s="40" t="n"/>
+      <c r="D327" s="40" t="n"/>
+      <c r="E327" s="40" t="n"/>
+      <c r="F327" s="40" t="n"/>
+      <c r="G327" s="40" t="n"/>
+      <c r="H327" s="17" t="n"/>
+    </row>
+    <row r="328" ht="22" customHeight="1">
+      <c r="A328" s="40" t="n"/>
+      <c r="B328" s="40" t="n"/>
+      <c r="C328" s="40" t="n"/>
+      <c r="D328" s="40" t="n"/>
+      <c r="E328" s="40" t="n"/>
+      <c r="F328" s="40" t="n"/>
+      <c r="G328" s="40" t="n"/>
+      <c r="H328" s="17" t="n"/>
+    </row>
+    <row r="329" ht="22" customHeight="1">
+      <c r="A329" s="40" t="n"/>
+      <c r="B329" s="40" t="n"/>
+      <c r="C329" s="40" t="n"/>
+      <c r="D329" s="40" t="n"/>
+      <c r="E329" s="40" t="n"/>
+      <c r="F329" s="40" t="n"/>
+      <c r="G329" s="40" t="n"/>
+      <c r="H329" s="17" t="n"/>
+    </row>
+    <row r="330" ht="22" customHeight="1">
+      <c r="A330" s="40" t="n"/>
+      <c r="B330" s="40" t="n"/>
+      <c r="C330" s="40" t="n"/>
+      <c r="D330" s="40" t="n"/>
+      <c r="E330" s="40" t="n"/>
+      <c r="F330" s="40" t="n"/>
+      <c r="G330" s="40" t="n"/>
+      <c r="H330" s="17" t="n"/>
+    </row>
+    <row r="331" ht="22" customHeight="1">
+      <c r="A331" s="40" t="n"/>
+      <c r="B331" s="40" t="n"/>
+      <c r="C331" s="40" t="n"/>
+      <c r="D331" s="40" t="n"/>
+      <c r="E331" s="40" t="n"/>
+      <c r="F331" s="40" t="n"/>
+      <c r="G331" s="40" t="n"/>
+      <c r="H331" s="17" t="n"/>
+    </row>
+    <row r="332" ht="22" customHeight="1">
+      <c r="A332" s="40" t="n"/>
+      <c r="B332" s="40" t="n"/>
+      <c r="C332" s="40" t="n"/>
+      <c r="D332" s="40" t="n"/>
+      <c r="E332" s="40" t="n"/>
+      <c r="F332" s="40" t="n"/>
+      <c r="G332" s="40" t="n"/>
+      <c r="H332" s="17" t="n"/>
+    </row>
+    <row r="333" ht="22" customHeight="1">
+      <c r="A333" s="40" t="n"/>
+      <c r="B333" s="40" t="n"/>
+      <c r="C333" s="40" t="n"/>
+      <c r="D333" s="40" t="n"/>
+      <c r="E333" s="40" t="n"/>
+      <c r="F333" s="40" t="n"/>
+      <c r="G333" s="40" t="n"/>
+      <c r="H333" s="17" t="n"/>
+    </row>
+    <row r="334" ht="22" customHeight="1">
+      <c r="A334" s="40" t="n"/>
+      <c r="B334" s="40" t="n"/>
+      <c r="C334" s="40" t="n"/>
+      <c r="D334" s="40" t="n"/>
+      <c r="E334" s="40" t="n"/>
+      <c r="F334" s="40" t="n"/>
+      <c r="G334" s="40" t="n"/>
+      <c r="H334" s="17" t="n"/>
+    </row>
+    <row r="335" ht="22" customHeight="1">
+      <c r="A335" s="40" t="n"/>
+      <c r="B335" s="40" t="n"/>
+      <c r="C335" s="40" t="n"/>
+      <c r="D335" s="40" t="n"/>
+      <c r="E335" s="40" t="n"/>
+      <c r="F335" s="40" t="n"/>
+      <c r="G335" s="40" t="n"/>
+      <c r="H335" s="17" t="n"/>
+    </row>
+    <row r="336" ht="22" customHeight="1">
+      <c r="A336" s="40" t="n"/>
+      <c r="B336" s="40" t="n"/>
+      <c r="C336" s="40" t="n"/>
+      <c r="D336" s="40" t="n"/>
+      <c r="E336" s="40" t="n"/>
+      <c r="F336" s="40" t="n"/>
+      <c r="G336" s="40" t="n"/>
+      <c r="H336" s="17" t="n"/>
+    </row>
+    <row r="337" ht="22" customHeight="1">
+      <c r="A337" s="40" t="n"/>
+      <c r="B337" s="40" t="n"/>
+      <c r="C337" s="40" t="n"/>
+      <c r="D337" s="40" t="n"/>
+      <c r="E337" s="40" t="n"/>
+      <c r="F337" s="40" t="n"/>
+      <c r="G337" s="40" t="n"/>
+      <c r="H337" s="17" t="n"/>
+    </row>
+    <row r="338" ht="22" customHeight="1">
+      <c r="A338" s="40" t="n"/>
+      <c r="B338" s="40" t="n"/>
+      <c r="C338" s="40" t="n"/>
+      <c r="D338" s="40" t="n"/>
+      <c r="E338" s="40" t="n"/>
+      <c r="F338" s="40" t="n"/>
+      <c r="G338" s="40" t="n"/>
+      <c r="H338" s="17" t="n"/>
+    </row>
+    <row r="339" ht="22" customHeight="1">
+      <c r="A339" s="40" t="n"/>
+      <c r="B339" s="40" t="n"/>
+      <c r="C339" s="40" t="n"/>
+      <c r="D339" s="40" t="n"/>
+      <c r="E339" s="40" t="n"/>
+      <c r="F339" s="40" t="n"/>
+      <c r="G339" s="40" t="n"/>
+      <c r="H339" s="17" t="n"/>
+    </row>
+    <row r="340" ht="22" customHeight="1">
+      <c r="A340" s="40" t="n"/>
+      <c r="B340" s="40" t="n"/>
+      <c r="C340" s="40" t="n"/>
+      <c r="D340" s="40" t="n"/>
+      <c r="E340" s="40" t="n"/>
+      <c r="F340" s="40" t="n"/>
+      <c r="G340" s="40" t="n"/>
+      <c r="H340" s="17" t="n"/>
+    </row>
+    <row r="341" ht="22" customHeight="1">
+      <c r="A341" s="40" t="n"/>
+      <c r="B341" s="40" t="n"/>
+      <c r="C341" s="40" t="n"/>
+      <c r="D341" s="40" t="n"/>
+      <c r="E341" s="40" t="n"/>
+      <c r="F341" s="40" t="n"/>
+      <c r="G341" s="40" t="n"/>
+      <c r="H341" s="17" t="n"/>
+    </row>
+    <row r="342" ht="22" customHeight="1">
+      <c r="A342" s="40" t="n"/>
+      <c r="B342" s="40" t="n"/>
+      <c r="C342" s="40" t="n"/>
+      <c r="D342" s="40" t="n"/>
+      <c r="E342" s="40" t="n"/>
+      <c r="F342" s="40" t="n"/>
+      <c r="G342" s="40" t="n"/>
+      <c r="H342" s="17" t="n"/>
+    </row>
+    <row r="343" ht="22" customHeight="1">
+      <c r="A343" s="40" t="n"/>
+      <c r="B343" s="40" t="n"/>
+      <c r="C343" s="40" t="n"/>
+      <c r="D343" s="40" t="n"/>
+      <c r="E343" s="40" t="n"/>
+      <c r="F343" s="40" t="n"/>
+      <c r="G343" s="40" t="n"/>
+      <c r="H343" s="17" t="n"/>
+    </row>
+    <row r="344" ht="22" customHeight="1">
+      <c r="A344" s="40" t="n"/>
+      <c r="B344" s="40" t="n"/>
+      <c r="C344" s="40" t="n"/>
+      <c r="D344" s="40" t="n"/>
+      <c r="E344" s="40" t="n"/>
+      <c r="F344" s="40" t="n"/>
+      <c r="G344" s="40" t="n"/>
+      <c r="H344" s="17" t="n"/>
+    </row>
+    <row r="345" ht="22" customHeight="1">
+      <c r="A345" s="40" t="n"/>
+      <c r="B345" s="40" t="n"/>
+      <c r="C345" s="40" t="n"/>
+      <c r="D345" s="40" t="n"/>
+      <c r="E345" s="40" t="n"/>
+      <c r="F345" s="40" t="n"/>
+      <c r="G345" s="40" t="n"/>
+      <c r="H345" s="17" t="n"/>
+    </row>
+    <row r="346" ht="22" customHeight="1">
+      <c r="A346" s="40" t="n"/>
+      <c r="B346" s="40" t="n"/>
+      <c r="C346" s="40" t="n"/>
+      <c r="D346" s="40" t="n"/>
+      <c r="E346" s="40" t="n"/>
+      <c r="F346" s="40" t="n"/>
+      <c r="G346" s="40" t="n"/>
+      <c r="H346" s="17" t="n"/>
+    </row>
+    <row r="347" ht="22" customHeight="1">
+      <c r="A347" s="40" t="n"/>
+      <c r="B347" s="40" t="n"/>
+      <c r="C347" s="40" t="n"/>
+      <c r="D347" s="40" t="n"/>
+      <c r="E347" s="40" t="n"/>
+      <c r="F347" s="40" t="n"/>
+      <c r="G347" s="40" t="n"/>
+      <c r="H347" s="17" t="n"/>
+    </row>
+    <row r="348" ht="22" customHeight="1">
+      <c r="A348" s="40" t="n"/>
+      <c r="B348" s="40" t="n"/>
+      <c r="C348" s="40" t="n"/>
+      <c r="D348" s="40" t="n"/>
+      <c r="E348" s="40" t="n"/>
+      <c r="F348" s="40" t="n"/>
+      <c r="G348" s="40" t="n"/>
+      <c r="H348" s="17" t="n"/>
+    </row>
+    <row r="349" ht="22" customHeight="1">
+      <c r="A349" s="40" t="n"/>
+      <c r="B349" s="40" t="n"/>
+      <c r="C349" s="40" t="n"/>
+      <c r="D349" s="40" t="n"/>
+      <c r="E349" s="40" t="n"/>
+      <c r="F349" s="40" t="n"/>
+      <c r="G349" s="40" t="n"/>
+      <c r="H349" s="17" t="n"/>
+    </row>
+    <row r="350" ht="22" customHeight="1">
+      <c r="A350" s="40" t="n"/>
+      <c r="B350" s="40" t="n"/>
+      <c r="C350" s="40" t="n"/>
+      <c r="D350" s="40" t="n"/>
+      <c r="E350" s="40" t="n"/>
+      <c r="F350" s="40" t="n"/>
+      <c r="G350" s="40" t="n"/>
+      <c r="H350" s="17" t="n"/>
+    </row>
+    <row r="351" ht="22" customHeight="1">
+      <c r="A351" s="40" t="n"/>
+      <c r="B351" s="40" t="n"/>
+      <c r="C351" s="40" t="n"/>
+      <c r="D351" s="40" t="n"/>
+      <c r="E351" s="40" t="n"/>
+      <c r="F351" s="40" t="n"/>
+      <c r="G351" s="40" t="n"/>
+      <c r="H351" s="17" t="n"/>
+    </row>
+    <row r="352" ht="22" customHeight="1">
+      <c r="A352" s="40" t="n"/>
+      <c r="B352" s="40" t="n"/>
+      <c r="C352" s="40" t="n"/>
+      <c r="D352" s="40" t="n"/>
+      <c r="E352" s="40" t="n"/>
+      <c r="F352" s="40" t="n"/>
+      <c r="G352" s="40" t="n"/>
+      <c r="H352" s="17" t="n"/>
+    </row>
+    <row r="353" ht="22" customHeight="1">
+      <c r="A353" s="40" t="n"/>
+      <c r="B353" s="40" t="n"/>
+      <c r="C353" s="40" t="n"/>
+      <c r="D353" s="40" t="n"/>
+      <c r="E353" s="40" t="n"/>
+      <c r="F353" s="40" t="n"/>
+      <c r="G353" s="40" t="n"/>
+      <c r="H353" s="17" t="n"/>
+    </row>
+    <row r="354" ht="22" customHeight="1">
+      <c r="A354" s="40" t="n"/>
+      <c r="B354" s="40" t="n"/>
+      <c r="C354" s="40" t="n"/>
+      <c r="D354" s="40" t="n"/>
+      <c r="E354" s="40" t="n"/>
+      <c r="F354" s="40" t="n"/>
+      <c r="G354" s="40" t="n"/>
+      <c r="H354" s="17" t="n"/>
+    </row>
+    <row r="355" ht="22" customHeight="1">
+      <c r="A355" s="40" t="n"/>
+      <c r="B355" s="40" t="n"/>
+      <c r="C355" s="40" t="n"/>
+      <c r="D355" s="40" t="n"/>
+      <c r="E355" s="40" t="n"/>
+      <c r="F355" s="40" t="n"/>
+      <c r="G355" s="40" t="n"/>
+      <c r="H355" s="17" t="n"/>
+    </row>
+    <row r="356" ht="22" customHeight="1">
+      <c r="A356" s="40" t="n"/>
+      <c r="B356" s="40" t="n"/>
+      <c r="C356" s="40" t="n"/>
+      <c r="D356" s="40" t="n"/>
+      <c r="E356" s="40" t="n"/>
+      <c r="F356" s="40" t="n"/>
+      <c r="G356" s="40" t="n"/>
+      <c r="H356" s="17" t="n"/>
+    </row>
+    <row r="357" ht="22" customHeight="1">
+      <c r="A357" s="40" t="n"/>
+      <c r="B357" s="40" t="n"/>
+      <c r="C357" s="40" t="n"/>
+      <c r="D357" s="40" t="n"/>
+      <c r="E357" s="40" t="n"/>
+      <c r="F357" s="40" t="n"/>
+      <c r="G357" s="40" t="n"/>
+      <c r="H357" s="17" t="n"/>
+    </row>
+    <row r="358" ht="22" customHeight="1">
+      <c r="A358" s="40" t="n"/>
+      <c r="B358" s="40" t="n"/>
+      <c r="C358" s="40" t="n"/>
+      <c r="D358" s="40" t="n"/>
+      <c r="E358" s="40" t="n"/>
+      <c r="F358" s="40" t="n"/>
+      <c r="G358" s="40" t="n"/>
+      <c r="H358" s="17" t="n"/>
+    </row>
+    <row r="359" ht="22" customHeight="1">
+      <c r="A359" s="40" t="n"/>
+      <c r="B359" s="40" t="n"/>
+      <c r="C359" s="40" t="n"/>
+      <c r="D359" s="40" t="n"/>
+      <c r="E359" s="40" t="n"/>
+      <c r="F359" s="40" t="n"/>
+      <c r="G359" s="40" t="n"/>
+      <c r="H359" s="17" t="n"/>
+    </row>
+    <row r="360" ht="22" customHeight="1">
+      <c r="A360" s="40" t="n"/>
+      <c r="B360" s="40" t="n"/>
+      <c r="C360" s="40" t="n"/>
+      <c r="D360" s="40" t="n"/>
+      <c r="E360" s="40" t="n"/>
+      <c r="F360" s="40" t="n"/>
+      <c r="G360" s="40" t="n"/>
+      <c r="H360" s="17" t="n"/>
+    </row>
+    <row r="361" ht="22" customHeight="1">
+      <c r="A361" s="40" t="n"/>
+      <c r="B361" s="40" t="n"/>
+      <c r="C361" s="40" t="n"/>
+      <c r="D361" s="40" t="n"/>
+      <c r="E361" s="40" t="n"/>
+      <c r="F361" s="40" t="n"/>
+      <c r="G361" s="40" t="n"/>
+      <c r="H361" s="17" t="n"/>
+    </row>
+    <row r="362" ht="22" customHeight="1">
+      <c r="A362" s="40" t="n"/>
+      <c r="B362" s="40" t="n"/>
+      <c r="C362" s="40" t="n"/>
+      <c r="D362" s="40" t="n"/>
+      <c r="E362" s="40" t="n"/>
+      <c r="F362" s="40" t="n"/>
+      <c r="G362" s="40" t="n"/>
+      <c r="H362" s="17" t="n"/>
+    </row>
+    <row r="363" ht="22" customHeight="1">
+      <c r="A363" s="40" t="n"/>
+      <c r="B363" s="40" t="n"/>
+      <c r="C363" s="40" t="n"/>
+      <c r="D363" s="40" t="n"/>
+      <c r="E363" s="40" t="n"/>
+      <c r="F363" s="40" t="n"/>
+      <c r="G363" s="40" t="n"/>
+      <c r="H363" s="17" t="n"/>
+    </row>
+    <row r="364" ht="22" customHeight="1">
+      <c r="A364" s="40" t="n"/>
+      <c r="B364" s="40" t="n"/>
+      <c r="C364" s="40" t="n"/>
+      <c r="D364" s="40" t="n"/>
+      <c r="E364" s="40" t="n"/>
+      <c r="F364" s="40" t="n"/>
+      <c r="G364" s="40" t="n"/>
+      <c r="H364" s="17" t="n"/>
+    </row>
+    <row r="365" ht="22" customHeight="1">
+      <c r="A365" s="40" t="n"/>
+      <c r="B365" s="40" t="n"/>
+      <c r="C365" s="40" t="n"/>
+      <c r="D365" s="40" t="n"/>
+      <c r="E365" s="40" t="n"/>
+      <c r="F365" s="40" t="n"/>
+      <c r="G365" s="40" t="n"/>
+      <c r="H365" s="17" t="n"/>
+    </row>
+    <row r="366" ht="22" customHeight="1">
+      <c r="A366" s="40" t="n"/>
+      <c r="B366" s="40" t="n"/>
+      <c r="C366" s="40" t="n"/>
+      <c r="D366" s="40" t="n"/>
+      <c r="E366" s="40" t="n"/>
+      <c r="F366" s="40" t="n"/>
+      <c r="G366" s="40" t="n"/>
+      <c r="H366" s="17" t="n"/>
+    </row>
+    <row r="367" ht="22" customHeight="1">
+      <c r="A367" s="40" t="n"/>
+      <c r="B367" s="40" t="n"/>
+      <c r="C367" s="40" t="n"/>
+      <c r="D367" s="40" t="n"/>
+      <c r="E367" s="40" t="n"/>
+      <c r="F367" s="40" t="n"/>
+      <c r="G367" s="40" t="n"/>
+      <c r="H367" s="17" t="n"/>
+    </row>
+    <row r="368" ht="22" customHeight="1">
+      <c r="A368" s="40" t="n"/>
+      <c r="B368" s="40" t="n"/>
+      <c r="C368" s="40" t="n"/>
+      <c r="D368" s="40" t="n"/>
+      <c r="E368" s="40" t="n"/>
+      <c r="F368" s="40" t="n"/>
+      <c r="G368" s="40" t="n"/>
+      <c r="H368" s="17" t="n"/>
+    </row>
+    <row r="369" ht="22" customHeight="1">
+      <c r="A369" s="40" t="n"/>
+      <c r="B369" s="40" t="n"/>
+      <c r="C369" s="40" t="n"/>
+      <c r="D369" s="40" t="n"/>
+      <c r="E369" s="40" t="n"/>
+      <c r="F369" s="40" t="n"/>
+      <c r="G369" s="40" t="n"/>
+      <c r="H369" s="17" t="n"/>
+    </row>
+    <row r="370" ht="22" customHeight="1">
+      <c r="A370" s="40" t="n"/>
+      <c r="B370" s="40" t="n"/>
+      <c r="C370" s="40" t="n"/>
+      <c r="D370" s="40" t="n"/>
+      <c r="E370" s="40" t="n"/>
+      <c r="F370" s="40" t="n"/>
+      <c r="G370" s="40" t="n"/>
+      <c r="H370" s="17" t="n"/>
+    </row>
+    <row r="371" ht="22" customHeight="1">
+      <c r="A371" s="40" t="n"/>
+      <c r="B371" s="40" t="n"/>
+      <c r="C371" s="40" t="n"/>
+      <c r="D371" s="40" t="n"/>
+      <c r="E371" s="40" t="n"/>
+      <c r="F371" s="40" t="n"/>
+      <c r="G371" s="40" t="n"/>
+      <c r="H371" s="17" t="n"/>
+    </row>
+    <row r="372" ht="22" customHeight="1">
+      <c r="A372" s="40" t="n"/>
+      <c r="B372" s="40" t="n"/>
+      <c r="C372" s="40" t="n"/>
+      <c r="D372" s="40" t="n"/>
+      <c r="E372" s="40" t="n"/>
+      <c r="F372" s="40" t="n"/>
+      <c r="G372" s="40" t="n"/>
+      <c r="H372" s="17" t="n"/>
+    </row>
+    <row r="373" ht="22" customHeight="1">
+      <c r="A373" s="40" t="n"/>
+      <c r="B373" s="40" t="n"/>
+      <c r="C373" s="40" t="n"/>
+      <c r="D373" s="40" t="n"/>
+      <c r="E373" s="40" t="n"/>
+      <c r="F373" s="40" t="n"/>
+      <c r="G373" s="40" t="n"/>
+      <c r="H373" s="17" t="n"/>
+    </row>
+    <row r="374" ht="22" customHeight="1">
+      <c r="A374" s="40" t="n"/>
+      <c r="B374" s="40" t="n"/>
+      <c r="C374" s="40" t="n"/>
+      <c r="D374" s="40" t="n"/>
+      <c r="E374" s="40" t="n"/>
+      <c r="F374" s="40" t="n"/>
+      <c r="G374" s="40" t="n"/>
+      <c r="H374" s="17" t="n"/>
+    </row>
+    <row r="375" ht="22" customHeight="1">
+      <c r="A375" s="40" t="n"/>
+      <c r="B375" s="40" t="n"/>
+      <c r="C375" s="40" t="n"/>
+      <c r="D375" s="40" t="n"/>
+      <c r="E375" s="40" t="n"/>
+      <c r="F375" s="40" t="n"/>
+      <c r="G375" s="40" t="n"/>
+      <c r="H375" s="17" t="n"/>
+    </row>
+    <row r="376" ht="22" customHeight="1">
+      <c r="A376" s="40" t="n"/>
+      <c r="B376" s="40" t="n"/>
+      <c r="C376" s="40" t="n"/>
+      <c r="D376" s="40" t="n"/>
+      <c r="E376" s="40" t="n"/>
+      <c r="F376" s="40" t="n"/>
+      <c r="G376" s="40" t="n"/>
+      <c r="H376" s="17" t="n"/>
+    </row>
+    <row r="377" ht="22" customHeight="1">
+      <c r="A377" s="40" t="n"/>
+      <c r="B377" s="40" t="n"/>
+      <c r="C377" s="40" t="n"/>
+      <c r="D377" s="40" t="n"/>
+      <c r="E377" s="40" t="n"/>
+      <c r="F377" s="40" t="n"/>
+      <c r="G377" s="40" t="n"/>
+      <c r="H377" s="17" t="n"/>
+    </row>
+    <row r="378" ht="22" customHeight="1">
+      <c r="A378" s="40" t="n"/>
+      <c r="B378" s="40" t="n"/>
+      <c r="C378" s="40" t="n"/>
+      <c r="D378" s="40" t="n"/>
+      <c r="E378" s="40" t="n"/>
+      <c r="F378" s="40" t="n"/>
+      <c r="G378" s="40" t="n"/>
+      <c r="H378" s="17" t="n"/>
+    </row>
+    <row r="379" ht="22" customHeight="1">
+      <c r="A379" s="40" t="n"/>
+      <c r="B379" s="40" t="n"/>
+      <c r="C379" s="40" t="n"/>
+      <c r="D379" s="40" t="n"/>
+      <c r="E379" s="40" t="n"/>
+      <c r="F379" s="40" t="n"/>
+      <c r="G379" s="40" t="n"/>
+      <c r="H379" s="17" t="n"/>
+    </row>
+    <row r="380" ht="22" customHeight="1">
+      <c r="A380" s="40" t="n"/>
+      <c r="B380" s="40" t="n"/>
+      <c r="C380" s="40" t="n"/>
+      <c r="D380" s="40" t="n"/>
+      <c r="E380" s="40" t="n"/>
+      <c r="F380" s="40" t="n"/>
+      <c r="G380" s="40" t="n"/>
+      <c r="H380" s="17" t="n"/>
+    </row>
+    <row r="381" ht="22" customHeight="1">
+      <c r="A381" s="40" t="n"/>
+      <c r="B381" s="40" t="n"/>
+      <c r="C381" s="40" t="n"/>
+      <c r="D381" s="40" t="n"/>
+      <c r="E381" s="40" t="n"/>
+      <c r="F381" s="40" t="n"/>
+      <c r="G381" s="40" t="n"/>
+      <c r="H381" s="17" t="n"/>
+    </row>
+    <row r="382" ht="22" customHeight="1">
+      <c r="A382" s="40" t="n"/>
+      <c r="B382" s="40" t="n"/>
+      <c r="C382" s="40" t="n"/>
+      <c r="D382" s="40" t="n"/>
+      <c r="E382" s="40" t="n"/>
+      <c r="F382" s="40" t="n"/>
+      <c r="G382" s="40" t="n"/>
+      <c r="H382" s="17" t="n"/>
+    </row>
+    <row r="383" ht="22" customHeight="1">
+      <c r="A383" s="40" t="n"/>
+      <c r="B383" s="40" t="n"/>
+      <c r="C383" s="40" t="n"/>
+      <c r="D383" s="40" t="n"/>
+      <c r="E383" s="40" t="n"/>
+      <c r="F383" s="40" t="n"/>
+      <c r="G383" s="40" t="n"/>
+      <c r="H383" s="17" t="n"/>
+    </row>
+    <row r="384" ht="22" customHeight="1">
+      <c r="A384" s="40" t="n"/>
+      <c r="B384" s="40" t="n"/>
+      <c r="C384" s="40" t="n"/>
+      <c r="D384" s="40" t="n"/>
+      <c r="E384" s="40" t="n"/>
+      <c r="F384" s="40" t="n"/>
+      <c r="G384" s="40" t="n"/>
+      <c r="H384" s="17" t="n"/>
+    </row>
+    <row r="385" ht="22" customHeight="1">
+      <c r="A385" s="40" t="n"/>
+      <c r="B385" s="40" t="n"/>
+      <c r="C385" s="40" t="n"/>
+      <c r="D385" s="40" t="n"/>
+      <c r="E385" s="40" t="n"/>
+      <c r="F385" s="40" t="n"/>
+      <c r="G385" s="40" t="n"/>
+      <c r="H385" s="17" t="n"/>
+    </row>
+    <row r="386" ht="22" customHeight="1">
+      <c r="A386" s="40" t="n"/>
+      <c r="B386" s="40" t="n"/>
+      <c r="C386" s="40" t="n"/>
+      <c r="D386" s="40" t="n"/>
+      <c r="E386" s="40" t="n"/>
+      <c r="F386" s="40" t="n"/>
+      <c r="G386" s="40" t="n"/>
+      <c r="H386" s="17" t="n"/>
+    </row>
+    <row r="387" ht="22" customHeight="1">
+      <c r="A387" s="40" t="n"/>
+      <c r="B387" s="40" t="n"/>
+      <c r="C387" s="40" t="n"/>
+      <c r="D387" s="40" t="n"/>
+      <c r="E387" s="40" t="n"/>
+      <c r="F387" s="40" t="n"/>
+      <c r="G387" s="40" t="n"/>
+      <c r="H387" s="17" t="n"/>
+    </row>
+    <row r="388" ht="22" customHeight="1">
+      <c r="A388" s="40" t="n"/>
+      <c r="B388" s="40" t="n"/>
+      <c r="C388" s="40" t="n"/>
+      <c r="D388" s="40" t="n"/>
+      <c r="E388" s="40" t="n"/>
+      <c r="F388" s="40" t="n"/>
+      <c r="G388" s="40" t="n"/>
+      <c r="H388" s="17" t="n"/>
+    </row>
+    <row r="389" ht="22" customHeight="1">
+      <c r="A389" s="40" t="n"/>
+      <c r="B389" s="40" t="n"/>
+      <c r="C389" s="40" t="n"/>
+      <c r="D389" s="40" t="n"/>
+      <c r="E389" s="40" t="n"/>
+      <c r="F389" s="40" t="n"/>
+      <c r="G389" s="40" t="n"/>
+      <c r="H389" s="17" t="n"/>
+    </row>
+    <row r="390" ht="22" customHeight="1">
+      <c r="A390" s="40" t="n"/>
+      <c r="B390" s="40" t="n"/>
+      <c r="C390" s="40" t="n"/>
+      <c r="D390" s="40" t="n"/>
+      <c r="E390" s="40" t="n"/>
+      <c r="F390" s="40" t="n"/>
+      <c r="G390" s="40" t="n"/>
+      <c r="H390" s="17" t="n"/>
+    </row>
+    <row r="391" ht="22" customHeight="1">
+      <c r="A391" s="40" t="n"/>
+      <c r="B391" s="40" t="n"/>
+      <c r="C391" s="40" t="n"/>
+      <c r="D391" s="40" t="n"/>
+      <c r="E391" s="40" t="n"/>
+      <c r="F391" s="40" t="n"/>
+      <c r="G391" s="40" t="n"/>
+      <c r="H391" s="17" t="n"/>
+    </row>
+    <row r="392" ht="22" customHeight="1">
+      <c r="A392" s="40" t="n"/>
+      <c r="B392" s="40" t="n"/>
+      <c r="C392" s="40" t="n"/>
+      <c r="D392" s="40" t="n"/>
+      <c r="E392" s="40" t="n"/>
+      <c r="F392" s="40" t="n"/>
+      <c r="G392" s="40" t="n"/>
+      <c r="H392" s="17" t="n"/>
+    </row>
+    <row r="393" ht="22" customHeight="1">
+      <c r="A393" s="40" t="n"/>
+      <c r="B393" s="40" t="n"/>
+      <c r="C393" s="40" t="n"/>
+      <c r="D393" s="40" t="n"/>
+      <c r="E393" s="40" t="n"/>
+      <c r="F393" s="40" t="n"/>
+      <c r="G393" s="40" t="n"/>
+      <c r="H393" s="17" t="n"/>
+    </row>
+    <row r="394" ht="22" customHeight="1">
+      <c r="A394" s="40" t="n"/>
+      <c r="B394" s="40" t="n"/>
+      <c r="C394" s="40" t="n"/>
+      <c r="D394" s="40" t="n"/>
+      <c r="E394" s="40" t="n"/>
+      <c r="F394" s="40" t="n"/>
+      <c r="G394" s="40" t="n"/>
+      <c r="H394" s="17" t="n"/>
+    </row>
+    <row r="395" ht="22" customHeight="1">
+      <c r="A395" s="40" t="n"/>
+      <c r="B395" s="40" t="n"/>
+      <c r="C395" s="40" t="n"/>
+      <c r="D395" s="40" t="n"/>
+      <c r="E395" s="40" t="n"/>
+      <c r="F395" s="40" t="n"/>
+      <c r="G395" s="40" t="n"/>
+      <c r="H395" s="17" t="n"/>
+    </row>
+    <row r="396" ht="22" customHeight="1">
+      <c r="A396" s="40" t="n"/>
+      <c r="B396" s="40" t="n"/>
+      <c r="C396" s="40" t="n"/>
+      <c r="D396" s="40" t="n"/>
+      <c r="E396" s="40" t="n"/>
+      <c r="F396" s="40" t="n"/>
+      <c r="G396" s="40" t="n"/>
+      <c r="H396" s="17" t="n"/>
+    </row>
+    <row r="397" ht="22" customHeight="1">
+      <c r="A397" s="40" t="n"/>
+      <c r="B397" s="40" t="n"/>
+      <c r="C397" s="40" t="n"/>
+      <c r="D397" s="40" t="n"/>
+      <c r="E397" s="40" t="n"/>
+      <c r="F397" s="40" t="n"/>
+      <c r="G397" s="40" t="n"/>
+      <c r="H397" s="17" t="n"/>
+    </row>
+    <row r="398" ht="22" customHeight="1">
+      <c r="A398" s="40" t="n"/>
+      <c r="B398" s="40" t="n"/>
+      <c r="C398" s="40" t="n"/>
+      <c r="D398" s="40" t="n"/>
+      <c r="E398" s="40" t="n"/>
+      <c r="F398" s="40" t="n"/>
+      <c r="G398" s="40" t="n"/>
+      <c r="H398" s="17" t="n"/>
+    </row>
+    <row r="399" ht="22" customHeight="1">
+      <c r="A399" s="40" t="n"/>
+      <c r="B399" s="40" t="n"/>
+      <c r="C399" s="40" t="n"/>
+      <c r="D399" s="40" t="n"/>
+      <c r="E399" s="40" t="n"/>
+      <c r="F399" s="40" t="n"/>
+      <c r="G399" s="40" t="n"/>
+      <c r="H399" s="17" t="n"/>
+    </row>
+    <row r="400" ht="22" customHeight="1">
+      <c r="A400" s="40" t="n"/>
+      <c r="B400" s="40" t="n"/>
+      <c r="C400" s="40" t="n"/>
+      <c r="D400" s="40" t="n"/>
+      <c r="E400" s="40" t="n"/>
+      <c r="F400" s="40" t="n"/>
+      <c r="G400" s="40" t="n"/>
+      <c r="H400" s="17" t="n"/>
+    </row>
+    <row r="401" ht="22" customHeight="1">
+      <c r="A401" s="40" t="n"/>
+      <c r="B401" s="40" t="n"/>
+      <c r="C401" s="40" t="n"/>
+      <c r="D401" s="40" t="n"/>
+      <c r="E401" s="40" t="n"/>
+      <c r="F401" s="40" t="n"/>
+      <c r="G401" s="40" t="n"/>
+      <c r="H401" s="17" t="n"/>
+    </row>
+    <row r="402" ht="22" customHeight="1">
+      <c r="A402" s="40" t="n"/>
+      <c r="B402" s="40" t="n"/>
+      <c r="C402" s="40" t="n"/>
+      <c r="D402" s="40" t="n"/>
+      <c r="E402" s="40" t="n"/>
+      <c r="F402" s="40" t="n"/>
+      <c r="G402" s="40" t="n"/>
+      <c r="H402" s="17" t="n"/>
+    </row>
+    <row r="403" ht="22" customHeight="1">
+      <c r="A403" s="40" t="n"/>
+      <c r="B403" s="40" t="n"/>
+      <c r="C403" s="40" t="n"/>
+      <c r="D403" s="40" t="n"/>
+      <c r="E403" s="40" t="n"/>
+      <c r="F403" s="40" t="n"/>
+      <c r="G403" s="40" t="n"/>
+      <c r="H403" s="17" t="n"/>
+    </row>
+    <row r="404" ht="22" customHeight="1">
+      <c r="A404" s="40" t="n"/>
+      <c r="B404" s="40" t="n"/>
+      <c r="C404" s="40" t="n"/>
+      <c r="D404" s="40" t="n"/>
+      <c r="E404" s="40" t="n"/>
+      <c r="F404" s="40" t="n"/>
+      <c r="G404" s="40" t="n"/>
+      <c r="H404" s="17" t="n"/>
+    </row>
+    <row r="405" ht="22" customHeight="1">
+      <c r="A405" s="40" t="n"/>
+      <c r="B405" s="40" t="n"/>
+      <c r="C405" s="40" t="n"/>
+      <c r="D405" s="40" t="n"/>
+      <c r="E405" s="40" t="n"/>
+      <c r="F405" s="40" t="n"/>
+      <c r="G405" s="40" t="n"/>
+      <c r="H405" s="17" t="n"/>
+    </row>
+    <row r="406" ht="22" customHeight="1">
+      <c r="A406" s="40" t="n"/>
+      <c r="B406" s="40" t="n"/>
+      <c r="C406" s="40" t="n"/>
+      <c r="D406" s="40" t="n"/>
+      <c r="E406" s="40" t="n"/>
+      <c r="F406" s="40" t="n"/>
+      <c r="G406" s="40" t="n"/>
+      <c r="H406" s="17" t="n"/>
+    </row>
+    <row r="407" ht="22" customHeight="1">
+      <c r="A407" s="40" t="n"/>
+      <c r="B407" s="40" t="n"/>
+      <c r="C407" s="40" t="n"/>
+      <c r="D407" s="40" t="n"/>
+      <c r="E407" s="40" t="n"/>
+      <c r="F407" s="40" t="n"/>
+      <c r="G407" s="40" t="n"/>
+      <c r="H407" s="17" t="n"/>
+    </row>
+    <row r="408" ht="22" customHeight="1">
+      <c r="A408" s="40" t="n"/>
+      <c r="B408" s="40" t="n"/>
+      <c r="C408" s="40" t="n"/>
+      <c r="D408" s="40" t="n"/>
+      <c r="E408" s="40" t="n"/>
+      <c r="F408" s="40" t="n"/>
+      <c r="G408" s="40" t="n"/>
+      <c r="H408" s="17" t="n"/>
+    </row>
+    <row r="409" ht="22" customHeight="1">
+      <c r="A409" s="40" t="n"/>
+      <c r="B409" s="40" t="n"/>
+      <c r="C409" s="40" t="n"/>
+      <c r="D409" s="40" t="n"/>
+      <c r="E409" s="40" t="n"/>
+      <c r="F409" s="40" t="n"/>
+      <c r="G409" s="40" t="n"/>
+      <c r="H409" s="17" t="n"/>
+    </row>
+    <row r="410" ht="22" customHeight="1">
+      <c r="A410" s="40" t="n"/>
+      <c r="B410" s="40" t="n"/>
+      <c r="C410" s="40" t="n"/>
+      <c r="D410" s="40" t="n"/>
+      <c r="E410" s="40" t="n"/>
+      <c r="F410" s="40" t="n"/>
+      <c r="G410" s="40" t="n"/>
+      <c r="H410" s="17" t="n"/>
+    </row>
+    <row r="411" ht="22" customHeight="1">
+      <c r="A411" s="40" t="n"/>
+      <c r="B411" s="40" t="n"/>
+      <c r="C411" s="40" t="n"/>
+      <c r="D411" s="40" t="n"/>
+      <c r="E411" s="40" t="n"/>
+      <c r="F411" s="40" t="n"/>
+      <c r="G411" s="40" t="n"/>
+      <c r="H411" s="17" t="n"/>
+    </row>
+    <row r="412" ht="22" customHeight="1">
+      <c r="A412" s="40" t="n"/>
+      <c r="B412" s="40" t="n"/>
+      <c r="C412" s="40" t="n"/>
+      <c r="D412" s="40" t="n"/>
+      <c r="E412" s="40" t="n"/>
+      <c r="F412" s="40" t="n"/>
+      <c r="G412" s="40" t="n"/>
+      <c r="H412" s="17" t="n"/>
+    </row>
+    <row r="413" ht="22" customHeight="1">
+      <c r="A413" s="40" t="n"/>
+      <c r="B413" s="40" t="n"/>
+      <c r="C413" s="40" t="n"/>
+      <c r="D413" s="40" t="n"/>
+      <c r="E413" s="40" t="n"/>
+      <c r="F413" s="40" t="n"/>
+      <c r="G413" s="40" t="n"/>
+      <c r="H413" s="17" t="n"/>
+    </row>
+    <row r="414" ht="22" customHeight="1">
+      <c r="A414" s="40" t="n"/>
+      <c r="B414" s="40" t="n"/>
+      <c r="C414" s="40" t="n"/>
+      <c r="D414" s="40" t="n"/>
+      <c r="E414" s="40" t="n"/>
+      <c r="F414" s="40" t="n"/>
+      <c r="G414" s="40" t="n"/>
+      <c r="H414" s="17" t="n"/>
+    </row>
+    <row r="415" ht="22" customHeight="1">
+      <c r="A415" s="40" t="n"/>
+      <c r="B415" s="40" t="n"/>
+      <c r="C415" s="40" t="n"/>
+      <c r="D415" s="40" t="n"/>
+      <c r="E415" s="40" t="n"/>
+      <c r="F415" s="40" t="n"/>
+      <c r="G415" s="40" t="n"/>
+      <c r="H415" s="17" t="n"/>
+    </row>
+    <row r="416" ht="22" customHeight="1">
+      <c r="A416" s="40" t="n"/>
+      <c r="B416" s="40" t="n"/>
+      <c r="C416" s="40" t="n"/>
+      <c r="D416" s="40" t="n"/>
+      <c r="E416" s="40" t="n"/>
+      <c r="F416" s="40" t="n"/>
+      <c r="G416" s="40" t="n"/>
+      <c r="H416" s="17" t="n"/>
+    </row>
+    <row r="417" ht="22" customHeight="1">
+      <c r="A417" s="40" t="n"/>
+      <c r="B417" s="40" t="n"/>
+      <c r="C417" s="40" t="n"/>
+      <c r="D417" s="40" t="n"/>
+      <c r="E417" s="40" t="n"/>
+      <c r="F417" s="40" t="n"/>
+      <c r="G417" s="40" t="n"/>
+      <c r="H417" s="17" t="n"/>
+    </row>
+    <row r="418" ht="22" customHeight="1">
+      <c r="A418" s="40" t="n"/>
+      <c r="B418" s="40" t="n"/>
+      <c r="C418" s="40" t="n"/>
+      <c r="D418" s="40" t="n"/>
+      <c r="E418" s="40" t="n"/>
+      <c r="F418" s="40" t="n"/>
+      <c r="G418" s="40" t="n"/>
+      <c r="H418" s="17" t="n"/>
+    </row>
+    <row r="419" ht="22" customHeight="1">
+      <c r="A419" s="40" t="n"/>
+      <c r="B419" s="40" t="n"/>
+      <c r="C419" s="40" t="n"/>
+      <c r="D419" s="40" t="n"/>
+      <c r="E419" s="40" t="n"/>
+      <c r="F419" s="40" t="n"/>
+      <c r="G419" s="40" t="n"/>
+      <c r="H419" s="17" t="n"/>
+    </row>
+    <row r="420" ht="22" customHeight="1">
+      <c r="A420" s="40" t="n"/>
+      <c r="B420" s="40" t="n"/>
+      <c r="C420" s="40" t="n"/>
+      <c r="D420" s="40" t="n"/>
+      <c r="E420" s="40" t="n"/>
+      <c r="F420" s="40" t="n"/>
+      <c r="G420" s="40" t="n"/>
+      <c r="H420" s="17" t="n"/>
+    </row>
+    <row r="421" ht="22" customHeight="1">
+      <c r="A421" s="40" t="n"/>
+      <c r="B421" s="40" t="n"/>
+      <c r="C421" s="40" t="n"/>
+      <c r="D421" s="40" t="n"/>
+      <c r="E421" s="40" t="n"/>
+      <c r="F421" s="40" t="n"/>
+      <c r="G421" s="40" t="n"/>
+      <c r="H421" s="17" t="n"/>
+    </row>
+    <row r="422" ht="22" customHeight="1">
+      <c r="A422" s="40" t="n"/>
+      <c r="B422" s="40" t="n"/>
+      <c r="C422" s="40" t="n"/>
+      <c r="D422" s="40" t="n"/>
+      <c r="E422" s="40" t="n"/>
+      <c r="F422" s="40" t="n"/>
+      <c r="G422" s="40" t="n"/>
+      <c r="H422" s="17" t="n"/>
+    </row>
+    <row r="423" ht="22" customHeight="1">
+      <c r="A423" s="40" t="n"/>
+      <c r="B423" s="40" t="n"/>
+      <c r="C423" s="40" t="n"/>
+      <c r="D423" s="40" t="n"/>
+      <c r="E423" s="40" t="n"/>
+      <c r="F423" s="40" t="n"/>
+      <c r="G423" s="40" t="n"/>
+      <c r="H423" s="17" t="n"/>
+    </row>
+    <row r="424" ht="22" customHeight="1">
+      <c r="A424" s="40" t="n"/>
+      <c r="B424" s="40" t="n"/>
+      <c r="C424" s="40" t="n"/>
+      <c r="D424" s="40" t="n"/>
+      <c r="E424" s="40" t="n"/>
+      <c r="F424" s="40" t="n"/>
+      <c r="G424" s="40" t="n"/>
+      <c r="H424" s="17" t="n"/>
+    </row>
+    <row r="425" ht="22" customHeight="1">
+      <c r="A425" s="40" t="n"/>
+      <c r="B425" s="40" t="n"/>
+      <c r="C425" s="40" t="n"/>
+      <c r="D425" s="40" t="n"/>
+      <c r="E425" s="40" t="n"/>
+      <c r="F425" s="40" t="n"/>
+      <c r="G425" s="40" t="n"/>
+      <c r="H425" s="17" t="n"/>
+    </row>
+    <row r="426" ht="22" customHeight="1">
+      <c r="A426" s="40" t="n"/>
+      <c r="B426" s="40" t="n"/>
+      <c r="C426" s="40" t="n"/>
+      <c r="D426" s="40" t="n"/>
+      <c r="E426" s="40" t="n"/>
+      <c r="F426" s="40" t="n"/>
+      <c r="G426" s="40" t="n"/>
+      <c r="H426" s="17" t="n"/>
+    </row>
+    <row r="427" ht="22" customHeight="1">
+      <c r="A427" s="40" t="n"/>
+      <c r="B427" s="40" t="n"/>
+      <c r="C427" s="40" t="n"/>
+      <c r="D427" s="40" t="n"/>
+      <c r="E427" s="40" t="n"/>
+      <c r="F427" s="40" t="n"/>
+      <c r="G427" s="40" t="n"/>
+      <c r="H427" s="17" t="n"/>
+    </row>
+    <row r="428" ht="22" customHeight="1">
+      <c r="A428" s="40" t="n"/>
+      <c r="B428" s="40" t="n"/>
+      <c r="C428" s="40" t="n"/>
+      <c r="D428" s="40" t="n"/>
+      <c r="E428" s="40" t="n"/>
+      <c r="F428" s="40" t="n"/>
+      <c r="G428" s="40" t="n"/>
+      <c r="H428" s="17" t="n"/>
+    </row>
+    <row r="429" ht="22" customHeight="1">
+      <c r="A429" s="40" t="n"/>
+      <c r="B429" s="40" t="n"/>
+      <c r="C429" s="40" t="n"/>
+      <c r="D429" s="40" t="n"/>
+      <c r="E429" s="40" t="n"/>
+      <c r="F429" s="40" t="n"/>
+      <c r="G429" s="40" t="n"/>
+      <c r="H429" s="17" t="n"/>
+    </row>
+    <row r="430" ht="22" customHeight="1">
+      <c r="A430" s="40" t="n"/>
+      <c r="B430" s="40" t="n"/>
+      <c r="C430" s="40" t="n"/>
+      <c r="D430" s="40" t="n"/>
+      <c r="E430" s="40" t="n"/>
+      <c r="F430" s="40" t="n"/>
+      <c r="G430" s="40" t="n"/>
+      <c r="H430" s="17" t="n"/>
+    </row>
+    <row r="431" ht="22" customHeight="1">
+      <c r="A431" s="40" t="n"/>
+      <c r="B431" s="40" t="n"/>
+      <c r="C431" s="40" t="n"/>
+      <c r="D431" s="40" t="n"/>
+      <c r="E431" s="40" t="n"/>
+      <c r="F431" s="40" t="n"/>
+      <c r="G431" s="40" t="n"/>
+      <c r="H431" s="17" t="n"/>
+    </row>
+    <row r="432" ht="22" customHeight="1">
+      <c r="A432" s="40" t="n"/>
+      <c r="B432" s="40" t="n"/>
+      <c r="C432" s="40" t="n"/>
+      <c r="D432" s="40" t="n"/>
+      <c r="E432" s="40" t="n"/>
+      <c r="F432" s="40" t="n"/>
+      <c r="G432" s="40" t="n"/>
+      <c r="H432" s="17" t="n"/>
+    </row>
+    <row r="433" ht="22" customHeight="1">
+      <c r="A433" s="40" t="n"/>
+      <c r="B433" s="40" t="n"/>
+      <c r="C433" s="40" t="n"/>
+      <c r="D433" s="40" t="n"/>
+      <c r="E433" s="40" t="n"/>
+      <c r="F433" s="40" t="n"/>
+      <c r="G433" s="40" t="n"/>
+      <c r="H433" s="17" t="n"/>
+    </row>
+    <row r="434" ht="22" customHeight="1">
+      <c r="A434" s="40" t="n"/>
+      <c r="B434" s="40" t="n"/>
+      <c r="C434" s="40" t="n"/>
+      <c r="D434" s="40" t="n"/>
+      <c r="E434" s="40" t="n"/>
+      <c r="F434" s="40" t="n"/>
+      <c r="G434" s="40" t="n"/>
+      <c r="H434" s="17" t="n"/>
+    </row>
+    <row r="435" ht="22" customHeight="1">
+      <c r="A435" s="40" t="n"/>
+      <c r="B435" s="40" t="n"/>
+      <c r="C435" s="40" t="n"/>
+      <c r="D435" s="40" t="n"/>
+      <c r="E435" s="40" t="n"/>
+      <c r="F435" s="40" t="n"/>
+      <c r="G435" s="40" t="n"/>
+      <c r="H435" s="17" t="n"/>
+    </row>
+    <row r="436" ht="22" customHeight="1">
+      <c r="A436" s="40" t="n"/>
+      <c r="B436" s="40" t="n"/>
+      <c r="C436" s="40" t="n"/>
+      <c r="D436" s="40" t="n"/>
+      <c r="E436" s="40" t="n"/>
+      <c r="F436" s="40" t="n"/>
+      <c r="G436" s="40" t="n"/>
+      <c r="H436" s="17" t="n"/>
+    </row>
+    <row r="437" ht="22" customHeight="1">
+      <c r="A437" s="40" t="n"/>
+      <c r="B437" s="40" t="n"/>
+      <c r="C437" s="40" t="n"/>
+      <c r="D437" s="40" t="n"/>
+      <c r="E437" s="40" t="n"/>
+      <c r="F437" s="40" t="n"/>
+      <c r="G437" s="40" t="n"/>
+      <c r="H437" s="17" t="n"/>
+    </row>
+    <row r="438" ht="22" customHeight="1">
+      <c r="A438" s="40" t="n"/>
+      <c r="B438" s="40" t="n"/>
+      <c r="C438" s="40" t="n"/>
+      <c r="D438" s="40" t="n"/>
+      <c r="E438" s="40" t="n"/>
+      <c r="F438" s="40" t="n"/>
+      <c r="G438" s="40" t="n"/>
+      <c r="H438" s="17" t="n"/>
+    </row>
+    <row r="439" ht="22" customHeight="1">
+      <c r="A439" s="40" t="n"/>
+      <c r="B439" s="40" t="n"/>
+      <c r="C439" s="40" t="n"/>
+      <c r="D439" s="40" t="n"/>
+      <c r="E439" s="40" t="n"/>
+      <c r="F439" s="40" t="n"/>
+      <c r="G439" s="40" t="n"/>
+      <c r="H439" s="17" t="n"/>
+    </row>
+    <row r="440" ht="22" customHeight="1">
+      <c r="A440" s="40" t="n"/>
+      <c r="B440" s="40" t="n"/>
+      <c r="C440" s="40" t="n"/>
+      <c r="D440" s="40" t="n"/>
+      <c r="E440" s="40" t="n"/>
+      <c r="F440" s="40" t="n"/>
+      <c r="G440" s="40" t="n"/>
+      <c r="H440" s="17" t="n"/>
+    </row>
+    <row r="441" ht="22" customHeight="1">
+      <c r="A441" s="40" t="n"/>
+      <c r="B441" s="40" t="n"/>
+      <c r="C441" s="40" t="n"/>
+      <c r="D441" s="40" t="n"/>
+      <c r="E441" s="40" t="n"/>
+      <c r="F441" s="40" t="n"/>
+      <c r="G441" s="40" t="n"/>
+      <c r="H441" s="17" t="n"/>
+    </row>
+    <row r="442" ht="22" customHeight="1">
+      <c r="A442" s="40" t="n"/>
+      <c r="B442" s="40" t="n"/>
+      <c r="C442" s="40" t="n"/>
+      <c r="D442" s="40" t="n"/>
+      <c r="E442" s="40" t="n"/>
+      <c r="F442" s="40" t="n"/>
+      <c r="G442" s="40" t="n"/>
+      <c r="H442" s="17" t="n"/>
+    </row>
+    <row r="443" ht="22" customHeight="1">
+      <c r="A443" s="40" t="n"/>
+      <c r="B443" s="40" t="n"/>
+      <c r="C443" s="40" t="n"/>
+      <c r="D443" s="40" t="n"/>
+      <c r="E443" s="40" t="n"/>
+      <c r="F443" s="40" t="n"/>
+      <c r="G443" s="40" t="n"/>
+      <c r="H443" s="17" t="n"/>
+    </row>
+    <row r="444" ht="22" customHeight="1">
+      <c r="A444" s="40" t="n"/>
+      <c r="B444" s="40" t="n"/>
+      <c r="C444" s="40" t="n"/>
+      <c r="D444" s="40" t="n"/>
+      <c r="E444" s="40" t="n"/>
+      <c r="F444" s="40" t="n"/>
+      <c r="G444" s="40" t="n"/>
+      <c r="H444" s="17" t="n"/>
+    </row>
+    <row r="445" ht="22" customHeight="1">
+      <c r="A445" s="40" t="n"/>
+      <c r="B445" s="40" t="n"/>
+      <c r="C445" s="40" t="n"/>
+      <c r="D445" s="40" t="n"/>
+      <c r="E445" s="40" t="n"/>
+      <c r="F445" s="40" t="n"/>
+      <c r="G445" s="40" t="n"/>
+      <c r="H445" s="17" t="n"/>
+    </row>
+    <row r="446" ht="22" customHeight="1">
+      <c r="A446" s="40" t="n"/>
+      <c r="B446" s="40" t="n"/>
+      <c r="C446" s="40" t="n"/>
+      <c r="D446" s="40" t="n"/>
+      <c r="E446" s="40" t="n"/>
+      <c r="F446" s="40" t="n"/>
+      <c r="G446" s="40" t="n"/>
+      <c r="H446" s="17" t="n"/>
+    </row>
+    <row r="447" ht="22" customHeight="1">
+      <c r="A447" s="40" t="n"/>
+      <c r="B447" s="40" t="n"/>
+      <c r="C447" s="40" t="n"/>
+      <c r="D447" s="40" t="n"/>
+      <c r="E447" s="40" t="n"/>
+      <c r="F447" s="40" t="n"/>
+      <c r="G447" s="40" t="n"/>
+      <c r="H447" s="17" t="n"/>
+    </row>
+    <row r="448" ht="22" customHeight="1">
+      <c r="A448" s="40" t="n"/>
+      <c r="B448" s="40" t="n"/>
+      <c r="C448" s="40" t="n"/>
+      <c r="D448" s="40" t="n"/>
+      <c r="E448" s="40" t="n"/>
+      <c r="F448" s="40" t="n"/>
+      <c r="G448" s="40" t="n"/>
+      <c r="H448" s="17" t="n"/>
+    </row>
+    <row r="449" ht="22" customHeight="1">
+      <c r="A449" s="40" t="n"/>
+      <c r="B449" s="40" t="n"/>
+      <c r="C449" s="40" t="n"/>
+      <c r="D449" s="40" t="n"/>
+      <c r="E449" s="40" t="n"/>
+      <c r="F449" s="40" t="n"/>
+      <c r="G449" s="40" t="n"/>
+      <c r="H449" s="17" t="n"/>
+    </row>
+    <row r="450" ht="22" customHeight="1">
+      <c r="A450" s="40" t="n"/>
+      <c r="B450" s="40" t="n"/>
+      <c r="C450" s="40" t="n"/>
+      <c r="D450" s="40" t="n"/>
+      <c r="E450" s="40" t="n"/>
+      <c r="F450" s="40" t="n"/>
+      <c r="G450" s="40" t="n"/>
+      <c r="H450" s="17" t="n"/>
+    </row>
+    <row r="451" ht="22" customHeight="1">
+      <c r="A451" s="40" t="n"/>
+      <c r="B451" s="40" t="n"/>
+      <c r="C451" s="40" t="n"/>
+      <c r="D451" s="40" t="n"/>
+      <c r="E451" s="40" t="n"/>
+      <c r="F451" s="40" t="n"/>
+      <c r="G451" s="40" t="n"/>
+      <c r="H451" s="17" t="n"/>
+    </row>
+    <row r="452" ht="22" customHeight="1">
+      <c r="A452" s="40" t="n"/>
+      <c r="B452" s="40" t="n"/>
+      <c r="C452" s="40" t="n"/>
+      <c r="D452" s="40" t="n"/>
+      <c r="E452" s="40" t="n"/>
+      <c r="F452" s="40" t="n"/>
+      <c r="G452" s="40" t="n"/>
+      <c r="H452" s="17" t="n"/>
+    </row>
+    <row r="453" ht="22" customHeight="1">
+      <c r="A453" s="40" t="n"/>
+      <c r="B453" s="40" t="n"/>
+      <c r="C453" s="40" t="n"/>
+      <c r="D453" s="40" t="n"/>
+      <c r="E453" s="40" t="n"/>
+      <c r="F453" s="40" t="n"/>
+      <c r="G453" s="40" t="n"/>
+      <c r="H453" s="17" t="n"/>
+    </row>
+    <row r="454" ht="22" customHeight="1">
+      <c r="A454" s="40" t="n"/>
+      <c r="B454" s="40" t="n"/>
+      <c r="C454" s="40" t="n"/>
+      <c r="D454" s="40" t="n"/>
+      <c r="E454" s="40" t="n"/>
+      <c r="F454" s="40" t="n"/>
+      <c r="G454" s="40" t="n"/>
+      <c r="H454" s="17" t="n"/>
+    </row>
+    <row r="455" ht="22" customHeight="1">
+      <c r="A455" s="40" t="n"/>
+      <c r="B455" s="40" t="n"/>
+      <c r="C455" s="40" t="n"/>
+      <c r="D455" s="40" t="n"/>
+      <c r="E455" s="40" t="n"/>
+      <c r="F455" s="40" t="n"/>
+      <c r="G455" s="40" t="n"/>
+      <c r="H455" s="17" t="n"/>
+    </row>
+    <row r="456" ht="22" customHeight="1">
+      <c r="A456" s="40" t="n"/>
+      <c r="B456" s="40" t="n"/>
+      <c r="C456" s="40" t="n"/>
+      <c r="D456" s="40" t="n"/>
+      <c r="E456" s="40" t="n"/>
+      <c r="F456" s="40" t="n"/>
+      <c r="G456" s="40" t="n"/>
+      <c r="H456" s="17" t="n"/>
+    </row>
+    <row r="457" ht="22" customHeight="1">
+      <c r="A457" s="40" t="n"/>
+      <c r="B457" s="40" t="n"/>
+      <c r="C457" s="40" t="n"/>
+      <c r="D457" s="40" t="n"/>
+      <c r="E457" s="40" t="n"/>
+      <c r="F457" s="40" t="n"/>
+      <c r="G457" s="40" t="n"/>
+      <c r="H457" s="17" t="n"/>
+    </row>
+    <row r="458" ht="22" customHeight="1">
+      <c r="A458" s="40" t="n"/>
+      <c r="B458" s="40" t="n"/>
+      <c r="C458" s="40" t="n"/>
+      <c r="D458" s="40" t="n"/>
+      <c r="E458" s="40" t="n"/>
+      <c r="F458" s="40" t="n"/>
+      <c r="G458" s="40" t="n"/>
+      <c r="H458" s="17" t="n"/>
+    </row>
+    <row r="459" ht="22" customHeight="1">
+      <c r="A459" s="40" t="n"/>
+      <c r="B459" s="40" t="n"/>
+      <c r="C459" s="40" t="n"/>
+      <c r="D459" s="40" t="n"/>
+      <c r="E459" s="40" t="n"/>
+      <c r="F459" s="40" t="n"/>
+      <c r="G459" s="40" t="n"/>
+      <c r="H459" s="17" t="n"/>
+    </row>
+    <row r="460" ht="22" customHeight="1">
+      <c r="A460" s="40" t="n"/>
+      <c r="B460" s="40" t="n"/>
+      <c r="C460" s="40" t="n"/>
+      <c r="D460" s="40" t="n"/>
+      <c r="E460" s="40" t="n"/>
+      <c r="F460" s="40" t="n"/>
+      <c r="G460" s="40" t="n"/>
+      <c r="H460" s="17" t="n"/>
+    </row>
+    <row r="461" ht="22" customHeight="1">
+      <c r="A461" s="40" t="n"/>
+      <c r="B461" s="40" t="n"/>
+      <c r="C461" s="40" t="n"/>
+      <c r="D461" s="40" t="n"/>
+      <c r="E461" s="40" t="n"/>
+      <c r="F461" s="40" t="n"/>
+      <c r="G461" s="40" t="n"/>
+      <c r="H461" s="17" t="n"/>
+    </row>
+    <row r="462" ht="22" customHeight="1">
+      <c r="A462" s="40" t="n"/>
+      <c r="B462" s="40" t="n"/>
+      <c r="C462" s="40" t="n"/>
+      <c r="D462" s="40" t="n"/>
+      <c r="E462" s="40" t="n"/>
+      <c r="F462" s="40" t="n"/>
+      <c r="G462" s="40" t="n"/>
+      <c r="H462" s="17" t="n"/>
+    </row>
+    <row r="463" ht="22" customHeight="1">
+      <c r="A463" s="40" t="n"/>
+      <c r="B463" s="40" t="n"/>
+      <c r="C463" s="40" t="n"/>
+      <c r="D463" s="40" t="n"/>
+      <c r="E463" s="40" t="n"/>
+      <c r="F463" s="40" t="n"/>
+      <c r="G463" s="40" t="n"/>
+      <c r="H463" s="17" t="n"/>
+    </row>
+    <row r="464" ht="22" customHeight="1">
+      <c r="A464" s="40" t="n"/>
+      <c r="B464" s="40" t="n"/>
+      <c r="C464" s="40" t="n"/>
+      <c r="D464" s="40" t="n"/>
+      <c r="E464" s="40" t="n"/>
+      <c r="F464" s="40" t="n"/>
+      <c r="G464" s="40" t="n"/>
+      <c r="H464" s="17" t="n"/>
+    </row>
+    <row r="465" ht="22" customHeight="1">
+      <c r="A465" s="40" t="n"/>
+      <c r="B465" s="40" t="n"/>
+      <c r="C465" s="40" t="n"/>
+      <c r="D465" s="40" t="n"/>
+      <c r="E465" s="40" t="n"/>
+      <c r="F465" s="40" t="n"/>
+      <c r="G465" s="40" t="n"/>
+      <c r="H465" s="17" t="n"/>
+    </row>
+    <row r="466" ht="22" customHeight="1">
+      <c r="A466" s="40" t="n"/>
+      <c r="B466" s="40" t="n"/>
+      <c r="C466" s="40" t="n"/>
+      <c r="D466" s="40" t="n"/>
+      <c r="E466" s="40" t="n"/>
+      <c r="F466" s="40" t="n"/>
+      <c r="G466" s="40" t="n"/>
+      <c r="H466" s="17" t="n"/>
+    </row>
+    <row r="467" ht="22" customHeight="1">
+      <c r="A467" s="40" t="n"/>
+      <c r="B467" s="40" t="n"/>
+      <c r="C467" s="40" t="n"/>
+      <c r="D467" s="40" t="n"/>
+      <c r="E467" s="40" t="n"/>
+      <c r="F467" s="40" t="n"/>
+      <c r="G467" s="40" t="n"/>
+      <c r="H467" s="17" t="n"/>
+    </row>
+    <row r="468" ht="22" customHeight="1">
+      <c r="A468" s="40" t="n"/>
+      <c r="B468" s="40" t="n"/>
+      <c r="C468" s="40" t="n"/>
+      <c r="D468" s="40" t="n"/>
+      <c r="E468" s="40" t="n"/>
+      <c r="F468" s="40" t="n"/>
+      <c r="G468" s="40" t="n"/>
+      <c r="H468" s="17" t="n"/>
+    </row>
+    <row r="469" ht="22" customHeight="1">
+      <c r="A469" s="40" t="n"/>
+      <c r="B469" s="40" t="n"/>
+      <c r="C469" s="40" t="n"/>
+      <c r="D469" s="40" t="n"/>
+      <c r="E469" s="40" t="n"/>
+      <c r="F469" s="40" t="n"/>
+      <c r="G469" s="40" t="n"/>
+      <c r="H469" s="17" t="n"/>
+    </row>
+    <row r="470" ht="22" customHeight="1">
+      <c r="A470" s="40" t="n"/>
+      <c r="B470" s="40" t="n"/>
+      <c r="C470" s="40" t="n"/>
+      <c r="D470" s="40" t="n"/>
+      <c r="E470" s="40" t="n"/>
+      <c r="F470" s="40" t="n"/>
+      <c r="G470" s="40" t="n"/>
+      <c r="H470" s="17" t="n"/>
+    </row>
+    <row r="471" ht="22" customHeight="1">
+      <c r="A471" s="40" t="n"/>
+      <c r="B471" s="40" t="n"/>
+      <c r="C471" s="40" t="n"/>
+      <c r="D471" s="40" t="n"/>
+      <c r="E471" s="40" t="n"/>
+      <c r="F471" s="40" t="n"/>
+      <c r="G471" s="40" t="n"/>
+      <c r="H471" s="17" t="n"/>
+    </row>
+    <row r="472" ht="22" customHeight="1">
+      <c r="A472" s="40" t="n"/>
+      <c r="B472" s="40" t="n"/>
+      <c r="C472" s="40" t="n"/>
+      <c r="D472" s="40" t="n"/>
+      <c r="E472" s="40" t="n"/>
+      <c r="F472" s="40" t="n"/>
+      <c r="G472" s="40" t="n"/>
+      <c r="H472" s="17" t="n"/>
+    </row>
+    <row r="473" ht="22" customHeight="1">
+      <c r="A473" s="40" t="n"/>
+      <c r="B473" s="40" t="n"/>
+      <c r="C473" s="40" t="n"/>
+      <c r="D473" s="40" t="n"/>
+      <c r="E473" s="40" t="n"/>
+      <c r="F473" s="40" t="n"/>
+      <c r="G473" s="40" t="n"/>
+      <c r="H473" s="17" t="n"/>
+    </row>
+    <row r="474" ht="22" customHeight="1">
+      <c r="A474" s="40" t="n"/>
+      <c r="B474" s="40" t="n"/>
+      <c r="C474" s="40" t="n"/>
+      <c r="D474" s="40" t="n"/>
+      <c r="E474" s="40" t="n"/>
+      <c r="F474" s="40" t="n"/>
+      <c r="G474" s="40" t="n"/>
+      <c r="H474" s="17" t="n"/>
+    </row>
+    <row r="475" ht="22" customHeight="1">
+      <c r="A475" s="40" t="n"/>
+      <c r="B475" s="40" t="n"/>
+      <c r="C475" s="40" t="n"/>
+      <c r="D475" s="40" t="n"/>
+      <c r="E475" s="40" t="n"/>
+      <c r="F475" s="40" t="n"/>
+      <c r="G475" s="40" t="n"/>
+      <c r="H475" s="17" t="n"/>
+    </row>
+    <row r="476" ht="22" customHeight="1">
+      <c r="A476" s="40" t="n"/>
+      <c r="B476" s="40" t="n"/>
+      <c r="C476" s="40" t="n"/>
+      <c r="D476" s="40" t="n"/>
+      <c r="E476" s="40" t="n"/>
+      <c r="F476" s="40" t="n"/>
+      <c r="G476" s="40" t="n"/>
+      <c r="H476" s="17" t="n"/>
+    </row>
+    <row r="477" ht="22" customHeight="1">
+      <c r="A477" s="40" t="n"/>
+      <c r="B477" s="40" t="n"/>
+      <c r="C477" s="40" t="n"/>
+      <c r="D477" s="40" t="n"/>
+      <c r="E477" s="40" t="n"/>
+      <c r="F477" s="40" t="n"/>
+      <c r="G477" s="40" t="n"/>
+      <c r="H477" s="17" t="n"/>
+    </row>
+    <row r="478" ht="22" customHeight="1">
+      <c r="A478" s="40" t="n"/>
+      <c r="B478" s="40" t="n"/>
+      <c r="C478" s="40" t="n"/>
+      <c r="D478" s="40" t="n"/>
+      <c r="E478" s="40" t="n"/>
+      <c r="F478" s="40" t="n"/>
+      <c r="G478" s="40" t="n"/>
+      <c r="H478" s="17" t="n"/>
+    </row>
+    <row r="479" ht="22" customHeight="1">
+      <c r="A479" s="40" t="n"/>
+      <c r="B479" s="40" t="n"/>
+      <c r="C479" s="40" t="n"/>
+      <c r="D479" s="40" t="n"/>
+      <c r="E479" s="40" t="n"/>
+      <c r="F479" s="40" t="n"/>
+      <c r="G479" s="40" t="n"/>
+      <c r="H479" s="17" t="n"/>
+    </row>
+    <row r="480" ht="22" customHeight="1">
+      <c r="A480" s="40" t="n"/>
+      <c r="B480" s="40" t="n"/>
+      <c r="C480" s="40" t="n"/>
+      <c r="D480" s="40" t="n"/>
+      <c r="E480" s="40" t="n"/>
+      <c r="F480" s="40" t="n"/>
+      <c r="G480" s="40" t="n"/>
+      <c r="H480" s="17" t="n"/>
+    </row>
+    <row r="481" ht="22" customHeight="1">
+      <c r="A481" s="40" t="n"/>
+      <c r="B481" s="40" t="n"/>
+      <c r="C481" s="40" t="n"/>
+      <c r="D481" s="40" t="n"/>
+      <c r="E481" s="40" t="n"/>
+      <c r="F481" s="40" t="n"/>
+      <c r="G481" s="40" t="n"/>
+      <c r="H481" s="17" t="n"/>
+    </row>
+    <row r="482" ht="22" customHeight="1">
+      <c r="A482" s="40" t="n"/>
+      <c r="B482" s="40" t="n"/>
+      <c r="C482" s="40" t="n"/>
+      <c r="D482" s="40" t="n"/>
+      <c r="E482" s="40" t="n"/>
+      <c r="F482" s="40" t="n"/>
+      <c r="G482" s="40" t="n"/>
+      <c r="H482" s="17" t="n"/>
+    </row>
+    <row r="483" ht="22" customHeight="1">
+      <c r="A483" s="40" t="n"/>
+      <c r="B483" s="40" t="n"/>
+      <c r="C483" s="40" t="n"/>
+      <c r="D483" s="40" t="n"/>
+      <c r="E483" s="40" t="n"/>
+      <c r="F483" s="40" t="n"/>
+      <c r="G483" s="40" t="n"/>
+      <c r="H483" s="17" t="n"/>
+    </row>
+    <row r="484" ht="22" customHeight="1">
+      <c r="A484" s="40" t="n"/>
+      <c r="B484" s="40" t="n"/>
+      <c r="C484" s="40" t="n"/>
+      <c r="D484" s="40" t="n"/>
+      <c r="E484" s="40" t="n"/>
+      <c r="F484" s="40" t="n"/>
+      <c r="G484" s="40" t="n"/>
+      <c r="H484" s="17" t="n"/>
+    </row>
+    <row r="485" ht="22" customHeight="1">
+      <c r="A485" s="40" t="n"/>
+      <c r="B485" s="40" t="n"/>
+      <c r="C485" s="40" t="n"/>
+      <c r="D485" s="40" t="n"/>
+      <c r="E485" s="40" t="n"/>
+      <c r="F485" s="40" t="n"/>
+      <c r="G485" s="40" t="n"/>
+      <c r="H485" s="17" t="n"/>
+    </row>
+    <row r="486" ht="22" customHeight="1">
+      <c r="A486" s="40" t="n"/>
+      <c r="B486" s="40" t="n"/>
+      <c r="C486" s="40" t="n"/>
+      <c r="D486" s="40" t="n"/>
+      <c r="E486" s="40" t="n"/>
+      <c r="F486" s="40" t="n"/>
+      <c r="G486" s="40" t="n"/>
+      <c r="H486" s="17" t="n"/>
+    </row>
+    <row r="487" ht="22" customHeight="1">
+      <c r="A487" s="40" t="n"/>
+      <c r="B487" s="40" t="n"/>
+      <c r="C487" s="40" t="n"/>
+      <c r="D487" s="40" t="n"/>
+      <c r="E487" s="40" t="n"/>
+      <c r="F487" s="40" t="n"/>
+      <c r="G487" s="40" t="n"/>
+      <c r="H487" s="17" t="n"/>
+    </row>
+    <row r="488" ht="22" customHeight="1">
+      <c r="A488" s="40" t="n"/>
+      <c r="B488" s="40" t="n"/>
+      <c r="C488" s="40" t="n"/>
+      <c r="D488" s="40" t="n"/>
+      <c r="E488" s="40" t="n"/>
+      <c r="F488" s="40" t="n"/>
+      <c r="G488" s="40" t="n"/>
+      <c r="H488" s="17" t="n"/>
+    </row>
+    <row r="489" ht="22" customHeight="1">
+      <c r="A489" s="40" t="n"/>
+      <c r="B489" s="40" t="n"/>
+      <c r="C489" s="40" t="n"/>
+      <c r="D489" s="40" t="n"/>
+      <c r="E489" s="40" t="n"/>
+      <c r="F489" s="40" t="n"/>
+      <c r="G489" s="40" t="n"/>
+      <c r="H489" s="17" t="n"/>
+    </row>
+    <row r="490" ht="22" customHeight="1">
+      <c r="A490" s="40" t="n"/>
+      <c r="B490" s="40" t="n"/>
+      <c r="C490" s="40" t="n"/>
+      <c r="D490" s="40" t="n"/>
+      <c r="E490" s="40" t="n"/>
+      <c r="F490" s="40" t="n"/>
+      <c r="G490" s="40" t="n"/>
+      <c r="H490" s="17" t="n"/>
+    </row>
+    <row r="491" ht="22" customHeight="1">
+      <c r="A491" s="40" t="n"/>
+      <c r="B491" s="40" t="n"/>
+      <c r="C491" s="40" t="n"/>
+      <c r="D491" s="40" t="n"/>
+      <c r="E491" s="40" t="n"/>
+      <c r="F491" s="40" t="n"/>
+      <c r="G491" s="40" t="n"/>
+      <c r="H491" s="17" t="n"/>
+    </row>
+    <row r="492" ht="22" customHeight="1">
+      <c r="A492" s="40" t="n"/>
+      <c r="B492" s="40" t="n"/>
+      <c r="C492" s="40" t="n"/>
+      <c r="D492" s="40" t="n"/>
+      <c r="E492" s="40" t="n"/>
+      <c r="F492" s="40" t="n"/>
+      <c r="G492" s="40" t="n"/>
+      <c r="H492" s="17" t="n"/>
+    </row>
+    <row r="493" ht="22" customHeight="1">
+      <c r="A493" s="40" t="n"/>
+      <c r="B493" s="40" t="n"/>
+      <c r="C493" s="40" t="n"/>
+      <c r="D493" s="40" t="n"/>
+      <c r="E493" s="40" t="n"/>
+      <c r="F493" s="40" t="n"/>
+      <c r="G493" s="40" t="n"/>
+      <c r="H493" s="17" t="n"/>
+    </row>
+    <row r="494" ht="22" customHeight="1">
+      <c r="A494" s="40" t="n"/>
+      <c r="B494" s="40" t="n"/>
+      <c r="C494" s="40" t="n"/>
+      <c r="D494" s="40" t="n"/>
+      <c r="E494" s="40" t="n"/>
+      <c r="F494" s="40" t="n"/>
+      <c r="G494" s="40" t="n"/>
+      <c r="H494" s="17" t="n"/>
+    </row>
+    <row r="495" ht="22" customHeight="1">
+      <c r="A495" s="40" t="n"/>
+      <c r="B495" s="40" t="n"/>
+      <c r="C495" s="40" t="n"/>
+      <c r="D495" s="40" t="n"/>
+      <c r="E495" s="40" t="n"/>
+      <c r="F495" s="40" t="n"/>
+      <c r="G495" s="40" t="n"/>
+      <c r="H495" s="17" t="n"/>
+    </row>
+    <row r="496" ht="22" customHeight="1">
+      <c r="A496" s="40" t="n"/>
+      <c r="B496" s="40" t="n"/>
+      <c r="C496" s="40" t="n"/>
+      <c r="D496" s="40" t="n"/>
+      <c r="E496" s="40" t="n"/>
+      <c r="F496" s="40" t="n"/>
+      <c r="G496" s="40" t="n"/>
+      <c r="H496" s="17" t="n"/>
+    </row>
+    <row r="497" ht="22" customHeight="1">
+      <c r="A497" s="40" t="n"/>
+      <c r="B497" s="40" t="n"/>
+      <c r="C497" s="40" t="n"/>
+      <c r="D497" s="40" t="n"/>
+      <c r="E497" s="40" t="n"/>
+      <c r="F497" s="40" t="n"/>
+      <c r="G497" s="40" t="n"/>
+      <c r="H497" s="17" t="n"/>
+    </row>
+    <row r="498" ht="22" customHeight="1">
+      <c r="A498" s="40" t="n"/>
+      <c r="B498" s="40" t="n"/>
+      <c r="C498" s="40" t="n"/>
+      <c r="D498" s="40" t="n"/>
+      <c r="E498" s="40" t="n"/>
+      <c r="F498" s="40" t="n"/>
+      <c r="G498" s="40" t="n"/>
+      <c r="H498" s="17" t="n"/>
+    </row>
+    <row r="499" ht="22" customHeight="1">
+      <c r="A499" s="40" t="n"/>
+      <c r="B499" s="40" t="n"/>
+      <c r="C499" s="40" t="n"/>
+      <c r="D499" s="40" t="n"/>
+      <c r="E499" s="40" t="n"/>
+      <c r="F499" s="40" t="n"/>
+      <c r="G499" s="40" t="n"/>
+      <c r="H499" s="17" t="n"/>
+    </row>
+    <row r="500" ht="22" customHeight="1">
+      <c r="A500" s="40" t="n"/>
+      <c r="B500" s="40" t="n"/>
+      <c r="C500" s="40" t="n"/>
+      <c r="D500" s="40" t="n"/>
+      <c r="E500" s="40" t="n"/>
+      <c r="F500" s="40" t="n"/>
+      <c r="G500" s="40" t="n"/>
+      <c r="H500" s="17" t="n"/>
+    </row>
+    <row r="501" ht="22" customHeight="1">
+      <c r="A501" s="40" t="n"/>
+      <c r="B501" s="40" t="n"/>
+      <c r="C501" s="40" t="n"/>
+      <c r="D501" s="40" t="n"/>
+      <c r="E501" s="40" t="n"/>
+      <c r="F501" s="40" t="n"/>
+      <c r="G501" s="40" t="n"/>
+      <c r="H501" s="17" t="n"/>
+    </row>
+    <row r="502" ht="22" customHeight="1">
+      <c r="A502" s="40" t="n"/>
+      <c r="B502" s="40" t="n"/>
+      <c r="C502" s="40" t="n"/>
+      <c r="D502" s="40" t="n"/>
+      <c r="E502" s="40" t="n"/>
+      <c r="F502" s="40" t="n"/>
+      <c r="G502" s="40" t="n"/>
+      <c r="H502" s="17" t="n"/>
+    </row>
+    <row r="503" ht="22" customHeight="1">
+      <c r="A503" s="40" t="n"/>
+      <c r="B503" s="40" t="n"/>
+      <c r="C503" s="40" t="n"/>
+      <c r="D503" s="40" t="n"/>
+      <c r="E503" s="40" t="n"/>
+      <c r="F503" s="40" t="n"/>
+      <c r="G503" s="40" t="n"/>
+      <c r="H503" s="17" t="n"/>
+    </row>
+    <row r="504" ht="22" customHeight="1">
+      <c r="A504" s="40" t="n"/>
+      <c r="B504" s="40" t="n"/>
+      <c r="C504" s="40" t="n"/>
+      <c r="D504" s="40" t="n"/>
+      <c r="E504" s="40" t="n"/>
+      <c r="F504" s="40" t="n"/>
+      <c r="G504" s="40" t="n"/>
+      <c r="H504" s="17" t="n"/>
+    </row>
+    <row r="505" ht="22" customHeight="1">
+      <c r="A505" s="40" t="n"/>
+      <c r="B505" s="40" t="n"/>
+      <c r="C505" s="40" t="n"/>
+      <c r="D505" s="40" t="n"/>
+      <c r="E505" s="40" t="n"/>
+      <c r="F505" s="40" t="n"/>
+      <c r="G505" s="40" t="n"/>
+      <c r="H505" s="17" t="n"/>
+    </row>
+    <row r="506" ht="22" customHeight="1">
+      <c r="A506" s="40" t="n"/>
+      <c r="B506" s="40" t="n"/>
+      <c r="C506" s="40" t="n"/>
+      <c r="D506" s="40" t="n"/>
+      <c r="E506" s="40" t="n"/>
+      <c r="F506" s="40" t="n"/>
+      <c r="G506" s="40" t="n"/>
+      <c r="H506" s="17" t="n"/>
+    </row>
+    <row r="507" ht="22" customHeight="1">
+      <c r="A507" s="40" t="n"/>
+      <c r="B507" s="40" t="n"/>
+      <c r="C507" s="40" t="n"/>
+      <c r="D507" s="40" t="n"/>
+      <c r="E507" s="40" t="n"/>
+      <c r="F507" s="40" t="n"/>
+      <c r="G507" s="40" t="n"/>
+      <c r="H507" s="17" t="n"/>
+    </row>
+    <row r="508" ht="22" customHeight="1">
+      <c r="A508" s="40" t="n"/>
+      <c r="B508" s="40" t="n"/>
+      <c r="C508" s="40" t="n"/>
+      <c r="D508" s="40" t="n"/>
+      <c r="E508" s="40" t="n"/>
+      <c r="F508" s="40" t="n"/>
+      <c r="G508" s="40" t="n"/>
+      <c r="H508" s="17" t="n"/>
+    </row>
+    <row r="509" ht="22" customHeight="1">
+      <c r="A509" s="40" t="n"/>
+      <c r="B509" s="40" t="n"/>
+      <c r="C509" s="40" t="n"/>
+      <c r="D509" s="40" t="n"/>
+      <c r="E509" s="40" t="n"/>
+      <c r="F509" s="40" t="n"/>
+      <c r="G509" s="40" t="n"/>
+      <c r="H509" s="17" t="n"/>
+    </row>
+    <row r="510" ht="22" customHeight="1">
+      <c r="A510" s="40" t="n"/>
+      <c r="B510" s="40" t="n"/>
+      <c r="C510" s="40" t="n"/>
+      <c r="D510" s="40" t="n"/>
+      <c r="E510" s="40" t="n"/>
+      <c r="F510" s="40" t="n"/>
+      <c r="G510" s="40" t="n"/>
+      <c r="H510" s="17" t="n"/>
+    </row>
+    <row r="511" ht="22" customHeight="1">
+      <c r="A511" s="40" t="n"/>
+      <c r="B511" s="40" t="n"/>
+      <c r="C511" s="40" t="n"/>
+      <c r="D511" s="40" t="n"/>
+      <c r="E511" s="40" t="n"/>
+      <c r="F511" s="40" t="n"/>
+      <c r="G511" s="40" t="n"/>
+      <c r="H511" s="17" t="n"/>
+    </row>
+    <row r="512" ht="22" customHeight="1">
+      <c r="A512" s="40" t="n"/>
+      <c r="B512" s="40" t="n"/>
+      <c r="C512" s="40" t="n"/>
+      <c r="D512" s="40" t="n"/>
+      <c r="E512" s="40" t="n"/>
+      <c r="F512" s="40" t="n"/>
+      <c r="G512" s="40" t="n"/>
+      <c r="H512" s="17" t="n"/>
+    </row>
+    <row r="513" ht="22" customHeight="1">
+      <c r="A513" s="40" t="n"/>
+      <c r="B513" s="40" t="n"/>
+      <c r="C513" s="40" t="n"/>
+      <c r="D513" s="40" t="n"/>
+      <c r="E513" s="40" t="n"/>
+      <c r="F513" s="40" t="n"/>
+      <c r="G513" s="40" t="n"/>
+      <c r="H513" s="17" t="n"/>
+    </row>
+    <row r="514" ht="22" customHeight="1">
+      <c r="A514" s="40" t="n"/>
+      <c r="B514" s="40" t="n"/>
+      <c r="C514" s="40" t="n"/>
+      <c r="D514" s="40" t="n"/>
+      <c r="E514" s="40" t="n"/>
+      <c r="F514" s="40" t="n"/>
+      <c r="G514" s="40" t="n"/>
+      <c r="H514" s="17" t="n"/>
+    </row>
+    <row r="515" ht="22" customHeight="1">
+      <c r="A515" s="40" t="n"/>
+      <c r="B515" s="40" t="n"/>
+      <c r="C515" s="40" t="n"/>
+      <c r="D515" s="40" t="n"/>
+      <c r="E515" s="40" t="n"/>
+      <c r="F515" s="40" t="n"/>
+      <c r="G515" s="40" t="n"/>
+      <c r="H515" s="17" t="n"/>
+    </row>
+    <row r="516" ht="22" customHeight="1">
+      <c r="A516" s="40" t="n"/>
+      <c r="B516" s="40" t="n"/>
+      <c r="C516" s="40" t="n"/>
+      <c r="D516" s="40" t="n"/>
+      <c r="E516" s="40" t="n"/>
+      <c r="F516" s="40" t="n"/>
+      <c r="G516" s="40" t="n"/>
+      <c r="H516" s="17" t="n"/>
+    </row>
+    <row r="517" ht="22" customHeight="1">
+      <c r="A517" s="40" t="n"/>
+      <c r="B517" s="40" t="n"/>
+      <c r="C517" s="40" t="n"/>
+      <c r="D517" s="40" t="n"/>
+      <c r="E517" s="40" t="n"/>
+      <c r="F517" s="40" t="n"/>
+      <c r="G517" s="40" t="n"/>
+      <c r="H517" s="17" t="n"/>
+    </row>
+    <row r="518" ht="22" customHeight="1">
+      <c r="A518" s="42" t="inlineStr">
         <is>
           <t>备注：正式数据必须来自同一份已冻结 reviewed_result。</t>
         </is>
       </c>
-      <c r="B70" s="19" t="n"/>
-      <c r="C70" s="19" t="n"/>
-      <c r="D70" s="19" t="n"/>
-      <c r="E70" s="19" t="n"/>
-      <c r="F70" s="19" t="n"/>
-      <c r="G70" s="19" t="n"/>
-      <c r="H70" s="19" t="n"/>
-    </row>
-    <row r="71" ht="26" customHeight="1">
-      <c r="A71" s="43" t="inlineStr">
+      <c r="B518" s="19" t="n"/>
+      <c r="C518" s="19" t="n"/>
+      <c r="D518" s="19" t="n"/>
+      <c r="E518" s="19" t="n"/>
+      <c r="F518" s="19" t="n"/>
+      <c r="G518" s="19" t="n"/>
+      <c r="H518" s="19" t="n"/>
+    </row>
+    <row r="519" ht="26" customHeight="1">
+      <c r="A519" s="43" t="inlineStr">
         <is>
           <t>最终判定</t>
         </is>
       </c>
-      <c r="B71" s="44" t="n"/>
-      <c r="C71" s="43" t="inlineStr">
+      <c r="B519" s="20" t="n"/>
+      <c r="C519" s="43" t="inlineStr">
         <is>
           <t>确认</t>
         </is>
       </c>
-      <c r="D71" s="44" t="n"/>
-      <c r="E71" s="43" t="inlineStr">
+      <c r="D519" s="20" t="n"/>
+      <c r="E519" s="43" t="inlineStr">
         <is>
           <t>是否同意量产</t>
         </is>
       </c>
-      <c r="F71" s="44" t="n"/>
-      <c r="G71" s="43" t="inlineStr">
+      <c r="F519" s="20" t="n"/>
+      <c r="G519" s="43" t="inlineStr">
         <is>
           <t>核准</t>
         </is>
       </c>
-      <c r="H71" s="44" t="n"/>
-    </row>
-    <row r="72" ht="24" customHeight="1">
-      <c r="A72" s="45" t="inlineStr">
+      <c r="H519" s="20" t="n"/>
+    </row>
+    <row r="520" ht="24" customHeight="1">
+      <c r="A520" s="45" t="inlineStr">
         <is>
           <t>结果</t>
         </is>
       </c>
-      <c r="B72" s="46" t="n"/>
-      <c r="C72" s="45" t="inlineStr">
+      <c r="B520" s="20" t="n"/>
+      <c r="C520" s="45" t="inlineStr">
         <is>
           <t>检验员</t>
         </is>
       </c>
-      <c r="D72" s="38" t="n"/>
-      <c r="E72" s="38" t="inlineStr">
+      <c r="D520" s="38" t="n"/>
+      <c r="E520" s="38" t="inlineStr">
         <is>
           <t>□是    □否</t>
         </is>
       </c>
-      <c r="F72" s="47" t="n"/>
-      <c r="G72" s="45" t="inlineStr">
+      <c r="F520" s="21" t="n"/>
+      <c r="G520" s="45" t="inlineStr">
         <is>
           <t>工程技术</t>
         </is>
       </c>
-      <c r="H72" s="38" t="n"/>
-    </row>
-    <row r="73" ht="24" customHeight="1">
-      <c r="A73" s="38" t="inlineStr">
+      <c r="H520" s="38" t="n"/>
+    </row>
+    <row r="521" ht="24" customHeight="1">
+      <c r="A521" s="38" t="inlineStr">
         <is>
           <t>□合格    □不合格</t>
         </is>
       </c>
-      <c r="B73" s="47" t="n"/>
-      <c r="C73" s="45" t="inlineStr">
+      <c r="B521" s="21" t="n"/>
+      <c r="C521" s="45" t="inlineStr">
         <is>
           <t>生产确认</t>
         </is>
       </c>
-      <c r="D73" s="38" t="n"/>
-      <c r="E73" s="48" t="n"/>
-      <c r="F73" s="49" t="n"/>
-      <c r="G73" s="45" t="inlineStr">
+      <c r="D521" s="38" t="n"/>
+      <c r="E521" s="22" t="n"/>
+      <c r="F521" s="23" t="n"/>
+      <c r="G521" s="45" t="inlineStr">
         <is>
           <t>品质核准</t>
         </is>
       </c>
-      <c r="H73" s="38" t="n"/>
-    </row>
-    <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="50" t="n"/>
-      <c r="B74" s="51" t="n"/>
-      <c r="C74" s="52" t="n"/>
-      <c r="D74" s="53" t="n"/>
-      <c r="E74" s="50" t="n"/>
-      <c r="F74" s="51" t="n"/>
-      <c r="G74" s="52" t="n"/>
-      <c r="H74" s="53" t="n"/>
+      <c r="H521" s="38" t="n"/>
+    </row>
+    <row r="522" ht="24" customHeight="1">
+      <c r="A522" s="24" t="n"/>
+      <c r="B522" s="25" t="n"/>
+      <c r="C522" s="26" t="n"/>
+      <c r="D522" s="27" t="n"/>
+      <c r="E522" s="24" t="n"/>
+      <c r="F522" s="25" t="n"/>
+      <c r="G522" s="26" t="n"/>
+      <c r="H522" s="27" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <autoFilter ref="A5:H69"/>
-  <mergeCells count="82">
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="E71:F71"/>
+  <mergeCells count="530">
     <mergeCell ref="G71:H71"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="G307:H307"/>
+    <mergeCell ref="G371:H371"/>
+    <mergeCell ref="G358:H358"/>
     <mergeCell ref="G66:H66"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G137:H137"/>
+    <mergeCell ref="G229:H229"/>
+    <mergeCell ref="G422:H422"/>
+    <mergeCell ref="G360:H360"/>
+    <mergeCell ref="G148:H148"/>
     <mergeCell ref="G68:H68"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D73:D74"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="G335:H335"/>
+    <mergeCell ref="G139:H139"/>
+    <mergeCell ref="G489:H489"/>
+    <mergeCell ref="G427:H427"/>
+    <mergeCell ref="G114:H114"/>
+    <mergeCell ref="G206:H206"/>
+    <mergeCell ref="G399:H399"/>
+    <mergeCell ref="G168:H168"/>
+    <mergeCell ref="G491:H491"/>
+    <mergeCell ref="G143:H143"/>
+    <mergeCell ref="G213:H213"/>
+    <mergeCell ref="G270:H270"/>
+    <mergeCell ref="G506:H506"/>
+    <mergeCell ref="G351:H351"/>
+    <mergeCell ref="G513:H513"/>
     <mergeCell ref="G59:H59"/>
-    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G117:H117"/>
     <mergeCell ref="G67:H67"/>
     <mergeCell ref="G61:H61"/>
+    <mergeCell ref="G425:H425"/>
+    <mergeCell ref="G359:H359"/>
     <mergeCell ref="G48:H48"/>
+    <mergeCell ref="G219:H219"/>
+    <mergeCell ref="G346:H346"/>
+    <mergeCell ref="G517:H517"/>
+    <mergeCell ref="G417:H417"/>
+    <mergeCell ref="G125:H125"/>
+    <mergeCell ref="G112:H112"/>
+    <mergeCell ref="G283:H283"/>
+    <mergeCell ref="G348:H348"/>
+    <mergeCell ref="G519:H519"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="G127:H127"/>
+    <mergeCell ref="G298:H298"/>
+    <mergeCell ref="G285:H285"/>
+    <mergeCell ref="G412:H412"/>
+    <mergeCell ref="G201:H201"/>
+    <mergeCell ref="G250:H250"/>
+    <mergeCell ref="G372:H372"/>
+    <mergeCell ref="G443:H443"/>
+    <mergeCell ref="G453:H453"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G138:H138"/>
+    <mergeCell ref="G76:H76"/>
+    <mergeCell ref="G380:H380"/>
+    <mergeCell ref="G203:H203"/>
+    <mergeCell ref="G374:H374"/>
+    <mergeCell ref="G230:H230"/>
+    <mergeCell ref="G301:H301"/>
+    <mergeCell ref="G361:H361"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G140:H140"/>
+    <mergeCell ref="G438:H438"/>
+    <mergeCell ref="G238:H238"/>
+    <mergeCell ref="G232:H232"/>
+    <mergeCell ref="G303:H303"/>
+    <mergeCell ref="G474:H474"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G440:H440"/>
+    <mergeCell ref="G296:H296"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="G367:H367"/>
+    <mergeCell ref="G87:H87"/>
+    <mergeCell ref="G354:H354"/>
+    <mergeCell ref="G329:H329"/>
+    <mergeCell ref="G133:H133"/>
+    <mergeCell ref="G369:H369"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="G418:H418"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="G356:H356"/>
+    <mergeCell ref="G393:H393"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="G368:H368"/>
+    <mergeCell ref="G135:H135"/>
+    <mergeCell ref="G306:H306"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G433:H433"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="G349:H349"/>
+    <mergeCell ref="G153:H153"/>
+    <mergeCell ref="G420:H420"/>
+    <mergeCell ref="G226:H226"/>
+    <mergeCell ref="G364:H364"/>
+    <mergeCell ref="G164:H164"/>
+    <mergeCell ref="G217:H217"/>
+    <mergeCell ref="G251:H251"/>
+    <mergeCell ref="G382:H382"/>
+    <mergeCell ref="A520:B520"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="G253:H253"/>
+    <mergeCell ref="G446:H446"/>
+    <mergeCell ref="G240:H240"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G190:H190"/>
+    <mergeCell ref="G146:H146"/>
+    <mergeCell ref="G317:H317"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G304:H304"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="G254:H254"/>
+    <mergeCell ref="G248:H248"/>
+    <mergeCell ref="G515:H515"/>
+    <mergeCell ref="G319:H319"/>
+    <mergeCell ref="G490:H490"/>
+    <mergeCell ref="G235:H235"/>
+    <mergeCell ref="G477:H477"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G159:H159"/>
+    <mergeCell ref="G395:H395"/>
+    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="G370:H370"/>
+    <mergeCell ref="G161:H161"/>
+    <mergeCell ref="G459:H459"/>
+    <mergeCell ref="G136:H136"/>
+    <mergeCell ref="G434:H434"/>
+    <mergeCell ref="G228:H228"/>
+    <mergeCell ref="G470:H470"/>
+    <mergeCell ref="G461:H461"/>
+    <mergeCell ref="G436:H436"/>
+    <mergeCell ref="G292:H292"/>
+    <mergeCell ref="G267:H267"/>
+    <mergeCell ref="G373:H373"/>
+    <mergeCell ref="G294:H294"/>
+    <mergeCell ref="G465:H465"/>
+    <mergeCell ref="G108:H108"/>
+    <mergeCell ref="G231:H231"/>
+    <mergeCell ref="G325:H325"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G91:H91"/>
+    <mergeCell ref="G318:H318"/>
+    <mergeCell ref="G85:H85"/>
+    <mergeCell ref="G256:H256"/>
+    <mergeCell ref="G389:H389"/>
+    <mergeCell ref="G383:H383"/>
+    <mergeCell ref="G183:H183"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G193:H193"/>
+    <mergeCell ref="G149:H149"/>
+    <mergeCell ref="G198:H198"/>
+    <mergeCell ref="G320:H320"/>
+    <mergeCell ref="G247:H247"/>
+    <mergeCell ref="G385:H385"/>
+    <mergeCell ref="G185:H185"/>
+    <mergeCell ref="G483:H483"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="G257:H257"/>
+    <mergeCell ref="G151:H151"/>
+    <mergeCell ref="G178:H178"/>
+    <mergeCell ref="G449:H449"/>
+    <mergeCell ref="H521:H522"/>
+    <mergeCell ref="G272:H272"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G209:H209"/>
+    <mergeCell ref="G175:H175"/>
+    <mergeCell ref="G162:H162"/>
+    <mergeCell ref="G338:H338"/>
+    <mergeCell ref="G460:H460"/>
+    <mergeCell ref="G398:H398"/>
+    <mergeCell ref="G509:H509"/>
+    <mergeCell ref="G496:H496"/>
+    <mergeCell ref="G177:H177"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G204:H204"/>
+    <mergeCell ref="G104:H104"/>
+    <mergeCell ref="G275:H275"/>
+    <mergeCell ref="G475:H475"/>
+    <mergeCell ref="G269:H269"/>
+    <mergeCell ref="G340:H340"/>
+    <mergeCell ref="G462:H462"/>
+    <mergeCell ref="G511:H511"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G302:H302"/>
+    <mergeCell ref="G333:H333"/>
+    <mergeCell ref="G252:H252"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="G366:H366"/>
+    <mergeCell ref="G155:H155"/>
+    <mergeCell ref="G130:H130"/>
+    <mergeCell ref="G391:H391"/>
+    <mergeCell ref="G480:H480"/>
+    <mergeCell ref="G157:H157"/>
+    <mergeCell ref="G132:H132"/>
+    <mergeCell ref="G328:H328"/>
+    <mergeCell ref="G455:H455"/>
+    <mergeCell ref="G122:H122"/>
+    <mergeCell ref="G430:H430"/>
+    <mergeCell ref="G224:H224"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="G172:H172"/>
+    <mergeCell ref="G199:H199"/>
+    <mergeCell ref="G392:H392"/>
+    <mergeCell ref="G386:H386"/>
+    <mergeCell ref="G186:H186"/>
+    <mergeCell ref="G457:H457"/>
+    <mergeCell ref="G484:H484"/>
+    <mergeCell ref="G288:H288"/>
+    <mergeCell ref="G263:H263"/>
+    <mergeCell ref="G152:H152"/>
+    <mergeCell ref="G323:H323"/>
+    <mergeCell ref="G394:H394"/>
+    <mergeCell ref="G499:H499"/>
+    <mergeCell ref="G486:H486"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G212:H212"/>
+    <mergeCell ref="C519:D519"/>
+    <mergeCell ref="G510:H510"/>
+    <mergeCell ref="E519:F519"/>
+    <mergeCell ref="G106:H106"/>
+    <mergeCell ref="G277:H277"/>
+    <mergeCell ref="G448:H448"/>
+    <mergeCell ref="G404:H404"/>
+    <mergeCell ref="G521:G522"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="G105:H105"/>
+    <mergeCell ref="G276:H276"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="G214:H214"/>
+    <mergeCell ref="G341:H341"/>
+    <mergeCell ref="G512:H512"/>
+    <mergeCell ref="G468:H468"/>
+    <mergeCell ref="G120:H120"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G107:H107"/>
+    <mergeCell ref="G278:H278"/>
+    <mergeCell ref="G405:H405"/>
+    <mergeCell ref="G196:H196"/>
+    <mergeCell ref="G419:H419"/>
+    <mergeCell ref="G207:H207"/>
+    <mergeCell ref="G505:H505"/>
+    <mergeCell ref="G225:H225"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G200:H200"/>
+    <mergeCell ref="G271:H271"/>
+    <mergeCell ref="G265:H265"/>
+    <mergeCell ref="G507:H507"/>
+    <mergeCell ref="G227:H227"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G202:H202"/>
+    <mergeCell ref="G273:H273"/>
+    <mergeCell ref="G444:H444"/>
+    <mergeCell ref="G291:H291"/>
+    <mergeCell ref="G331:H331"/>
+    <mergeCell ref="G502:H502"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="G176:H176"/>
+    <mergeCell ref="G347:H347"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="G268:H268"/>
+    <mergeCell ref="G476:H476"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="G128:H128"/>
+    <mergeCell ref="G184:H184"/>
+    <mergeCell ref="G426:H426"/>
+    <mergeCell ref="G171:H171"/>
+    <mergeCell ref="G220:H220"/>
+    <mergeCell ref="G342:H342"/>
+    <mergeCell ref="G413:H413"/>
+    <mergeCell ref="G407:H407"/>
+    <mergeCell ref="G121:H121"/>
+    <mergeCell ref="G357:H357"/>
+    <mergeCell ref="G284:H284"/>
+    <mergeCell ref="G222:H222"/>
+    <mergeCell ref="G344:H344"/>
+    <mergeCell ref="G415:H415"/>
+    <mergeCell ref="G471:H471"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="G123:H123"/>
+    <mergeCell ref="G110:H110"/>
+    <mergeCell ref="G215:H215"/>
+    <mergeCell ref="G408:H408"/>
+    <mergeCell ref="G423:H423"/>
+    <mergeCell ref="G410:H410"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="G439:H439"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G441:H441"/>
+    <mergeCell ref="G497:H497"/>
+    <mergeCell ref="G297:H297"/>
+    <mergeCell ref="G435:H435"/>
+    <mergeCell ref="G362:H362"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="G241:H241"/>
+    <mergeCell ref="G312:H312"/>
+    <mergeCell ref="G508:H508"/>
+    <mergeCell ref="G299:H299"/>
+    <mergeCell ref="G355:H355"/>
+    <mergeCell ref="G293:H293"/>
     <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="G243:H243"/>
+    <mergeCell ref="G388:H388"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="G192:H192"/>
+    <mergeCell ref="G432:H432"/>
+    <mergeCell ref="G428:H428"/>
+    <mergeCell ref="G154:H154"/>
+    <mergeCell ref="G246:H246"/>
+    <mergeCell ref="G129:H129"/>
+    <mergeCell ref="D521:D522"/>
+    <mergeCell ref="G365:H365"/>
+    <mergeCell ref="E520:F522"/>
+    <mergeCell ref="G221:H221"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G463:H463"/>
+    <mergeCell ref="G492:H492"/>
+    <mergeCell ref="G454:H454"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="G131:H131"/>
+    <mergeCell ref="G236:H236"/>
+    <mergeCell ref="G429:H429"/>
+    <mergeCell ref="G223:H223"/>
+    <mergeCell ref="G300:H300"/>
+    <mergeCell ref="G431:H431"/>
+    <mergeCell ref="G287:H287"/>
+    <mergeCell ref="G458:H458"/>
+    <mergeCell ref="G126:H126"/>
+    <mergeCell ref="G289:H289"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="G249:H249"/>
+    <mergeCell ref="G205:H205"/>
+    <mergeCell ref="G376:H376"/>
+    <mergeCell ref="G314:H314"/>
+    <mergeCell ref="G447:H447"/>
+    <mergeCell ref="G363:H363"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G142:H142"/>
+    <mergeCell ref="G313:H313"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="G378:H378"/>
+    <mergeCell ref="G234:H234"/>
+    <mergeCell ref="G305:H305"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="G144:H144"/>
+    <mergeCell ref="G315:H315"/>
+    <mergeCell ref="G442:H442"/>
+    <mergeCell ref="G173:H173"/>
+    <mergeCell ref="G406:H406"/>
+    <mergeCell ref="G473:H473"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G170:H170"/>
+    <mergeCell ref="G437:H437"/>
+    <mergeCell ref="G262:H262"/>
+    <mergeCell ref="G504:H504"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G308:H308"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G326:H326"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="G239:H239"/>
+    <mergeCell ref="G310:H310"/>
+    <mergeCell ref="C521:C522"/>
+    <mergeCell ref="A521:B522"/>
+    <mergeCell ref="G92:H92"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G353:H353"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G290:H290"/>
+    <mergeCell ref="G384:H384"/>
+    <mergeCell ref="G150:H150"/>
+    <mergeCell ref="G255:H255"/>
+    <mergeCell ref="G321:H321"/>
+    <mergeCell ref="G242:H242"/>
+    <mergeCell ref="G478:H478"/>
+    <mergeCell ref="A518:H518"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="G208:H208"/>
+    <mergeCell ref="G379:H379"/>
+    <mergeCell ref="G450:H450"/>
+    <mergeCell ref="G244:H244"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G145:H145"/>
+    <mergeCell ref="G194:H194"/>
+    <mergeCell ref="G316:H316"/>
+    <mergeCell ref="G387:H387"/>
+    <mergeCell ref="G381:H381"/>
+    <mergeCell ref="G181:H181"/>
+    <mergeCell ref="G237:H237"/>
+    <mergeCell ref="G452:H452"/>
+    <mergeCell ref="G479:H479"/>
+    <mergeCell ref="G160:H160"/>
+    <mergeCell ref="G147:H147"/>
+    <mergeCell ref="G174:H174"/>
+    <mergeCell ref="G445:H445"/>
+    <mergeCell ref="G245:H245"/>
+    <mergeCell ref="G494:H494"/>
+    <mergeCell ref="A519:B519"/>
+    <mergeCell ref="G481:H481"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G189:H189"/>
+    <mergeCell ref="G456:H456"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G397:H397"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="G163:H163"/>
+    <mergeCell ref="G334:H334"/>
+    <mergeCell ref="G113:H113"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="G94:H94"/>
+    <mergeCell ref="G165:H165"/>
+    <mergeCell ref="G336:H336"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="G311:H311"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="G158:H158"/>
+    <mergeCell ref="G77:H77"/>
+    <mergeCell ref="G375:H375"/>
+    <mergeCell ref="G169:H169"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G233:H233"/>
+    <mergeCell ref="G469:H469"/>
+    <mergeCell ref="G191:H191"/>
+    <mergeCell ref="G258:H258"/>
+    <mergeCell ref="G451:H451"/>
     <mergeCell ref="G49:H49"/>
     <mergeCell ref="G24:H24"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="G195:H195"/>
+    <mergeCell ref="G266:H266"/>
+    <mergeCell ref="G322:H322"/>
+    <mergeCell ref="G493:H493"/>
+    <mergeCell ref="G260:H260"/>
+    <mergeCell ref="G309:H309"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="G259:H259"/>
     <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G197:H197"/>
+    <mergeCell ref="G324:H324"/>
+    <mergeCell ref="G495:H495"/>
+    <mergeCell ref="G482:H482"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="G261:H261"/>
+    <mergeCell ref="G115:H115"/>
     <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G400:H400"/>
+    <mergeCell ref="G179:H179"/>
     <mergeCell ref="G39:H39"/>
-    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="G166:H166"/>
+    <mergeCell ref="G337:H337"/>
+    <mergeCell ref="G464:H464"/>
+    <mergeCell ref="G402:H402"/>
+    <mergeCell ref="G141:H141"/>
+    <mergeCell ref="G116:H116"/>
+    <mergeCell ref="G500:H500"/>
+    <mergeCell ref="G414:H414"/>
+    <mergeCell ref="G377:H377"/>
+    <mergeCell ref="G352:H352"/>
+    <mergeCell ref="G103:H103"/>
     <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G69:H69"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A73:B74"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="G401:H401"/>
+    <mergeCell ref="G339:H339"/>
+    <mergeCell ref="G466:H466"/>
+    <mergeCell ref="G118:H118"/>
+    <mergeCell ref="G416:H416"/>
+    <mergeCell ref="G167:H167"/>
+    <mergeCell ref="G210:H210"/>
+    <mergeCell ref="G403:H403"/>
     <mergeCell ref="G32:H32"/>
     <mergeCell ref="G63:H63"/>
-    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G330:H330"/>
+    <mergeCell ref="G134:H134"/>
     <mergeCell ref="G50:H50"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="E72:F74"/>
-    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="G286:H286"/>
+    <mergeCell ref="G96:H96"/>
+    <mergeCell ref="G332:H332"/>
+    <mergeCell ref="G503:H503"/>
     <mergeCell ref="G52:H52"/>
+    <mergeCell ref="G350:H350"/>
+    <mergeCell ref="G421:H421"/>
     <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="G396:H396"/>
+    <mergeCell ref="G390:H390"/>
+    <mergeCell ref="G488:H488"/>
+    <mergeCell ref="G156:H156"/>
+    <mergeCell ref="G327:H327"/>
+    <mergeCell ref="G498:H498"/>
+    <mergeCell ref="G93:H93"/>
+    <mergeCell ref="G264:H264"/>
+    <mergeCell ref="G187:H187"/>
+    <mergeCell ref="G485:H485"/>
+    <mergeCell ref="G279:H279"/>
+    <mergeCell ref="G472:H472"/>
+    <mergeCell ref="G124:H124"/>
+    <mergeCell ref="G180:H180"/>
     <mergeCell ref="G45:H45"/>
+    <mergeCell ref="G216:H216"/>
+    <mergeCell ref="G487:H487"/>
+    <mergeCell ref="G343:H343"/>
+    <mergeCell ref="G514:H514"/>
+    <mergeCell ref="G281:H281"/>
+    <mergeCell ref="G501:H501"/>
     <mergeCell ref="G55:H55"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="G188:H188"/>
+    <mergeCell ref="G182:H182"/>
+    <mergeCell ref="G111:H111"/>
+    <mergeCell ref="G424:H424"/>
+    <mergeCell ref="G109:H109"/>
+    <mergeCell ref="G280:H280"/>
     <mergeCell ref="G47:H47"/>
-    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G218:H218"/>
+    <mergeCell ref="G274:H274"/>
+    <mergeCell ref="G345:H345"/>
+    <mergeCell ref="G411:H411"/>
+    <mergeCell ref="G467:H467"/>
+    <mergeCell ref="G516:H516"/>
+    <mergeCell ref="G119:H119"/>
+    <mergeCell ref="G295:H295"/>
     <mergeCell ref="G46:H46"/>
-    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G211:H211"/>
+    <mergeCell ref="G282:H282"/>
+    <mergeCell ref="G409:H409"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.25" bottom="0.25" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="65" fitToHeight="2" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="65" fitToHeight="16" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C受控模板 sip-v1</oddFooter>
@@ -1914,8 +6879,22 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
+  <rowBreaks count="15" manualBreakCount="15">
     <brk id="37" min="0" max="16383" man="1"/>
+    <brk id="69" min="0" max="16383" man="1"/>
+    <brk id="101" min="0" max="16383" man="1"/>
+    <brk id="133" min="0" max="16383" man="1"/>
+    <brk id="165" min="0" max="16383" man="1"/>
+    <brk id="197" min="0" max="16383" man="1"/>
+    <brk id="229" min="0" max="16383" man="1"/>
+    <brk id="261" min="0" max="16383" man="1"/>
+    <brk id="293" min="0" max="16383" man="1"/>
+    <brk id="325" min="0" max="16383" man="1"/>
+    <brk id="357" min="0" max="16383" man="1"/>
+    <brk id="389" min="0" max="16383" man="1"/>
+    <brk id="421" min="0" max="16383" man="1"/>
+    <brk id="453" min="0" max="16383" man="1"/>
+    <brk id="485" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
